--- a/seo_inventory_report.xlsx
+++ b/seo_inventory_report.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SEO AdSense 盤點'!$A$1:$K$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SEO AdSense 盤點'!$A$1:$K$154</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -157,8 +157,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SEOInventory" displayName="SEOInventory" ref="A1:K168" headerRowCount="1">
-  <autoFilter ref="A1:K168"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SEOInventory" displayName="SEOInventory" ref="A1:K154" headerRowCount="1">
+  <autoFilter ref="A1:K154"/>
   <tableColumns count="11">
     <tableColumn id="1" name="編號"/>
     <tableColumn id="2" name="頁面分類"/>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K168"/>
+  <dimension ref="A1:K154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -579,7 +579,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 未配置（合規）</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
@@ -3910,17 +3910,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>法律條款</t>
+          <t>首頁</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>en/contact.html</t>
+          <t>en/index.html</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/contact.html</t>
+          <t>https://gugopro.com/en/index.html</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Contact Us | GugoPro Official</t>
+          <t>GugoPro Official Homepage | AI and Utility Tools</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>Web AI, data and utility tools for everyday work.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>156</v>
+        <v>108</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -3961,17 +3961,17 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>en/index.html</t>
+          <t>en/tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/index.html</t>
+          <t>https://gugopro.com/en/tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>GugoPro Official Homepage | AI and Utility Tools</t>
+          <t>Redirecting - AI Multilingual Speaking Tutor | GugoPro</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Web AI, data and utility tools for everyday work.</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3996,14 +3996,14 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4012,17 +4012,17 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>法律條款</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>en/legal/about.html</t>
+          <t>en/tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/legal/about.html</t>
+          <t>https://gugopro.com/en/tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>About GugoPro | GugoPro</t>
+          <t>Redirecting - Face-to-Face Travel Voice Translator | GugoPro</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>About GugoPro</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4063,17 +4063,17 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>法律條款</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>en/legal/contact.html</t>
+          <t>en/tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/legal/contact.html</t>
+          <t>https://gugopro.com/en/tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4083,12 +4083,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Contact Us | GugoPro</t>
+          <t>Redirecting - AI Tarot Master | GugoPro</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4098,14 +4098,14 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4114,17 +4114,17 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>法律條款</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>en/legal/disclaimer.html</t>
+          <t>en/tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/legal/disclaimer.html</t>
+          <t>https://gugopro.com/en/tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4134,12 +4134,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer | GugoPro</t>
+          <t>Redirecting - GugoPro AI Ziwei Astrology Master | GugoPro</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4149,14 +4149,14 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4165,17 +4165,17 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>法律條款</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>en/legal/privacy.html</t>
+          <t>en/tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/legal/privacy.html</t>
+          <t>https://gugopro.com/en/tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Privacy Policy | GugoPro</t>
+          <t>Redirecting - YouTube Sequel Tracker | GugoPro</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Privacy Policy</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4200,14 +4200,14 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4216,17 +4216,17 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>法律條款</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>en/legal/terms.html</t>
+          <t>en/tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/legal/terms.html</t>
+          <t>https://gugopro.com/en/tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Terms of Service | GugoPro</t>
+          <t>Redirecting - YouTube Study Player | GugoPro</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Terms of Service</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4251,14 +4251,14 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai/english-speaking-tutor.html</t>
+          <t>en/tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai/english-speaking-tutor.html</t>
+          <t>https://gugopro.com/en/tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - AI Multilingual Speaking Tutor | GugoPro</t>
+          <t>Redirecting - AI Nutritionist | GugoPro</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai/realtime-translator.html</t>
+          <t>en/tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai/realtime-translator.html</t>
+          <t>https://gugopro.com/en/tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - Face-to-Face Travel Voice Translator | GugoPro</t>
+          <t>Redirecting - AI Weight Loss Coach | GugoPro</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai/tarot-master.html</t>
+          <t>en/tools/pdf/pdf-suite.html</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai/tarot-master.html</t>
+          <t>https://gugopro.com/en/tools/pdf/pdf-suite.html</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - AI Tarot Master | GugoPro</t>
+          <t>Redirecting - PDF Suite | GugoPro</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -4420,29 +4420,21 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai/ziwei-astrology.html</t>
+          <t>googled0dfad57039c64f6.html</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai/ziwei-astrology.html</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>Redirecting - GugoPro AI Ziwei Astrology Master | GugoPro</t>
-        </is>
-      </c>
+          <t>https://gugopro.com/googled0dfad57039c64f6.html</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
@@ -4462,7 +4454,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4471,32 +4463,32 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>首頁</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai-media/ai-video-tracker.html</t>
+          <t>index.html</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai-media/ai-video-tracker.html</t>
+          <t>https://gugopro.com/index.html</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - YouTube Sequel Tracker | GugoPro</t>
+          <t>GugoPro 工具箱｜YouTube 雙語字幕學習、AI 翻譯塔羅、TDEE 減脂計算與跨境選品等 10 款免費免安裝工具</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>GugoPro 工具箱</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4506,14 +4498,14 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80">
@@ -4522,17 +4514,17 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>首頁</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>en/tools/english/l-player-study.html</t>
+          <t>index_en.html</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/english/l-player-study.html</t>
+          <t>https://gugopro.com/index_en.html</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4542,12 +4534,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - YouTube Study Player | GugoPro</t>
+          <t>GugoPro Hub | 10 Free Browser Tools for YouTube Study, AI Translation &amp; Tarot, TDEE, and Product Research</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>GugoPro Hub</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4557,14 +4549,14 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81">
@@ -4573,32 +4565,32 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>首頁</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>en/tools/health/tdee-macros-calculator.html</t>
+          <t>index_ja.html</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/health/tdee-macros-calculator.html</t>
+          <t>https://gugopro.com/index_ja.html</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - AI Nutritionist | GugoPro</t>
+          <t>GugoPro ツールボックス｜YouTube 2言語字幕学習、AI 翻訳タロット、TDEE 減脂計算、越境EC商品選定など無料ブラウザツール10選</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>GugoPro ツールボックス</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4608,14 +4600,14 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82">
@@ -4624,32 +4616,32 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>en/tools/health/weight-loss-planner.html</t>
+          <t>ja/articles/affective-filter-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/health/weight-loss-planner.html</t>
+          <t>https://gugopro.com/ja/articles/affective-filter-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - AI Weight Loss Coach | GugoPro</t>
+          <t>話す恐怖を克服する心理学：クラッシェンの「情意フィルター仮説」、外国語不安（FLA）と AI チューターのゼロ圧力スピーキング完全ガイド｜GugoPro 言語学習コラム</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>話す恐怖を克服する心理学：クラッシェンの「情意フィルター仮説」、外国語不安（FLA）と AI チューターのゼロ圧力スピーキング完全ガイド</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4659,14 +4651,14 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -4675,32 +4667,32 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>歷史工具</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>en/tools/pdf/pdf-suite.html</t>
+          <t>ja/articles/amazon-ai-product-research-guide.html</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/pdf/pdf-suite.html</t>
+          <t>https://gugopro.com/ja/articles/amazon-ai-product-research-guide.html</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - PDF Suite | GugoPro</t>
+          <t>2026 越境EC・高精度リサーチ完全攻略：AIセマンティック・リバースエンジニアリングによるAmazonヒット商品開発、競合低評価（VOC）痛点分析とListingキーワード配置マトリクス｜GugoPro EC戦略コラム</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>2026 越境EC・高精度リサーチ完全攻略：AIセマンティック・リバースエンジニアリングによるAmazonヒット商品開発、競合低評価（VOC）痛点分析とListingキーワード配置マトリクス</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4710,11 +4702,11 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>1</v>
@@ -4726,24 +4718,32 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>googled0dfad57039c64f6.html</t>
+          <t>ja/articles/carb-cycling-and-home-workout-guide.html</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/googled0dfad57039c64f6.html</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr"/>
+          <t>https://gugopro.com/ja/articles/carb-cycling-and-home-workout-guide.html</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>炭水化物循環法（カーボサイクル）完全減脂ガイド：高・低炭水化物日の生化学機序、器具不要の自宅燃焼ルーティン、筋分解防止の極意｜GugoPro 運動生理学コラム</t>
+        </is>
+      </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>炭水化物循環法（カーボサイクル）完全減脂ガイド：高・低炭水化物日の生化学機序、器具不要の自宅燃焼ルーティン、筋分解防止の極意</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4753,14 +4753,14 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>guides/risk-reward-ratio.html</t>
+          <t>ja/articles/diabetes-and-insulin-resistance-guide.html</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/guides/risk-reward-ratio.html</t>
+          <t>https://gugopro.com/ja/articles/diabetes-and-insulin-resistance-guide.html</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>zh-Hant</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>交易風險報酬比（R:R）｜GugoPro 財經學院</t>
+          <t>糖尿病予備群・インスリン抵抗性の食事法完全ガイド：GI/GL値・カーボカウントからAI写真食事管理まで——血糖値スパイクを防ぐ栄養素調控｜GugoPro 代謝医学コラム</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>交易風險報酬比（R:R）：先理解，再計算，最後管理風險。</t>
+          <t>糖尿病予備群・インスリン抵抗性の食事法完全ガイド：GI/GL値・カーボカウントからAI写真食事管理まで——血糖値スパイクを防ぐ栄養素調控</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -4820,32 +4820,32 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>index.html</t>
+          <t>ja/articles/english-intro-break-the-ice.html</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/index.html</t>
+          <t>https://gugopro.com/ja/articles/english-intro-break-the-ice.html</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>zh-TW</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>GugoPro 工具箱｜YouTube 雙語字幕學習、AI 翻譯塔羅、TDEE 減脂計算與跨境選品等 10 款免費免安裝工具</t>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイング完全ガイド｜GugoPro 言語科学コラム</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>GugoPro 工具箱</t>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4859,10 +4859,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>214</v>
+        <v>170</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>index_en.html</t>
+          <t>ja/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/index_en.html</t>
+          <t>https://gugopro.com/ja/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>GugoPro Hub | 10 Free Browser Tools for YouTube Study, AI Translation &amp; Tarot, TDEE, and Product Research</t>
+          <t>脂肪肝を逆転する減糖＆地中海食完全ガイド：内臓脂肪燃焼からPFC黄金比率・外食AI管理まで——MASLDを根本改善する長寿実戦マニュアル｜GugoPro 肝臓代謝コラム</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>GugoPro Hub</t>
+          <t>脂肪肝を逆転する減糖＆地中海食完全ガイド：内臓脂肪燃焼からPFC黄金比率・外食AI管理まで——MASLDを根本改善する長寿実戦マニュアル</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>396</v>
+        <v>206</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -4922,17 +4922,17 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>index_ja.html</t>
+          <t>ja/articles/gemini-api-free-tier-and-developer-guide.html</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/index_ja.html</t>
+          <t>https://gugopro.com/ja/articles/gemini-api-free-tier-and-developer-guide.html</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4942,12 +4942,12 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>GugoPro ツールボックス｜YouTube 2言語字幕学習、AI 翻訳タロット、TDEE 減脂計算、越境EC商品選定など無料ブラウザツール10選</t>
+          <t>2026 開発者完全攻略ハンドブック：Google Gemini 公式無料APIを活用したゼロコスト商用グレードアプリのアーキテクチャ設計とエラー完全トラブルシューティング指南｜GugoPro クラウドシステムコラム</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>GugoPro ツールボックス</t>
+          <t>2026 開発者完全攻略ハンドブック：Google Gemini 公式無料APIを活用したゼロコスト商用グレードアプリのアーキテクチャ設計とエラー完全トラブルシューティング指南</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>213</v>
+        <v>271</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/affective-filter-with-ai-tutor.html</t>
+          <t>ja/articles/how-to-master-tarot-guide.html</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/affective-filter-with-ai-tutor.html</t>
+          <t>https://gugopro.com/ja/articles/how-to-master-tarot-guide.html</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>話す恐怖を克服する心理学：クラッシェンの「情意フィルター仮説」、外国語不安（FLA）と AI チューターのゼロ圧力スピーキング完全ガイド｜GugoPro 言語学習コラム</t>
+          <t>タロットマスターへの道：78枚の丸暗記を脱し「直観的フロー・リーディング」へ——古典記号論、ナラティブ心理学、AI協同による限界的練習完全ガイド｜GugoPro 意思決定科学コラム</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>話す恐怖を克服する心理学：クラッシェンの「情意フィルター仮説」、外国語不安（FLA）と AI チューターのゼロ圧力スピーキング完全ガイド</t>
+          <t>如何にしてタロットマスターとなるか？ 78枚の意味の丸暗記から「直観的フロー・リーディング」へ：古典記号論・ナラティブ心理学・AI協同による限界的練習完全手引</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>221</v>
+        <v>145</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>2</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/amazon-ai-product-research-guide.html</t>
+          <t>ja/articles/how-to-master-ziwei-guide.html</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/amazon-ai-product-research-guide.html</t>
+          <t>https://gugopro.com/ja/articles/how-to-master-ziwei-guide.html</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5044,12 +5044,12 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026 越境EC・高精度リサーチ完全攻略：AIセマンティック・リバースエンジニアリングによるAmazonヒット商品開発、競合低評価（VOC）痛点分析とListingキーワード配置マトリクス｜GugoPro EC戦略コラム</t>
+          <t>紫微斗数マスターへの道：百の星の丸暗記を脱し「動態格局解盤」へ——文化記号論、システムダイナミクス、AI協同による限界的練習完全ガイド｜GugoPro 意思決定科学コラム</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>2026 越境EC・高精度リサーチ完全攻略：AIセマンティック・リバースエンジニアリングによるAmazonヒット商品開発、競合低評価（VOC）痛点分析とListingキーワード配置マトリクス</t>
+          <t>紫微斗数マスターへの道：百の星の丸暗記を脱し「動態格局解盤」へ——文化記号論、システムダイナミクス、AI協同による限界的練習完全ガイド</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5063,10 +5063,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>227</v>
+        <v>199</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/carb-cycling-and-home-workout-guide.html</t>
+          <t>ja/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/carb-cycling-and-home-workout-guide.html</t>
+          <t>https://gugopro.com/ja/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>炭水化物循環法（カーボサイクル）完全減脂ガイド：高・低炭水化物日の生化学機序、器具不要の自宅燃焼ルーティン、筋分解防止の極意｜GugoPro 運動生理学コラム</t>
+          <t>168断食はカロリー計算より本当に痩せるのか？細胞自噬、インスリン仮説からエネルギー赤字の真相まで：リバウンドと筋肉減少の罠を解体する完全ガイド｜GugoPro 代謝内分泌コラム</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>炭水化物循環法（カーボサイクル）完全減脂ガイド：高・低炭水化物日の生化学機序、器具不要の自宅燃焼ルーティン、筋分解防止の極意</t>
+          <t>168断食はカロリー計算より本当に痩せるのか？細胞自噬、インスリン仮説からエネルギー赤字の真相まで：リバウンドと筋肉減少の罠を解体する完全ガイド</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>2</v>
@@ -5131,12 +5131,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/diabetes-and-insulin-resistance-guide.html</t>
+          <t>ja/articles/investment/01-compound-interest-guide.html</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/diabetes-and-insulin-resistance-guide.html</t>
+          <t>https://gugopro.com/ja/articles/investment/01-compound-interest-guide.html</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>糖尿病予備群・インスリン抵抗性の食事法完全ガイド：GI/GL値・カーボカウントからAI写真食事管理まで——血糖値スパイクを防ぐ栄養素調控｜GugoPro 代謝医学コラム</t>
+          <t>複利効果と時間価値：バランスシートから最初のファイナンシャルシステムを構築するには？ | GugoPro Academy</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>糖尿病予備群・インスリン抵抗性の食事法完全ガイド：GI/GL値・カーボカウントからAI写真食事管理まで——血糖値スパイクを防ぐ栄養素調控</t>
+          <t>複利効果と時間価値：バランスシートから最初のファイナンシャルシステムを構築するには？</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>164</v>
+        <v>43</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/english-intro-break-the-ice.html</t>
+          <t>ja/articles/investment/02-etf-investing-bible.html</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/english-intro-break-the-ice.html</t>
+          <t>https://gugopro.com/ja/articles/investment/02-etf-investing-bible.html</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイング完全ガイド｜GugoPro 言語科学コラム</t>
+          <t>インデックス投資バイブル：台湾 0050/006208 vs 米国 VTI/VOO/QQQ 完全解析 | GugoPro Academy</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
+          <t>インデックス投資バイブル：台湾 0050/006208 vs 米国 VTI/VOO/QQQ 完全解析</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>170</v>
+        <v>63</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
+          <t>ja/articles/investment/03-asset-allocation-rebalancing.html</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
+          <t>https://gugopro.com/ja/articles/investment/03-asset-allocation-rebalancing.html</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>脂肪肝を逆転する減糖＆地中海食完全ガイド：内臓脂肪燃焼からPFC黄金比率・外食AI管理まで——MASLDを根本改善する長寿実戦マニュアル｜GugoPro 肝臓代謝コラム</t>
+          <t>資産配分と動的リバランス：目標ウェイトから取引摩擦まで｜GugoPro Academy</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>脂肪肝を逆転する減糖＆地中海食完全ガイド：内臓脂肪燃焼からPFC黄金比率・外食AI管理まで——MASLDを根本改善する長寿実戦マニュアル</t>
+          <t>資産配分と動的リバランス： 目標ウェイトを実行可能な意思決定ルールにする。</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>206</v>
+        <v>88</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/gemini-api-free-tier-and-developer-guide.html</t>
+          <t>ja/articles/investment/04-brokerage-comparison.html</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/gemini-api-free-tier-and-developer-guide.html</t>
+          <t>https://gugopro.com/ja/articles/investment/04-brokerage-comparison.html</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026 開発者完全攻略ハンドブック：Google Gemini 公式無料APIを活用したゼロコスト商用グレードアプリのアーキテクチャ設計とエラー完全トラブルシューティング指南｜GugoPro クラウドシステムコラム</t>
+          <t>米国ブローカー口座開設完全ガイド：台湾の複委託 vs 海外ブローカー | GugoPro Academy</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>2026 開発者完全攻略ハンドブック：Google Gemini 公式無料APIを活用したゼロコスト商用グレードアプリのアーキテクチャ設計とエラー完全トラブルシューティング指南</t>
+          <t>米国ブローカー口座開設完全ガイド：台湾の複委託 vs 海外ブローカー（Firstrade、IB、Schwab）比較</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>271</v>
+        <v>63</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/how-to-master-tarot-guide.html</t>
+          <t>ja/articles/investment/05-fundamental-valuation-metrics.html</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/how-to-master-tarot-guide.html</t>
+          <t>https://gugopro.com/ja/articles/investment/05-fundamental-valuation-metrics.html</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>タロットマスターへの道：78枚の丸暗記を脱し「直観的フロー・リーディング」へ——古典記号論、ナラティブ心理学、AI協同による限界的練習完全ガイド｜GugoPro 意思決定科学コラム</t>
+          <t>ファンダメンタル評価指標：P/E、P/B、ROE | GugoPro Academy</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>如何にしてタロットマスターとなるか？ 78枚の意味の丸暗記から「直観的フロー・リーディング」へ：古典記号論・ナラティブ心理学・AI協同による限界的練習完全手引</t>
+          <t>ファンダメンタル評価指標：P/E（株価収益率）、P/B（株価純資産倍率）、ROEの正しい読み方</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>145</v>
+        <v>61</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -5386,12 +5386,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/how-to-master-ziwei-guide.html</t>
+          <t>ja/articles/investment/06-sharpe-mdd-risk-control.html</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/how-to-master-ziwei-guide.html</t>
+          <t>https://gugopro.com/ja/articles/investment/06-sharpe-mdd-risk-control.html</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>紫微斗数マスターへの道：百の星の丸暗記を脱し「動態格局解盤」へ——文化記号論、システムダイナミクス、AI協同による限界的練習完全ガイド｜GugoPro 意思決定科学コラム</t>
+          <t>リスクリターンと最大ドローダウン分析：Sharpe、Sortino、Calmar 実装ガイド｜GugoPro Academy</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>紫微斗数マスターへの道：百の星の丸暗記を脱し「動態格局解盤」へ——文化記号論、システムダイナミクス、AI協同による限界的練習完全ガイド</t>
+          <t>リスクリターンと最大ドローダウンの分析</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5420,10 +5420,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
+          <t>ja/articles/investment/07-fire-4-percent-rule.html</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
+          <t>https://gugopro.com/ja/articles/investment/07-fire-4-percent-rule.html</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>168断食はカロリー計算より本当に痩せるのか？細胞自噬、インスリン仮説からエネルギー赤字の真相まで：リバウンドと筋肉減少の罠を解体する完全ガイド｜GugoPro 代謝内分泌コラム</t>
+          <t>【退職金プラン】FIRE ムーブメントと 4% ルールとは？引き出し率と退職資金の不足額の計算方法 | GugoPro Academy</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>168断食はカロリー計算より本当に痩せるのか？細胞自噬、インスリン仮説からエネルギー赤字の真相まで：リバウンドと筋肉減少の罠を解体する完全ガイド</t>
+          <t>【退職金プラン】FIRE ムーブメントと 4% ルールとは？引き出し率と退職資金の不足額の計算方法</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>233</v>
+        <v>85</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/01-compound-interest-guide.html</t>
+          <t>ja/articles/investment/08-overseas-tax-guide.html</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/01-compound-interest-guide.html</t>
+          <t>https://gugopro.com/ja/articles/investment/08-overseas-tax-guide.html</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>複利効果と時間価値：バランスシートから最初のファイナンシャルシステムを構築するには？ | GugoPro Academy</t>
+          <t>【節税と確定申告】米国株投資はどう申告するか？海外所得 750 萬 の免税枠と 30% 配当源泉徴収の実務 | GugoPro Academy</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>複利効果と時間価値：バランスシートから最初のファイナンシャルシステムを構築するには？</t>
+          <t>【節税と確定申告】米国株投資はどう申告するか？海外所得 750 萬 の免税枠と 30% 配当源泉徴収の実務</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5522,10 +5522,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/02-etf-investing-bible.html</t>
+          <t>ja/articles/investment/09-high-dividend-etf-trap.html</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/02-etf-investing-bible.html</t>
+          <t>https://gugopro.com/ja/articles/investment/09-high-dividend-etf-trap.html</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>インデックス投資バイブル：台湾 0050/006208 vs 米国 VTI/VOO/QQQ 完全解析 | GugoPro Academy</t>
+          <t>【高配当 ETF 評価】台湾上場 ETF 00878/00919/00929 vs 米国 ETF SCHD：高配当利回りの罠を解くと総リターンの真実が見える | GugoPro Academy</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>インデックス投資バイブル：台湾 0050/006208 vs 米国 VTI/VOO/QQQ 完全解析</t>
+          <t>【高配当 ETF 評価】台湾上場 ETF 00878/00919/00929 vs 米国 ETF SCHD：高配当利回りの罠を解くと総リターンの真実が見える</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5590,12 +5590,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/03-asset-allocation-rebalancing.html</t>
+          <t>ja/articles/investment/10-bond-investing-guide.html</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/03-asset-allocation-rebalancing.html</t>
+          <t>https://gugopro.com/ja/articles/investment/10-bond-investing-guide.html</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5605,12 +5605,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>資産配分と動的リバランス：目標ウェイトから取引摩擦まで｜GugoPro Academy</t>
+          <t>【債券投資ガイド】米国債 (TLT/IEF) vs 投資適格社債 (LQD)：利下げサイクルにおける資産配分戦略 | GugoPro Academy</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>資産配分と動的リバランス： 目標ウェイトを実行可能な意思決定ルールにする。</t>
+          <t>【債券投資ガイド】米国債 (TLT/IEF) vs 投資適格社債 (LQD)：利下げサイクルにおける資産配分戦略</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/04-brokerage-comparison.html</t>
+          <t>ja/articles/investment/11-brokerage-deep-review.html</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/04-brokerage-comparison.html</t>
+          <t>https://gugopro.com/ja/articles/investment/11-brokerage-deep-review.html</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>米国ブローカー口座開設完全ガイド：台湾の複委託 vs 海外ブローカー | GugoPro Academy</t>
+          <t>【海外証券会社評価大全】IB（盈透／Interactive Brokers）、Firstrade、Charles Schwab（嘉信理財）─ 長所・短所、安全性と隠れたコスト比較 | GugoPro Academy</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>米国ブローカー口座開設完全ガイド：台湾の複委託 vs 海外ブローカー（Firstrade、IB、Schwab）比較</t>
+          <t>【海外証券会社評価大全】IB（盈透／Interactive Brokers）、Firstrade、Charles Schwab（嘉信理財）─ 長所・短所、安全性と隠れたコスト比較</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/05-fundamental-valuation-metrics.html</t>
+          <t>ja/articles/investment/12-inflation-hedging-reits-gold.html</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/05-fundamental-valuation-metrics.html</t>
+          <t>https://gugopro.com/ja/articles/investment/12-inflation-hedging-reits-gold.html</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>ファンダメンタル評価指標：P/E、P/B、ROE | GugoPro Academy</t>
+          <t>【ヘッジ資産】金（GLD）と不動産投資信託（REITs）はインフレ対策として資産配分にどう組み込むか？ | GugoPro Academy</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>ファンダメンタル評価指標：P/E（株価収益率）、P/B（株価純資産倍率）、ROEの正しい読み方</t>
+          <t>【ヘッジ資産】金（GLD）と不動産投資信託（REITs）はインフレ対策として資産配分にどう組み込むか？</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/06-sharpe-mdd-risk-control.html</t>
+          <t>ja/articles/investment/13-technical-indicators-truth.html</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/06-sharpe-mdd-risk-control.html</t>
+          <t>https://gugopro.com/ja/articles/investment/13-technical-indicators-truth.html</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>リスクリターンと最大ドローダウン分析：Sharpe、Sortino、Calmar 実装ガイド｜GugoPro Academy</t>
+          <t>【テクニカル分析の真実】移動平均線 (MA)、RSI、MACD は本当に役立つのか？クオンツトレーダーが見るテクニカル指標の有効場面と盲点 | GugoPro Academy</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>リスクリターンと最大ドローダウンの分析</t>
+          <t>【テクニカル分析の真実】移動平均線 (MA)、RSI、MACD は本当に役立つのか？クオンツトレーダーが見るテクニカル指標の有効場面と盲点</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5794,12 +5794,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/07-fire-4-percent-rule.html</t>
+          <t>ja/articles/investment/14-backtesting-overfitting-guide.html</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/07-fire-4-percent-rule.html</t>
+          <t>https://gugopro.com/ja/articles/investment/14-backtesting-overfitting-guide.html</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>【退職金プラン】FIRE ムーブメントと 4% ルールとは？引き出し率と退職資金の不足額の計算方法 | GugoPro Academy</t>
+          <t>【システムトレード】バックテスト (Backtesting/回測) とは？過学習 (Overfitting/過度擬合) と歴史的罠を避ける方法 | GugoPro Academy</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>【退職金プラン】FIRE ムーブメントと 4% ルールとは？引き出し率と退職資金の不足額の計算方法</t>
+          <t>【システムトレード】バックテスト (Backtesting/回測) とは？過学習 (Overfitting/過度擬合) と歴史的罠を避ける方法</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -5845,12 +5845,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/08-overseas-tax-guide.html</t>
+          <t>ja/articles/investment/15-quant-research-workflow.html</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/08-overseas-tax-guide.html</t>
+          <t>https://gugopro.com/ja/articles/investment/15-quant-research-workflow.html</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>【節税と確定申告】米国株投資はどう申告するか？海外所得 750 萬 の免税枠と 30% 配当源泉徴収の実務 | GugoPro Academy</t>
+          <t>量的研究ワークフロー：5MAオフセット、ボラティリティのZ‑Score、アウト‑オブ‑サンプルバックテスト｜GugoPro Academy Z-Score</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>【節税と確定申告】米国株投資はどう申告するか？海外所得 750 萬 の免税枠と 30% 配当源泉徴収の実務</t>
+          <t>量的研究ワークフロー： 5MA、ボラティリティ、バックテストを同じ証拠チェーンに組み込む。</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5879,7 +5879,7 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -5896,12 +5896,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/09-high-dividend-etf-trap.html</t>
+          <t>ja/articles/investment/16-futures-pairs-basis.html</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/09-high-dividend-etf-trap.html</t>
+          <t>https://gugopro.com/ja/articles/investment/16-futures-pairs-basis.html</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5911,12 +5911,12 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>【高配当 ETF 評価】台湾上場 ETF 00878/00919/00929 vs 米国 ETF SCHD：高配当利回りの罠を解くと総リターンの真実が見える | GugoPro Academy</t>
+          <t>臺指期／富台期のペア取引と期現價差：Basisからロールリスクまで｜GugoPro Academy</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>【高配当 ETF 評価】台湾上場 ETF 00878/00919/00929 vs 米国 ETF SCHD：高配当利回りの罠を解くと総リターンの真実が見える</t>
+          <t>臺指期／富台期ペア取引： まず Basis を分解し、その後で裁定について議論する。</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -5947,12 +5947,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/10-bond-investing-guide.html</t>
+          <t>ja/articles/investment/17-practical-trading.html</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/10-bond-investing-guide.html</t>
+          <t>https://gugopro.com/ja/articles/investment/17-practical-trading.html</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>【債券投資ガイド】米国債 (TLT/IEF) vs 投資適格社債 (LQD)：利下げサイクルにおける資産配分戦略 | GugoPro Academy</t>
+          <t>第13類 実戦取引：取引計画、実行、リスク管理、レビューの完全なナレッジツリー｜GugoPro Academy</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>【債券投資ガイド】米国債 (TLT/IEF) vs 投資適格社債 (LQD)：利下げサイクルにおける資産配分戦略</t>
+          <t>実戦トレーディング： アイデアを実行可能でストップが設定でき、再検討できるプロセスにする。</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/11-brokerage-deep-review.html</t>
+          <t>ja/articles/investment/18-trend-following-breakout-playbook.html</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/11-brokerage-deep-review.html</t>
+          <t>https://gugopro.com/ja/articles/investment/18-trend-following-breakout-playbook.html</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>【海外証券会社評価大全】IB（盈透／Interactive Brokers）、Firstrade、Charles Schwab（嘉信理財）─ 長所・短所、安全性と隠れたコスト比較 | GugoPro Academy</t>
+          <t>トレンド追跡とブレイクアウト戦略プレイブック：ルール、ポジション、フェイクブレイク、バックテスト検証｜GugoPro Academy</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>【海外証券会社評価大全】IB（盈透／Interactive Brokers）、Firstrade、Charles Schwab（嘉信理財）─ 長所・短所、安全性と隠れたコスト比較</t>
+          <t>トレンド追跡とブレイクアウト戦略： 自分の「見解」を検証可能なルールに書き換える。</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6044,17 +6044,17 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>首頁</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/12-inflation-hedging-reits-gold.html</t>
+          <t>ja/articles/investment/index.html</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/12-inflation-hedging-reits-gold.html</t>
+          <t>https://gugopro.com/ja/articles/investment/index.html</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>【ヘッジ資産】金（GLD）と不動産投資信託（REITs）はインフレ対策として資産配分にどう組み込むか？ | GugoPro Academy</t>
+          <t>投資教育アカデミー | GugoPro Academy</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>【ヘッジ資産】金（GLD）と不動産投資信託（REITs）はインフレ対策として資産配分にどう組み込むか？</t>
+          <t>システム化 投資教育と実戦のマトリクス</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6100,12 +6100,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/13-technical-indicators-truth.html</t>
+          <t>ja/articles/modern-ziwei-guide.html</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/13-technical-indicators-truth.html</t>
+          <t>https://gugopro.com/ja/articles/modern-ziwei-guide.html</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>【テクニカル分析の真実】移動平均線 (MA)、RSI、MACD は本当に役立つのか？クオンツトレーダーが見るテクニカル指標の有効場面と盲点 | GugoPro Academy</t>
+          <t>宿命論とオカルト的脅迫からの脱却：現代心理学で再構築する紫微斗数——十二宮位、四化の動態からAI意思決定反省モデルへ｜GugoPro 意思決定科学コラム</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>【テクニカル分析の真実】移動平均線 (MA)、RSI、MACD は本当に役立つのか？クオンツトレーダーが見るテクニカル指標の有効場面と盲点</t>
+          <t>宿命論とオカルト的脅迫からの脱却：現代心理学で再構築する紫微斗数——十二宮位、四化の動態からAI意思決定反省モデルへ</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>80</v>
+        <v>169</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/14-backtesting-overfitting-guide.html</t>
+          <t>ja/articles/shadowing-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/14-backtesting-overfitting-guide.html</t>
+          <t>https://gugopro.com/ja/articles/shadowing-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>【システムトレード】バックテスト (Backtesting/回測) とは？過学習 (Overfitting/過度擬合) と歴史的罠を避ける方法 | GugoPro Academy</t>
+          <t>「話せない英語」にサヨナラ！シャドーイング、CEFR文脈出力、AIチューターによるスピーキング実践ガイド｜GugoPro 言語科学コラム</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>【システムトレード】バックテスト (Backtesting/回測) とは？過学習 (Overfitting/過度擬合) と歴史的罠を避ける方法</t>
+          <t>「話せない英語」にサヨナラ！シャドーイング、CEFR文脈輸出、AIチューターによるスピーキング実践ガイド</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/15-quant-research-workflow.html</t>
+          <t>ja/articles/tarot-decision-framework.html</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/15-quant-research-workflow.html</t>
+          <t>https://gugopro.com/ja/articles/tarot-decision-framework.html</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>量的研究ワークフロー：5MAオフセット、ボラティリティのZ‑Score、アウト‑オブ‑サンプルバックテスト｜GugoPro Academy Z-Score</t>
+          <t>迷信的宿命論からの脱却：ユングの「元型」心理学・共時性からAIタロットへ——キャリアの二者択一と関係性不安を解体する構造化意思決定モデル｜GugoPro 意思決定科学コラム</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>量的研究ワークフロー： 5MA、ボラティリティ、バックテストを同じ証拠チェーンに組み込む。</t>
+          <t>迷信的宿命論からの脱却：ユングの「元型」心理学・共時性からAIタロットへ——キャリアの二者択一と関係性不安を解体する構造化意思決定モデル</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6236,10 +6236,10 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>92</v>
+        <v>161</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -6253,12 +6253,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/16-futures-pairs-basis.html</t>
+          <t>ja/articles/tblt-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/16-futures-pairs-basis.html</t>
+          <t>https://gugopro.com/ja/articles/tblt-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>臺指期／富台期のペア取引と期現價差：Basisからロールリスクまで｜GugoPro Academy</t>
+          <t>丸暗記にサヨナラ！タスク型教授法（TBLT）、Robinson認知仮説とAIチューターによる英会話実践ガイド｜GugoPro 言語科学コラム</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>臺指期／富台期ペア取引： まず Basis を分解し、その後で裁定について議論する。</t>
+          <t>丸暗記にサヨナラ！タスク型教授法（TBLT）、Robinson認知仮説とAIチューターによる英会話実践ガイド</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6287,10 +6287,10 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>84</v>
+        <v>184</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/17-practical-trading.html</t>
+          <t>ja/articles/tdee-and-macros-guide.html</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/17-practical-trading.html</t>
+          <t>https://gugopro.com/ja/articles/tdee-and-macros-guide.html</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>第13類 実戦取引：取引計画、実行、リスク管理、レビューの完全なナレッジツリー｜GugoPro Academy</t>
+          <t>無駄な食事制限とリバウンドを完全に卒業！熱力学エネルギー収支、適応熱産生からAI食事解析まで：外食派のためのTDEE＆PFCバランス精密調整バイブル｜GugoPro 代謝健康專欄</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>実戦トレーディング： アイデアを実行可能でストップが設定でき、再検討できるプロセスにする。</t>
+          <t>無駄な食事制限とリバウンドを完全に卒業！熱力学エネルギー収支、適応熱産生からAI食事解析まで：外食派のためのTDEE＆PFCバランス精密調整バイブル</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6338,10 +6338,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>89</v>
+        <v>248</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/18-trend-following-breakout-playbook.html</t>
+          <t>ja/articles/travel-translator-guide.html</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/18-trend-following-breakout-playbook.html</t>
+          <t>https://gugopro.com/ja/articles/travel-translator-guide.html</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>トレンド追跡とブレイクアウト戦略プレイブック：ルール、ポジション、フェイクブレイク、バックテスト検証｜GugoPro Academy</t>
+          <t>スマホの気まずい手渡しにサヨナラ！180°対面反転UIのデザイン美学・HCI空間心理学と海外旅行会話実践ガイド｜GugoPro 異文化コミュニケーションコラム</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>トレンド追跡とブレイクアウト戦略： 自分の「見解」を検証可能なルールに書き換える。</t>
+          <t>スマホの気まずい手渡しにサヨナラ！180°対面反転UIのデザイン美学・HCI空間心理学と海外旅行会話実践ガイド</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>117</v>
+        <v>206</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -6401,17 +6401,17 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/index.html</t>
+          <t>ja/articles/weight-loss-planner-guide.html</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/index.html</t>
+          <t>https://gugopro.com/ja/articles/weight-loss-planner-guide.html</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>投資教育アカデミー | GugoPro Academy</t>
+          <t>線形減量の幻想からの脱却！Wishnofsky 7700kcal法則の破綻からレジスタンストレーニング期分け・停滞期突破まで：動的減量計画とカロリー赤字完全ガイド｜GugoPro 運動生理学コラム</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>システム化 投資教育と実戦のマトリクス</t>
+          <t>線形減量の幻想からの脱却！Wishnofsky 7700kcal法則の破綻からレジスタンストレーニング期分け・停滞期突破まで：動的減量計画とカロリー赤字完全ガイド</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>68</v>
+        <v>229</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/modern-ziwei-guide.html</t>
+          <t>ja/articles/youtube-english-listening-and-shadowing-guide.html</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/modern-ziwei-guide.html</t>
+          <t>https://gugopro.com/ja/articles/youtube-english-listening-and-shadowing-guide.html</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>宿命論とオカルト的脅迫からの脱却：現代心理学で再構築する紫微斗数——十二宮位、四化の動態からAI意思決定反省モデルへ｜GugoPro 意思決定科学コラム</t>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイングで母語レベルの聴覚神経回路を構築する完全ガイド｜GugoPro 言語科学コラム</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>宿命論とオカルト的脅迫からの脱却：現代心理学で再構築する紫微斗数——十二宮位、四化の動態からAI意思決定反省モデルへ</t>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>2</v>
@@ -6508,12 +6508,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/shadowing-with-ai-tutor.html</t>
+          <t>ja/articles/youtube-listening-connected-speech-guide.html</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/shadowing-with-ai-tutor.html</t>
+          <t>https://gugopro.com/ja/articles/youtube-listening-connected-speech-guide.html</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>「話せない英語」にサヨナラ！シャドーイング、CEFR文脈出力、AIチューターによるスピーキング実践ガイド｜GugoPro 言語科学コラム</t>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイング完全ガイド｜GugoPro 言語科学コラム</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>「話せない英語」にサヨナラ！シャドーイング、CEFR文脈輸出、AIチューターによるスピーキング実践ガイド</t>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>2</v>
@@ -6559,12 +6559,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/tarot-decision-framework.html</t>
+          <t>ja/articles/youtube-sequel-tracker-guide.html</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/tarot-decision-framework.html</t>
+          <t>https://gugopro.com/ja/articles/youtube-sequel-tracker-guide.html</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>迷信的宿命論からの脱却：ユングの「元型」心理学・共時性からAIタロットへ——キャリアの二者択一と関係性不安を解体する構造化意思決定モデル｜GugoPro 意思決定科学コラム</t>
+          <t>2026年YouTube動画推薦アルゴリズムとシリーズ検索完全ガイド：推薦漏れを解消しNLP正規表現ノイズ除去と差分照合で跨チャンネル追跡を実現する｜GugoPro ストリーミング研究コラム</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>迷信的宿命論からの脱却：ユングの「元型」心理学・共時性からAIタロットへ——キャリアの二者択一と関係性不安を解体する構造化意思決定モデル</t>
+          <t>2026年YouTube動画推薦アルゴリズムとシリーズ検索完全ガイド：推薦漏れを解消し NLP正規表現ノイズ除去と差分照合 で跨チャンネル追跡を実現する</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6593,7 +6593,7 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>161</v>
+        <v>224</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>2</v>
@@ -6605,17 +6605,17 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/tblt-with-ai-tutor.html</t>
+          <t>ja/tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/tblt-with-ai-tutor.html</t>
+          <t>https://gugopro.com/ja/tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6625,12 +6625,12 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>丸暗記にサヨナラ！タスク型教授法（TBLT）、Robinson認知仮説とAIチューターによる英会話実践ガイド｜GugoPro 言語科学コラム</t>
+          <t>リダイレクト中 - AI多言語スピーキングチューター | GugoPro</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>丸暗記にサヨナラ！タスク型教授法（TBLT）、Robinson認知仮説とAIチューターによる英会話実践ガイド</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6640,14 +6640,14 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -6656,17 +6656,17 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/tdee-and-macros-guide.html</t>
+          <t>ja/tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/tdee-and-macros-guide.html</t>
+          <t>https://gugopro.com/ja/tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>無駄な食事制限とリバウンドを完全に卒業！熱力学エネルギー収支、適応熱産生からAI食事解析まで：外食派のためのTDEE＆PFCバランス精密調整バイブル｜GugoPro 代謝健康專欄</t>
+          <t>リダイレクト中 - 対面型リアルタイム音声翻訳 | GugoPro</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>無駄な食事制限とリバウンドを完全に卒業！熱力学エネルギー収支、適応熱産生からAI食事解析まで：外食派のためのTDEE＆PFCバランス精密調整バイブル</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6691,14 +6691,14 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -6707,17 +6707,17 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/travel-translator-guide.html</t>
+          <t>ja/tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/travel-translator-guide.html</t>
+          <t>https://gugopro.com/ja/tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>スマホの気まずい手渡しにサヨナラ！180°対面反転UIのデザイン美学・HCI空間心理学と海外旅行会話実践ガイド｜GugoPro 異文化コミュニケーションコラム</t>
+          <t>リダイレクト中 - AIタロットマスター | GugoPro</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>スマホの気まずい手渡しにサヨナラ！180°対面反転UIのデザイン美学・HCI空間心理学と海外旅行会話実践ガイド</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -6742,14 +6742,14 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -6758,17 +6758,17 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/weight-loss-planner-guide.html</t>
+          <t>ja/tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/weight-loss-planner-guide.html</t>
+          <t>https://gugopro.com/ja/tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>線形減量の幻想からの脱却！Wishnofsky 7700kcal法則の破綻からレジスタンストレーニング期分け・停滞期突破まで：動的減量計画とカロリー赤字完全ガイド｜GugoPro 運動生理学コラム</t>
+          <t>リダイレクト中 - AI紫微斗数マスター | GugoPro</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>線形減量の幻想からの脱却！Wishnofsky 7700kcal法則の破綻からレジスタンストレーニング期分け・停滞期突破まで：動的減量計画とカロリー赤字完全ガイド</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -6793,14 +6793,14 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -6809,17 +6809,17 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/youtube-english-listening-and-shadowing-guide.html</t>
+          <t>ja/tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/youtube-english-listening-and-shadowing-guide.html</t>
+          <t>https://gugopro.com/ja/tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイングで母語レベルの聴覚神経回路を構築する完全ガイド｜GugoPro 言語科学コラム</t>
+          <t>リダイレクト中 - YouTube続編追跡 | GugoPro</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6844,14 +6844,14 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -6860,17 +6860,17 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/youtube-listening-connected-speech-guide.html</t>
+          <t>ja/tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/youtube-listening-connected-speech-guide.html</t>
+          <t>https://gugopro.com/ja/tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6880,12 +6880,12 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイング完全ガイド｜GugoPro 言語科学コラム</t>
+          <t>リダイレクト中 - YouTube学習プレイヤー | GugoPro</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -6895,14 +6895,14 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -6911,17 +6911,17 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/youtube-sequel-tracker-guide.html</t>
+          <t>ja/tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/youtube-sequel-tracker-guide.html</t>
+          <t>https://gugopro.com/ja/tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026年YouTube動画推薦アルゴリズムとシリーズ検索完全ガイド：推薦漏れを解消しNLP正規表現ノイズ除去と差分照合で跨チャンネル追跡を実現する｜GugoPro ストリーミング研究コラム</t>
+          <t>リダイレクト中 - AI栄養士 | GugoPro</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>2026年YouTube動画推薦アルゴリズムとシリーズ検索完全ガイド：推薦漏れを解消し NLP正規表現ノイズ除去と差分照合 で跨チャンネル追跡を実現する</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -6946,14 +6946,14 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -6962,17 +6962,17 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>法律條款</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>ja/legal/about.html</t>
+          <t>ja/tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/legal/about.html</t>
+          <t>https://gugopro.com/ja/tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>GugoProについて | GugoPro</t>
+          <t>リダイレクト中 - AI減量コーチ | GugoPro</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>GugoProについて</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -6997,14 +6997,14 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -7018,27 +7018,27 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>ja/legal/contact.html</t>
+          <t>privacy.html</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/legal/contact.html</t>
+          <t>https://gugopro.com/privacy.html</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>お問い合わせ | GugoPro</t>
+          <t>隱私權政策｜GugoPro</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>お問い合わせ</t>
+          <t>隱私權政策</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7069,27 +7069,27 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>ja/legal/disclaimer.html</t>
+          <t>terms.html</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/legal/disclaimer.html</t>
+          <t>https://gugopro.com/terms.html</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>免責事項 | GugoPro</t>
+          <t>服務條款｜GugoPro</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>免責事項</t>
+          <t>服務條款</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7115,32 +7115,32 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>法律條款</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>ja/legal/privacy.html</t>
+          <t>tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/legal/privacy.html</t>
+          <t>https://gugopro.com/tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>プライバシーポリシー | GugoPro</t>
+          <t>AI多國語言對話導師</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>プライバシーポリシー</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7154,10 +7154,10 @@
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>136</v>
+        <v>65</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -7166,32 +7166,32 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>法律條款</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>ja/legal/terms.html</t>
+          <t>tools/ai/gemini-api-quota.html</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/legal/terms.html</t>
+          <t>https://gugopro.com/tools/ai/gemini-api-quota.html</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>利用規約 | GugoPro</t>
+          <t>Gemini API 配額服務導覽｜GugoPro</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>利用規約</t>
+          <t>Gemini API 配額服務導覽</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7205,7 +7205,7 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>0</v>
@@ -7217,27 +7217,27 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/ai/english-speaking-tutor.html</t>
+          <t>tools/ai/nutritionist.html</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/ai/english-speaking-tutor.html</t>
+          <t>https://gugopro.com/tools/ai/nutritionist.html</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - AI多言語スピーキングチューター | GugoPro</t>
+          <t>AI 專屬營養師｜AI 營養諮詢、TDEE 與飲食紀錄工具、免安裝與隱私說明 - GugoPro</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -7252,11 +7252,11 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>1</v>
@@ -7273,27 +7273,27 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/ai/realtime-translator.html</t>
+          <t>tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/ai/realtime-translator.html</t>
+          <t>https://gugopro.com/tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - 対面型リアルタイム音声翻訳 | GugoPro</t>
+          <t>面對面旅遊對話翻譯｜出國旅遊即時翻譯與雙向語音對話｜GugoPro</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>面對面旅遊對話翻譯：出國旅遊即時翻譯與雙向語音對話</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7303,14 +7303,14 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="K134" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="K134" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -7324,22 +7324,22 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/ai/tarot-master.html</t>
+          <t>tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/ai/tarot-master.html</t>
+          <t>https://gugopro.com/tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - AIタロットマスター | GugoPro</t>
+          <t>AI 塔羅大師｜五種塔羅牌陣、提問指南與自我反思 - GugoPro</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -7354,11 +7354,11 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="K135" s="2" t="n">
         <v>1</v>
@@ -7375,27 +7375,27 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/ai/ziwei-astrology.html</t>
+          <t>tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/ai/ziwei-astrology.html</t>
+          <t>https://gugopro.com/tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - AI紫微斗数マスター | GugoPro</t>
+          <t>AI 紫微斗數大師｜紫微斗數線上排盤資料整理與十二宮位指南 - GugoPro</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>把命盤問題，整理成可行動的洞察</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7405,11 +7405,11 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>1</v>
@@ -7426,44 +7426,44 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/ai-media/ai-video-tracker.html</t>
+          <t>tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/ai-media/ai-video-tracker.html</t>
+          <t>https://gugopro.com/tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - YouTube続編追跡 | GugoPro</t>
+          <t>YouTube 續集與新季追蹤器 - GugoPro</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
+          <t>YouTube 續集與新季追蹤器</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>可見</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I137" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
       <c r="J137" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="K137" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="K137" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -7472,32 +7472,32 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/english/l-player-study.html</t>
+          <t>tools/compound-interest.html</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/english/l-player-study.html</t>
+          <t>https://gugopro.com/tools/compound-interest.html</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - YouTube学習プレイヤー | GugoPro</t>
+          <t>Compound Interest 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>進階複利與退休目標規劃計算機</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7507,14 +7507,14 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139">
@@ -7528,41 +7528,41 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/health/tdee-macros-calculator.html</t>
+          <t>tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/health/tdee-macros-calculator.html</t>
+          <t>https://gugopro.com/tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - AI栄養士 | GugoPro</t>
+          <t>【AB English Podcast】Ep.1 自我介紹與日常社交對話 (Mia &amp; Alex)｜L-Player</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>YouTube 影音「聽・寫・口說」多國語言跟讀器</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>可見</t>
+          <t>疑似隱藏</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="K139" s="2" t="n">
         <v>1</v>
@@ -7574,32 +7574,32 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/health/weight-loss-planner.html</t>
+          <t>tools/etf-dividend-calculator.html</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/health/weight-loss-planner.html</t>
+          <t>https://gugopro.com/tools/etf-dividend-calculator.html</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-Hant</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - AI減量コーチ | GugoPro</t>
+          <t>Etf Dividend Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>把配息拆成一條， 看得懂的現金流曲線。</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7609,14 +7609,14 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="K140" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="K140" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -7625,17 +7625,17 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>法律條款</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>privacy.html</t>
+          <t>tools/finance/kelly-criterion-calculator.html</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/privacy.html</t>
+          <t>https://gugopro.com/tools/finance/kelly-criterion-calculator.html</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -7645,12 +7645,12 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>隱私權政策｜GugoPro</t>
+          <t>Kelly Criterion Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>隱私權政策</t>
+          <t>凱利公式與資金控管模擬器</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7664,10 +7664,10 @@
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -7676,17 +7676,17 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>quant/pine-script-basics.html</t>
+          <t>tools/finance/sports-hedging-calculator.html</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/quant/pine-script-basics.html</t>
+          <t>https://gugopro.com/tools/finance/sports-hedging-calculator.html</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Unit 4.2: TradingView Pine Script 程式交易入門 | GugoPro 財經教學學院</t>
+          <t>Sports Hedging Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>TradingView Pine Script 程式交易入門與指標開發</t>
+          <t>運動彩券賠率換算與套利對沖計算器</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -7727,32 +7727,32 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>support.html</t>
+          <t>tools/games/mahjong-waits-calculator.html</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/support.html</t>
+          <t>https://gugopro.com/tools/games/mahjong-waits-calculator.html</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>zh-TW</t>
+          <t>zh-Hant</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>GugoPro｜贊助支持</t>
+          <t>Mahjong Waits Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>支持 GugoPro</t>
+          <t>麻將聽牌張數與進張勝率計算器</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="K143" s="2" t="n">
         <v>0</v>
@@ -7778,17 +7778,17 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>法律條款</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>terms.html</t>
+          <t>tools/games/poker-odds-calculator.html</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/terms.html</t>
+          <t>https://gugopro.com/tools/games/poker-odds-calculator.html</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>服務條款｜GugoPro</t>
+          <t>Poker Odds Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>服務條款</t>
+          <t>德州撲克即時勝率計算器 Texas Hold'em Odds Calculator</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="K144" s="2" t="n">
         <v>0</v>
@@ -7829,32 +7829,32 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>tools/ai/english-speaking-tutor.html</t>
+          <t>tools/gaming/gacha-odds-calculator.html</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/ai/english-speaking-tutor.html</t>
+          <t>https://gugopro.com/tools/gaming/gacha-odds-calculator.html</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>zh-TW</t>
+          <t>zh-Hant</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>AI多國語言對話導師</t>
+          <t>Gacha Odds Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>Gacha Odds &amp; Pity Simulator v5</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7868,10 +7868,10 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>tools/ai/gemini-api-quota.html</t>
+          <t>tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/ai/gemini-api-quota.html</t>
+          <t>https://gugopro.com/tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Gemini API 配額服務導覽｜GugoPro</t>
+          <t>AI 專屬營養師 | GugoPro</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Gemini API 配額服務導覽</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7919,10 +7919,10 @@
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -7931,17 +7931,17 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>歷史工具</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>tools/ai/nutritionist.html</t>
+          <t>tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/ai/nutritionist.html</t>
+          <t>https://gugopro.com/tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>AI 專屬營養師｜AI 營養諮詢、TDEE 與飲食紀錄工具、免安裝與隱私說明 - GugoPro</t>
+          <t>AI減肥瘦身教練｜科學減脂與熱量赤字規劃 | GugoPro</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K147" s="2" t="n">
         <v>1</v>
@@ -7982,17 +7982,17 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>tools/ai/realtime-translator.html</t>
+          <t>tools/pdf/pdf-suite.html</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/ai/realtime-translator.html</t>
+          <t>https://gugopro.com/tools/pdf/pdf-suite.html</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -8002,12 +8002,12 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>面對面旅遊對話翻譯｜出國旅遊即時翻譯與雙向語音對話｜GugoPro</t>
+          <t>PDF 全能工作站｜免安裝線上閱讀、合併、分割與標註、零檔案外洩 - GugoPro</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>面對面旅遊對話翻譯：出國旅遊即時翻譯與雙向語音對話</t>
+          <t>先選擇要處理的文件</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8017,14 +8017,14 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -8033,17 +8033,17 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>tools/ai/tarot-master.html</t>
+          <t>tools/poker/poker-odds-calculator.html</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/ai/tarot-master.html</t>
+          <t>https://gugopro.com/tools/poker/poker-odds-calculator.html</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -8053,12 +8053,12 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>AI 塔羅大師｜五種塔羅牌陣、提問指南與自我反思 - GugoPro</t>
+          <t>Poker Odds Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>德州撲克即時勝率計算器 Texas Hold'em Odds Calculator</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -8084,32 +8084,32 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>tools/ai/ziwei-astrology.html</t>
+          <t>tools/realestate-amortization.html</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/ai/ziwei-astrology.html</t>
+          <t>https://gugopro.com/tools/realestate-amortization.html</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>zh-TW</t>
+          <t>zh-Hant</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>AI 紫微斗數大師｜紫微斗數線上排盤資料整理與十二宮位指南 - GugoPro</t>
+          <t>Realestate Amortization 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>把命盤問題，整理成可行動的洞察</t>
+          <t>房貸本息攤還、利息與提前還款工具</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -8135,32 +8135,32 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>tools/ai-media/ai-video-tracker.html</t>
+          <t>tools/risk-reward-calculator.html</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/ai-media/ai-video-tracker.html</t>
+          <t>https://gugopro.com/tools/risk-reward-calculator.html</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>zh-TW</t>
+          <t>zh-Hant</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>YouTube 續集與新季追蹤器 - GugoPro</t>
+          <t>Risk Reward Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>YouTube 續集與新季追蹤器</t>
+          <t>先看即時價格，再決定風險。</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8170,11 +8170,11 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="K151" s="2" t="n">
         <v>0</v>
@@ -8191,12 +8191,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>tools/compound-interest.html</t>
+          <t>tools/tradingview-guide.html</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/compound-interest.html</t>
+          <t>https://gugopro.com/tools/tradingview-guide.html</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -8206,12 +8206,12 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Compound Interest 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
+          <t>Tradingview Guide 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>進階複利與退休目標規劃計算機</t>
+          <t>全球最強圖表工具 TradingView</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
         <v>62</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>tools/english/l-player-study.html</t>
+          <t>tools/tutorials/how-to-get-gemini-api-key.html</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/english/l-player-study.html</t>
+          <t>https://gugopro.com/tools/tutorials/how-to-get-gemini-api-key.html</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8257,17 +8257,17 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>【AB English Podcast】Ep.1 自我介紹與日常社交對話 (Mia &amp; Alex)｜L-Player</t>
+          <t>Gemini API Key 申請教學｜Google Gemini API Key 取得與安全設定教學、免安裝與隱私說明 - GugoPro</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>YouTube 影音「聽・寫・口說」多國語言跟讀器</t>
+          <t>Google Gemini API Key 1 分鐘快速申請步驟</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>疑似隱藏</t>
+          <t>可見</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="K153" s="2" t="n">
         <v>1</v>
@@ -8293,27 +8293,27 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>tools/etf-dividend-calculator.html</t>
+          <t>tools/tw-market/taiwan-pair-trading.html</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/etf-dividend-calculator.html</t>
+          <t>https://gugopro.com/tools/tw-market/taiwan-pair-trading.html</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>zh-Hant</t>
+          <t>zh-Hant-TW</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Etf Dividend Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
+          <t>Taiwan Pair Trading 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>把配息拆成一條， 看得懂的現金流曲線。</t>
+          <t>台灣股票與期貨 配對交易掃描工作站</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8327,728 +8327,14 @@
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="K154" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="n">
-        <v>154</v>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>tools/finance/kelly-criterion-calculator.html</t>
-        </is>
-      </c>
-      <c r="D155" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/finance/kelly-criterion-calculator.html</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>Kelly Criterion Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>凱利公式與資金控管模擬器</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I155" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J155" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="K155" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="n">
-        <v>155</v>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>tools/finance/sports-hedging-calculator.html</t>
-        </is>
-      </c>
-      <c r="D156" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/finance/sports-hedging-calculator.html</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>Sports Hedging Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>運動彩券賠率換算與套利對沖計算器</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I156" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J156" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="K156" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="n">
-        <v>156</v>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>tools/games/mahjong-waits-calculator.html</t>
-        </is>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/games/mahjong-waits-calculator.html</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr">
-        <is>
-          <t>zh-Hant</t>
-        </is>
-      </c>
-      <c r="F157" s="2" t="inlineStr">
-        <is>
-          <t>Mahjong Waits Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t>麻將聽牌張數與進張勝率計算器</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J157" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="K157" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>tools/games/poker-odds-calculator.html</t>
-        </is>
-      </c>
-      <c r="D158" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/games/poker-odds-calculator.html</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>Poker Odds Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>德州撲克即時勝率計算器 Texas Hold'em Odds Calculator</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I158" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J158" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="K158" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="n">
-        <v>158</v>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>tools/gaming/gacha-odds-calculator.html</t>
-        </is>
-      </c>
-      <c r="D159" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/gaming/gacha-odds-calculator.html</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t>zh-Hant</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>Gacha Odds Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>Gacha Odds &amp; Pity Simulator v5</t>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J159" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="K159" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="n">
-        <v>159</v>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>tools/health/tdee-macros-calculator.html</t>
-        </is>
-      </c>
-      <c r="D160" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/health/tdee-macros-calculator.html</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>AI 專屬營養師 | GugoPro</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I160" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J160" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="K160" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="n">
-        <v>160</v>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>tools/health/weight-loss-planner.html</t>
-        </is>
-      </c>
-      <c r="D161" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/health/weight-loss-planner.html</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F161" s="2" t="inlineStr">
-        <is>
-          <t>AI減肥瘦身教練｜科學減脂與熱量赤字規劃 | GugoPro</t>
-        </is>
-      </c>
-      <c r="G161" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I161" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J161" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="K161" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="n">
-        <v>161</v>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>tools/pdf/pdf-suite.html</t>
-        </is>
-      </c>
-      <c r="D162" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/pdf/pdf-suite.html</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t>PDF 全能工作站｜免安裝線上閱讀、合併、分割與標註、零檔案外洩 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t>先選擇要處理的文件</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I162" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="J162" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="K162" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="n">
-        <v>162</v>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>tools/poker/poker-odds-calculator.html</t>
-        </is>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/poker/poker-odds-calculator.html</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t>Poker Odds Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>德州撲克即時勝率計算器 Texas Hold'em Odds Calculator</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J163" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="K163" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="n">
-        <v>163</v>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>tools/realestate-amortization.html</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/realestate-amortization.html</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>zh-Hant</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>Realestate Amortization 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>房貸本息攤還、利息與提前還款工具</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J164" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="K164" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="n">
-        <v>164</v>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>tools/risk-reward-calculator.html</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/risk-reward-calculator.html</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>zh-Hant</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>Risk Reward Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>先看即時價格，再決定風險。</t>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="K165" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="n">
-        <v>165</v>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>tools/tradingview-guide.html</t>
-        </is>
-      </c>
-      <c r="D166" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/tradingview-guide.html</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>Tradingview Guide 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>全球最強圖表工具 TradingView</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J166" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="K166" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="n">
-        <v>166</v>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>tools/tutorials/how-to-get-gemini-api-key.html</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/tutorials/how-to-get-gemini-api-key.html</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>Gemini API Key 申請教學｜Google Gemini API Key 取得與安全設定教學、免安裝與隱私說明 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t>Google Gemini API Key 1 分鐘快速申請步驟</t>
-        </is>
-      </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J167" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="K167" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="n">
-        <v>167</v>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>tools/tw-market/taiwan-pair-trading.html</t>
-        </is>
-      </c>
-      <c r="D168" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/tw-market/taiwan-pair-trading.html</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>zh-Hant-TW</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>Taiwan Pair Trading 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t>台灣股票與期貨 配對交易掃描工作站</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J168" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="K168" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K168"/>
+  <autoFilter ref="A1:K154"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -9203,24 +8489,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId151"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId167"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId168"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId154"/>
   </tableParts>
 </worksheet>
 </file>
@@ -9257,7 +8529,7 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>167</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3">
@@ -9307,7 +8579,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -9317,7 +8589,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -9357,7 +8629,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/seo_inventory_report.xlsx
+++ b/seo_inventory_report.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SEO AdSense 盤點'!$A$1:$K$154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SEO AdSense 盤點'!$A$1:$K$137</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -157,8 +157,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SEOInventory" displayName="SEOInventory" ref="A1:K154" headerRowCount="1">
-  <autoFilter ref="A1:K154"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SEOInventory" displayName="SEOInventory" ref="A1:K137" headerRowCount="1">
+  <autoFilter ref="A1:K137"/>
   <tableColumns count="11">
     <tableColumn id="1" name="編號"/>
     <tableColumn id="2" name="頁面分類"/>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K154"/>
+  <dimension ref="A1:K137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -646,17 +646,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>amazon/index.html</t>
+          <t>articles/affective-filter-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/amazon/index.html</t>
+          <t>https://gugopro.com/articles/affective-filter-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Amazon AI 全品類智能選品導購 | GugoPro</t>
+          <t>克服開口恐懼的心理學解方：克拉申「情意濾網假說」、外語焦慮（FLA）與 AI 導師的零壓力口說閉環｜GugoPro 語言學習專欄</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>🛒 Amazon AI 智能購物導師</t>
+          <t>克服開口恐懼的心理學解方：克拉申「情意濾網假說」、外語焦慮（FLA）與 AI 導師的零壓力口說閉環</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -697,17 +697,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>amazon-jp/index.html</t>
+          <t>articles/amazon-ai-product-research-guide.html</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/amazon-jp/index.html</t>
+          <t>https://gugopro.com/articles/amazon-ai-product-research-guide.html</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -717,12 +717,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Amazon AI 智能購物導師 | GugoPro 多模態尋寶助手</t>
+          <t>2026 跨境電商與高階海淘全指南：如何利用 AI 語意反向工程打造 Amazon 爆款選品、競品差評痛點挖掘與 Listing 關鍵字佈局矩陣｜GugoPro 電商戰略專欄</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>🛒 Amazon AI 智能購物導師</t>
+          <t>2026 跨境電商與高階海淘全指南：如何利用 AI 語意反向工程打造 Amazon 爆款選品、競品差評痛點挖掘與 Listing 關鍵字佈局矩陣</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>89</v>
+        <v>210</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>1</v>
@@ -748,17 +748,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>amazon-us/index.html</t>
+          <t>articles/carb-cycling-and-home-workout-guide.html</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/amazon-us/index.html</t>
+          <t>https://gugopro.com/articles/carb-cycling-and-home-workout-guide.html</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Amazon AI 全品類智能選品導購 | GugoPro</t>
+          <t>碳水循環法（Carb Cycling）怎麼吃最減脂？高低碳日生化機制、居家無器材燃脂課表與防止掉肌肉全攻略｜GugoPro 減脂運動生理學專欄</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>🛒 Amazon AI 智能購物導師</t>
+          <t>碳水循環法（Carb Cycling）怎麼吃最減脂？高低碳日生化機制、居家無器材燃脂課表與防止掉肌肉全攻略</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -787,10 +787,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>76</v>
+        <v>207</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -804,12 +804,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>articles/affective-filter-with-ai-tutor.html</t>
+          <t>articles/diabetes-and-insulin-resistance-guide.html</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/affective-filter-with-ai-tutor.html</t>
+          <t>https://gugopro.com/articles/diabetes-and-insulin-resistance-guide.html</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>克服開口恐懼的心理學解方：克拉申「情意濾網假說」、外語焦慮（FLA）與 AI 導師的零壓力口說閉環｜GugoPro 語言學習專欄</t>
+          <t>糖尿病前期與胰島素阻抗怎麼吃？從升糖指數（GI/GL）、碳水計數到 AI 拍餐：告別血糖震盪的巨量營養素調控全指南｜GugoPro 慢病代謝專欄</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>克服開口恐懼的心理學解方：克拉申「情意濾網假說」、外語焦慮（FLA）與 AI 導師的零壓力口說閉環</t>
+          <t>糖尿病前期與胰島素阻抗怎麼吃？從升糖指數（GI/GL）、碳水計數到 AI 拍餐：告別血糖震盪的巨量營養素調控全指南</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>2</v>
@@ -855,12 +855,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>articles/amazon-ai-product-research-guide.html</t>
+          <t>articles/english-intro-break-the-ice.html</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/amazon-ai-product-research-guide.html</t>
+          <t>https://gugopro.com/articles/english-intro-break-the-ice.html</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026 跨境電商與高階海淘全指南：如何利用 AI 語意反向工程打造 Amazon 爆款選品、競品差評痛點挖掘與 Listing 關鍵字佈局矩陣｜GugoPro 電商戰略專欄</t>
+          <t>看 YouTube 學英文為何總是無效？結合音韻知覺理論、Levenshtein 聽寫差量比對與影子跟讀（Shadowing）打造母語聽覺神經迴路全指南｜GugoPro 語言科學專欄</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026 跨境電商與高階海淘全指南：如何利用 AI 語意反向工程打造 Amazon 爆款選品、競品差評痛點挖掘與 Listing 關鍵字佈局矩陣</t>
+          <t>看 YouTube 學英文為何總是無效？結合音韻知覺理論、 Levenshtein 聽寫差量比對與影子跟讀（Shadowing） 打造母語聽覺神經迴路全指南</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -906,12 +906,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>articles/carb-cycling-and-home-workout-guide.html</t>
+          <t>articles/fatty-liver-and-mediterranean-diet-guide.html</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/carb-cycling-and-home-workout-guide.html</t>
+          <t>https://gugopro.com/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>碳水循環法（Carb Cycling）怎麼吃最減脂？高低碳日生化機制、居家無器材燃脂課表與防止掉肌肉全攻略｜GugoPro 減脂運動生理學專欄</t>
+          <t>減醣飲食與地中海飲食怎麼吃？從逆轉脂肪肝、內臟脂肪燃燒到三大營養素黃金配比：外食族健康長壽實戰手冊｜GugoPro 肝臟代謝專欄</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>碳水循環法（Carb Cycling）怎麼吃最減脂？高低碳日生化機制、居家無器材燃脂課表與防止掉肌肉全攻略</t>
+          <t>減醣飲食與地中海飲食怎麼吃？從逆轉脂肪肝、內臟脂肪燃燒到三大營養素黃金配比：外食族健康長壽實戰手冊</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>articles/diabetes-and-insulin-resistance-guide.html</t>
+          <t>articles/gemini-api-free-tier-and-developer-guide.html</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/diabetes-and-insulin-resistance-guide.html</t>
+          <t>https://gugopro.com/articles/gemini-api-free-tier-and-developer-guide.html</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>糖尿病前期與胰島素阻抗怎麼吃？從升糖指數（GI/GL）、碳水計數到 AI 拍餐：告別血糖震盪的巨量營養素調控全指南｜GugoPro 慢病代謝專欄</t>
+          <t>2026 終極開發者手冊：利用 Google Gemini 官方免費 API 打造零成本商用級應用之架構設計與故障排除全指南｜GugoPro 雲端系統專欄</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>糖尿病前期與胰島素阻抗怎麼吃？從升糖指數（GI/GL）、碳水計數到 AI 拍餐：告別血糖震盪的巨量營養素調控全指南</t>
+          <t>2026 終極開發者手冊：利用 Google Gemini 官方免費 API 打造零成本商用級應用之架構設計與故障排除全指南</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>194</v>
+        <v>260</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>2</v>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>articles/english-intro-break-the-ice.html</t>
+          <t>articles/how-to-master-tarot-guide.html</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/english-intro-break-the-ice.html</t>
+          <t>https://gugopro.com/articles/how-to-master-tarot-guide.html</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>看 YouTube 學英文為何總是無效？結合音韻知覺理論、Levenshtein 聽寫差量比對與影子跟讀（Shadowing）打造母語聽覺神經迴路全指南｜GugoPro 語言科學專欄</t>
+          <t>如何成為塔羅牌大師？從 78 張牌義生吞活剝到「直覺流動解牌」：結合古典符號學、敘事心理學與 AI 協同實戰刻意練習全指南｜GugoPro 決策科學專欄</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>看 YouTube 學英文為何總是無效？結合音韻知覺理論、 Levenshtein 聽寫差量比對與影子跟讀（Shadowing） 打造母語聽覺神經迴路全指南</t>
+          <t>如何成為塔羅牌大師？從 78 張牌義生吞活剝到「直覺流動解牌」：結合古典符號學、敘事心理學與 AI 協同實戰刻意練習全指南</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>224</v>
+        <v>159</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>2</v>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>articles/fatty-liver-and-mediterranean-diet-guide.html</t>
+          <t>articles/how-to-master-ziwei-guide.html</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
+          <t>https://gugopro.com/articles/how-to-master-ziwei-guide.html</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>減醣飲食與地中海飲食怎麼吃？從逆轉脂肪肝、內臟脂肪燃燒到三大營養素黃金配比：外食族健康長壽實戰手冊｜GugoPro 肝臟代謝專欄</t>
+          <t>如何成為紫微斗數大師？從死背百顆星曜到「動態格局解盤」：結合文化符號學、系統動力學與 AI 協同實戰刻意練習全指南｜GugoPro 決策科學專欄</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>減醣飲食與地中海飲食怎麼吃？從逆轉脂肪肝、內臟脂肪燃燒到三大營養素黃金配比：外食族健康長壽實戰手冊</t>
+          <t>如何成為紫微斗數大師？從死背百顆星曜到「動態格局解盤」：結合文化符號學、系統動力學與 AI 協同實戰刻意練習全指南</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>articles/gemini-api-free-tier-and-developer-guide.html</t>
+          <t>articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/gemini-api-free-tier-and-developer-guide.html</t>
+          <t>https://gugopro.com/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026 終極開發者手冊：利用 Google Gemini 官方免費 API 打造零成本商用級應用之架構設計與故障排除全指南｜GugoPro 雲端系統專欄</t>
+          <t>168 斷食真的比算熱量有效嗎？從自噬反應、胰島素假說到熱量赤字真相：打破越斷越肥的復胖陷阱｜GugoPro 減脂代謝專欄</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2026 終極開發者手冊：利用 Google Gemini 官方免費 API 打造零成本商用級應用之架構設計與故障排除全指南</t>
+          <t>168 斷食真的比算熱量有效嗎？從自噬反應、胰島素假說到熱量赤字真相：打破越斷越肥的復胖陷阱</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>2</v>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>articles/how-to-master-tarot-guide.html</t>
+          <t>articles/modern-ziwei-guide.html</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/how-to-master-tarot-guide.html</t>
+          <t>https://gugopro.com/articles/modern-ziwei-guide.html</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>如何成為塔羅牌大師？從 78 張牌義生吞活剝到「直覺流動解牌」：結合古典符號學、敘事心理學與 AI 協同實戰刻意練習全指南｜GugoPro 決策科學專欄</t>
+          <t>告別宿命論與玄學恐嚇！用現代心理學重構紫微斗數：從十二宮位、四化動態到 AI 決策反思模型｜GugoPro 決策科學專欄</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>如何成為塔羅牌大師？從 78 張牌義生吞活剝到「直覺流動解牌」：結合古典符號學、敘事心理學與 AI 協同實戰刻意練習全指南</t>
+          <t>告別宿命論與玄學恐嚇！用現代心理學重構紫微斗數：從十二宮位、四化動態到 AI 決策反思模型</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>2</v>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>articles/how-to-master-ziwei-guide.html</t>
+          <t>articles/shadowing-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/how-to-master-ziwei-guide.html</t>
+          <t>https://gugopro.com/articles/shadowing-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>如何成為紫微斗數大師？從死背百顆星曜到「動態格局解盤」：結合文化符號學、系統動力學與 AI 協同實戰刻意練習全指南｜GugoPro 決策科學專欄</t>
+          <t>擺脫「啞巴英語」的科學自學法：結合影子跟讀（Shadowing）、CEFR 脈絡輸出與 AI 導師的高效閉環｜GugoPro 語言學習專欄</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>如何成為紫微斗數大師？從死背百顆星曜到「動態格局解盤」：結合文化符號學、系統動力學與 AI 協同實戰刻意練習全指南</t>
+          <t>擺脫「啞巴英語」的科學自學法：結合影子跟讀（Shadowing）、CEFR 脈絡輸出與 AI 導師的高效閉環</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>207</v>
+        <v>141</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>2</v>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
+          <t>articles/tarot-decision-framework.html</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
+          <t>https://gugopro.com/articles/tarot-decision-framework.html</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>168 斷食真的比算熱量有效嗎？從自噬反應、胰島素假說到熱量赤字真相：打破越斷越肥的復胖陷阱｜GugoPro 減脂代謝專欄</t>
+          <t>告別迷信宿命論！從榮格「原型」心理學、共時性到 AI 塔羅：拆解職涯二選一與感情焦慮的結構化決策模型｜GugoPro 決策科學專欄</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>168 斷食真的比算熱量有效嗎？從自噬反應、胰島素假說到熱量赤字真相：打破越斷越肥的復胖陷阱</t>
+          <t>告別迷信宿命論！從榮格「原型」心理學、共時性到 AI 塔羅：拆解職涯二選一與感情焦慮的結構化決策模型</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>265</v>
+        <v>143</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>2</v>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>articles/modern-ziwei-guide.html</t>
+          <t>articles/tblt-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/modern-ziwei-guide.html</t>
+          <t>https://gugopro.com/articles/tblt-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>告別宿命論與玄學恐嚇！用現代心理學重構紫微斗數：從十二宮位、四化動態到 AI 決策反思模型｜GugoPro 決策科學專欄</t>
+          <t>告別死記硬背！結合任務型教學法（TBLT）、Robinson 認知假說與 AI 導師的高效口說實戰指南｜GugoPro 語言學習專欄</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>告別宿命論與玄學恐嚇！用現代心理學重構紫微斗數：從十二宮位、四化動態到 AI 決策反思模型</t>
+          <t>告別死記硬背！結合任務型教學法（TBLT）、Robinson 認知假說與 AI 導師的高效口說實戰指南</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>2</v>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>articles/shadowing-with-ai-tutor.html</t>
+          <t>articles/tdee-and-macros-guide.html</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/shadowing-with-ai-tutor.html</t>
+          <t>https://gugopro.com/articles/tdee-and-macros-guide.html</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>擺脫「啞巴英語」的科學自學法：結合影子跟讀（Shadowing）、CEFR 脈絡輸出與 AI 導師的高效閉環｜GugoPro 語言學習專欄</t>
+          <t>告別無效節食與溜溜球效應！從能量平衡熱力學、自適應產熱到 AI 拍餐估算：外食族 TDEE 與三大營養素精準調控全指南｜GugoPro 代謝健康專欄</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>擺脫「啞巴英語」的科學自學法：結合影子跟讀（Shadowing）、CEFR 脈絡輸出與 AI 導師的高效閉環</t>
+          <t>告別無效節食與溜溜球效應！從能量平衡熱力學、自適應產熱到 AI 拍餐估算：外食族 TDEE 與三大營養素精準調控全指南</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>2</v>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>articles/tarot-decision-framework.html</t>
+          <t>articles/travel-translator-guide.html</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/tarot-decision-framework.html</t>
+          <t>https://gugopro.com/articles/travel-translator-guide.html</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>告別迷信宿命論！從榮格「原型」心理學、共時性到 AI 塔羅：拆解職涯二選一與感情焦慮的結構化決策模型｜GugoPro 決策科學專欄</t>
+          <t>告別尷尬遞手機！180° 面對面翻轉介面的設計美學、人機互動（HCI）空間心理學與出國溝通實戰指南｜GugoPro 跨文化專欄</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>告別迷信宿命論！從榮格「原型」心理學、共時性到 AI 塔羅：拆解職涯二選一與感情焦慮的結構化決策模型</t>
+          <t>告別尷尬遞手機！180° 面對面翻轉介面的設計美學、人機互動（HCI）空間心理學與出國溝通實戰指南</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>143</v>
+        <v>184</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>2</v>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>articles/tblt-with-ai-tutor.html</t>
+          <t>articles/weight-loss-planner-guide.html</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/tblt-with-ai-tutor.html</t>
+          <t>https://gugopro.com/articles/weight-loss-planner-guide.html</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>告別死記硬背！結合任務型教學法（TBLT）、Robinson 認知假說與 AI 導師的高效口說實戰指南｜GugoPro 語言學習專欄</t>
+          <t>告別線性減重迷思！從 Wishnofsky 7700大卡法則失真、阻力訓練期程化到停滯期突破：動態減脂計畫與熱量赤字全指南｜GugoPro 運動生理學專欄</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>告別死記硬背！結合任務型教學法（TBLT）、Robinson 認知假說與 AI 導師的高效口說實戰指南</t>
+          <t>告別線性減重迷思！從 Wishnofsky 7700大卡法則失真、阻力訓練期程化到停滯期突破：動態減脂計畫與熱量赤字全指南</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>2</v>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>articles/tdee-and-macros-guide.html</t>
+          <t>articles/youtube-english-listening-and-shadowing-guide.html</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/tdee-and-macros-guide.html</t>
+          <t>https://gugopro.com/articles/youtube-english-listening-and-shadowing-guide.html</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>告別無效節食與溜溜球效應！從能量平衡熱力學、自適應產熱到 AI 拍餐估算：外食族 TDEE 與三大營養素精準調控全指南｜GugoPro 代謝健康專欄</t>
+          <t>解鎖 YouTube 雙語精聽與影子跟讀：L-Player 零摩擦學習系統操作全書與神經聽覺重塑指南｜GugoPro 語言科學專欄</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>告別無效節食與溜溜球效應！從能量平衡熱力學、自適應產熱到 AI 拍餐估算：外食族 TDEE 與三大營養素精準調控全指南</t>
+          <t>解鎖 YouTube 雙語精聽與影子跟讀： L-Player 零摩擦學習系統操作全書與神經聽覺重塑指南</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>189</v>
+        <v>244</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>2</v>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>articles/travel-translator-guide.html</t>
+          <t>articles/youtube-listening-connected-speech-guide.html</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/travel-translator-guide.html</t>
+          <t>https://gugopro.com/articles/youtube-listening-connected-speech-guide.html</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>告別尷尬遞手機！180° 面對面翻轉介面的設計美學、人機互動（HCI）空間心理學與出國溝通實戰指南｜GugoPro 跨文化專欄</t>
+          <t>看 YouTube 學英文為何總是無效？結合音韻知覺理論、Levenshtein 聽寫差量比對與影子跟讀（Shadowing）打造母語聽覺神經迴路全指南｜GugoPro 語言科學專欄</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>告別尷尬遞手機！180° 面對面翻轉介面的設計美學、人機互動（HCI）空間心理學與出國溝通實戰指南</t>
+          <t>看 YouTube 學英文為何總是無效？結合音韻知覺理論、 Levenshtein 聽寫差量比對與影子跟讀（Shadowing） 打造母語聽覺神經迴路全指南</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>184</v>
+        <v>224</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>2</v>
@@ -1620,12 +1620,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>articles/weight-loss-planner-guide.html</t>
+          <t>articles/youtube-sequel-tracker-guide.html</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/weight-loss-planner-guide.html</t>
+          <t>https://gugopro.com/articles/youtube-sequel-tracker-guide.html</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1635,12 +1635,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>告別線性減重迷思！從 Wishnofsky 7700大卡法則失真、阻力訓練期程化到停滯期突破：動態減脂計畫與熱量赤字全指南｜GugoPro 運動生理學專欄</t>
+          <t>2026 YouTube 影音演算法與連載檢索全指南：如何破解推薦漏片迷思、利用 NLP 正則去噪與差量比對打造跨頻道追劇閉環｜GugoPro 串流媒體研究專欄</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>告別線性減重迷思！從 Wishnofsky 7700大卡法則失真、阻力訓練期程化到停滯期突破：動態減脂計畫與熱量赤字全指南</t>
+          <t>2026 YouTube 影音演算法與連載檢索全指南：如何破解推薦漏片迷思、利用 NLP 正則去噪與差量比對 打造跨頻道追劇閉環</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>2</v>
@@ -1666,17 +1666,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>法律條款</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>articles/youtube-english-listening-and-shadowing-guide.html</t>
+          <t>contact.html</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/youtube-english-listening-and-shadowing-guide.html</t>
+          <t>https://gugopro.com/contact.html</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>解鎖 YouTube 雙語精聽與影子跟讀：L-Player 零摩擦學習系統操作全書與神經聽覺重塑指南｜GugoPro 語言科學專欄</t>
+          <t>聯絡我們 | GugoPro 官方</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>解鎖 YouTube 雙語精聽與影子跟讀： L-Player 零摩擦學習系統操作全書與神經聽覺重塑指南</t>
+          <t>聯絡我們</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>244</v>
+        <v>62</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1717,17 +1717,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>法律條款</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>articles/youtube-listening-connected-speech-guide.html</t>
+          <t>disclaimer.html</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/youtube-listening-connected-speech-guide.html</t>
+          <t>https://gugopro.com/disclaimer.html</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>看 YouTube 學英文為何總是無效？結合音韻知覺理論、Levenshtein 聽寫差量比對與影子跟讀（Shadowing）打造母語聽覺神經迴路全指南｜GugoPro 語言科學專欄</t>
+          <t>免責聲明｜GugoPro 工具與 AI 服務使用限制</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>看 YouTube 學英文為何總是無效？結合音韻知覺理論、 Levenshtein 聽寫差量比對與影子跟讀（Shadowing） 打造母語聽覺神經迴路全指南</t>
+          <t>GugoPro 免責聲明</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>224</v>
+        <v>57</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1773,27 +1773,27 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>articles/youtube-sequel-tracker-guide.html</t>
+          <t>en/articles/affective-filter-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/youtube-sequel-tracker-guide.html</t>
+          <t>https://gugopro.com/en/articles/affective-filter-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>zh-TW</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026 YouTube 影音演算法與連載檢索全指南：如何破解推薦漏片迷思、利用 NLP 正則去噪與差量比對打造跨頻道追劇閉環｜GugoPro 串流媒體研究專欄</t>
+          <t>Overcoming the Fear of Speaking: Krashen's Affective Filter, Foreign Language Anxiety (FLA), and Zero-Pressure AI Tutoring | GugoPro Language Science</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2026 YouTube 影音演算法與連載檢索全指南：如何破解推薦漏片迷思、利用 NLP 正則去噪與差量比對 打造跨頻道追劇閉環</t>
+          <t>Overcoming the Fear of Speaking: Krashen's Affective Filter, Foreign Language Anxiety (FLA), and Zero-Pressure AI Tutoring</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>199</v>
+        <v>455</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>2</v>
@@ -1819,32 +1819,32 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>法律條款</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>contact.html</t>
+          <t>en/articles/amazon-ai-product-research-guide.html</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/contact.html</t>
+          <t>https://gugopro.com/en/articles/amazon-ai-product-research-guide.html</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>zh-TW</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>聯絡我們 | GugoPro 官方</t>
+          <t>2026 Cross-Border E-Commerce &amp; Global Sourcing Master Guide: Leveraging AI Semantic Reverse Engineering for Amazon Product Research, Negative Review Mining, and Listing Matrix Architecture | GugoPro Strategy Column</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>聯絡我們</t>
+          <t>2026 Cross-Border E-Commerce &amp; Global Sourcing Master Guide: Leveraging AI Semantic Reverse Engineering for Amazon Product Research, Negative Review Mining, and Listing Keyword Matrix Architecture</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1858,10 +1858,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>62</v>
+        <v>452</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1870,32 +1870,32 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>法律條款</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>disclaimer.html</t>
+          <t>en/articles/carb-cycling-and-home-workout-guide.html</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/disclaimer.html</t>
+          <t>https://gugopro.com/en/articles/carb-cycling-and-home-workout-guide.html</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>zh-TW</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>免責聲明｜GugoPro 工具與 AI 服務使用限制</t>
+          <t>How to Master Carb Cycling for Maximum Fat Loss: High/Low Carb Biochemistry, Home Bodyweight Workout Splits, and Preserving Muscle Mass | GugoPro Exercise Physiology Column</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>GugoPro 免責聲明</t>
+          <t>How to Master Carb Cycling for Maximum Fat Loss: High/Low Carb Biochemistry, Home Bodyweight Workout Splits, and Preserving Muscle Mass</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>57</v>
+        <v>452</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>en/articles/affective-filter-with-ai-tutor.html</t>
+          <t>en/articles/diabetes-and-insulin-resistance-guide.html</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/affective-filter-with-ai-tutor.html</t>
+          <t>https://gugopro.com/en/articles/diabetes-and-insulin-resistance-guide.html</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Fear of Speaking: Krashen's Affective Filter, Foreign Language Anxiety (FLA), and Zero-Pressure AI Tutoring | GugoPro Language Science</t>
+          <t>What to Eat for Prediabetes and Insulin Resistance? From GI/GL and Carb Counting to AI Meal Tracking: The Definitive Macronutrient Guide to Ending Glucose Spikes | GugoPro Metabolic Science Column</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Fear of Speaking: Krashen's Affective Filter, Foreign Language Anxiety (FLA), and Zero-Pressure AI Tutoring</t>
+          <t>What to Eat for Prediabetes and Insulin Resistance? From GI/GL and Carb Counting to AI Meal Tracking: The Definitive Macronutrient Guide to Ending Glucose Spikes</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>2</v>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>en/articles/amazon-ai-product-research-guide.html</t>
+          <t>en/articles/english-intro-break-the-ice.html</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/amazon-ai-product-research-guide.html</t>
+          <t>https://gugopro.com/en/articles/english-intro-break-the-ice.html</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026 Cross-Border E-Commerce &amp; Global Sourcing Master Guide: Leveraging AI Semantic Reverse Engineering for Amazon Product Research, Negative Review Mining, and Listing Matrix Architecture | GugoPro Strategy Column</t>
+          <t>Why Watching YouTube Fails for English Learning: Speech Perception, Levenshtein Dictation Diff, and Shadowing Guide | GugoPro Language Science</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026 Cross-Border E-Commerce &amp; Global Sourcing Master Guide: Leveraging AI Semantic Reverse Engineering for Amazon Product Research, Negative Review Mining, and Listing Keyword Matrix Architecture</t>
+          <t>Why Watching YouTube Fails for English Learning: Building Native Auditory Circuits via Speech Perception, Levenshtein Dictation Diff, and Shadowing</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>452</v>
+        <v>413</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2028,12 +2028,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>en/articles/carb-cycling-and-home-workout-guide.html</t>
+          <t>en/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/carb-cycling-and-home-workout-guide.html</t>
+          <t>https://gugopro.com/en/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>How to Master Carb Cycling for Maximum Fat Loss: High/Low Carb Biochemistry, Home Bodyweight Workout Splits, and Preserving Muscle Mass | GugoPro Exercise Physiology Column</t>
+          <t>What to Eat for Fatty Liver: Low-Carb vs. Mediterranean Diet? From Reversing Hepatic Steatosis &amp; Visceral Fat to Optimal Macronutrient Ratios: The Dining-Out Longevity Handbook | GugoPro Liver Metabolism Column</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>How to Master Carb Cycling for Maximum Fat Loss: High/Low Carb Biochemistry, Home Bodyweight Workout Splits, and Preserving Muscle Mass</t>
+          <t>What to Eat for Fatty Liver: Low-Carb vs. Mediterranean Diet? From Reversing Hepatic Steatosis &amp; Visceral Fat to Optimal Macronutrient Ratios: The Dining-Out Longevity Handbook</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>2</v>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>en/articles/diabetes-and-insulin-resistance-guide.html</t>
+          <t>en/articles/gemini-api-free-tier-and-developer-guide.html</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/diabetes-and-insulin-resistance-guide.html</t>
+          <t>https://gugopro.com/en/articles/gemini-api-free-tier-and-developer-guide.html</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2094,12 +2094,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>What to Eat for Prediabetes and Insulin Resistance? From GI/GL and Carb Counting to AI Meal Tracking: The Definitive Macronutrient Guide to Ending Glucose Spikes | GugoPro Metabolic Science Column</t>
+          <t>2026 Developer Blueprint: Building Zero-Cost Commercial-Grade Apps with Google Gemini Free API &amp; Comprehensive Error Troubleshooting Guide | GugoPro Cloud Systems Column</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>What to Eat for Prediabetes and Insulin Resistance? From GI/GL and Carb Counting to AI Meal Tracking: The Definitive Macronutrient Guide to Ending Glucose Spikes</t>
+          <t>2026 Developer Blueprint: Building Zero-Cost Commercial-Grade Apps with Google Gemini Free API &amp; Comprehensive Error Troubleshooting Guide</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>437</v>
+        <v>394</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>2</v>
@@ -2130,12 +2130,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>en/articles/english-intro-break-the-ice.html</t>
+          <t>en/articles/how-to-master-tarot-guide.html</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/english-intro-break-the-ice.html</t>
+          <t>https://gugopro.com/en/articles/how-to-master-tarot-guide.html</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Why Watching YouTube Fails for English Learning: Speech Perception, Levenshtein Dictation Diff, and Shadowing Guide | GugoPro Language Science</t>
+          <t>How to Become a Tarot Master? From Rote Memorization to Intuitive Flow Reading: A Deliberate Practice Guide Combining Classical Semiotics, Narrative Psychology, and AI Collaboration | GugoPro Decision Science Column</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Why Watching YouTube Fails for English Learning: Building Native Auditory Circuits via Speech Perception, Levenshtein Dictation Diff, and Shadowing</t>
+          <t>How to Become a Tarot Master? From Rote Memorization to "Intuitive Flow Reading": A Comprehensive Deliberate Practice Guide Combining Classical Semiotics, Narrative Psychology, and AI Collaboration</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>413</v>
+        <v>384</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>2</v>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>en/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
+          <t>en/articles/how-to-master-ziwei-guide.html</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
+          <t>https://gugopro.com/en/articles/how-to-master-ziwei-guide.html</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2196,12 +2196,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>What to Eat for Fatty Liver: Low-Carb vs. Mediterranean Diet? From Reversing Hepatic Steatosis &amp; Visceral Fat to Optimal Macronutrient Ratios: The Dining-Out Longevity Handbook | GugoPro Liver Metabolism Column</t>
+          <t>How to Become a Ziwei Astrology Master? From Rote Memorization to Dynamic Pattern Reading: A Deliberate Practice Guide Combining Cultural Semiotics, System Dynamics, and AI Collaboration | GugoPro Decision Science Column</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>What to Eat for Fatty Liver: Low-Carb vs. Mediterranean Diet? From Reversing Hepatic Steatosis &amp; Visceral Fat to Optimal Macronutrient Ratios: The Dining-Out Longevity Handbook</t>
+          <t>How to Become a Ziwei Astrology Master? From Rote Memorization of 108 Stars to "Dynamic Pattern Reading": A Deliberate Practice Guide Combining Cultural Semiotics, System Dynamics, and AI Collaboration</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>473</v>
+        <v>497</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>2</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>en/articles/gemini-api-free-tier-and-developer-guide.html</t>
+          <t>en/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/gemini-api-free-tier-and-developer-guide.html</t>
+          <t>https://gugopro.com/en/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026 Developer Blueprint: Building Zero-Cost Commercial-Grade Apps with Google Gemini Free API &amp; Comprehensive Error Troubleshooting Guide | GugoPro Cloud Systems Column</t>
+          <t>Is 16:8 Intermittent Fasting Really Better Than Counting Calories? From Autophagy and the Insulin Hypothesis to Caloric Deficit Realities: Escaping the Fasting Rebound Trap | GugoPro Metabolic Science Column</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2026 Developer Blueprint: Building Zero-Cost Commercial-Grade Apps with Google Gemini Free API &amp; Comprehensive Error Troubleshooting Guide</t>
+          <t>Is 16:8 Intermittent Fasting Really Better Than Counting Calories? From Autophagy and the Insulin Hypothesis to Caloric Deficit Realities: Escaping the Fasting Rebound Trap</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>394</v>
+        <v>643</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>2</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>en/articles/how-to-master-tarot-guide.html</t>
+          <t>en/articles/investment/01-compound-interest-guide.html</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/how-to-master-tarot-guide.html</t>
+          <t>https://gugopro.com/en/articles/investment/01-compound-interest-guide.html</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Tarot Master? From Rote Memorization to Intuitive Flow Reading: A Deliberate Practice Guide Combining Classical Semiotics, Narrative Psychology, and AI Collaboration | GugoPro Decision Science Column</t>
+          <t>Compounding and time value of money: how to build your first financial system from a balance sheet? | GugoPro Academy</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Tarot Master? From Rote Memorization to "Intuitive Flow Reading": A Comprehensive Deliberate Practice Guide Combining Classical Semiotics, Narrative Psychology, and AI Collaboration</t>
+          <t>Compounding and time value of money: how to build your first financial system from a balance sheet?</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>384</v>
+        <v>164</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>en/articles/how-to-master-ziwei-guide.html</t>
+          <t>en/articles/investment/02-etf-investing-bible.html</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/how-to-master-ziwei-guide.html</t>
+          <t>https://gugopro.com/en/articles/investment/02-etf-investing-bible.html</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Ziwei Astrology Master? From Rote Memorization to Dynamic Pattern Reading: A Deliberate Practice Guide Combining Cultural Semiotics, System Dynamics, and AI Collaboration | GugoPro Decision Science Column</t>
+          <t>Index Investing Bible: Taiwan 0050/006208 vs US VTI/VOO/QQQ — complete analysis | GugoPro Academy</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Ziwei Astrology Master? From Rote Memorization of 108 Stars to "Dynamic Pattern Reading": A Deliberate Practice Guide Combining Cultural Semiotics, System Dynamics, and AI Collaboration</t>
+          <t>Index Investing Bible: Taiwan 0050/006208 vs US VTI/VOO/QQQ — complete analysis</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>497</v>
+        <v>171</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>en/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
+          <t>en/articles/investment/03-asset-allocation-rebalancing.html</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
+          <t>https://gugopro.com/en/articles/investment/03-asset-allocation-rebalancing.html</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Is 16:8 Intermittent Fasting Really Better Than Counting Calories? From Autophagy and the Insulin Hypothesis to Caloric Deficit Realities: Escaping the Fasting Rebound Trap | GugoPro Metabolic Science Column</t>
+          <t>Asset allocation and dynamic rebalancing: from target weights to trading frictions｜GugoPro Academy</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Is 16:8 Intermittent Fasting Really Better Than Counting Calories? From Autophagy and the Insulin Hypothesis to Caloric Deficit Realities: Escaping the Fasting Rebound Trap</t>
+          <t>Asset allocation and dynamic rebalancing: Turn target weights into actionable decision rules.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>643</v>
+        <v>217</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/01-compound-interest-guide.html</t>
+          <t>en/articles/investment/04-brokerage-comparison.html</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/01-compound-interest-guide.html</t>
+          <t>https://gugopro.com/en/articles/investment/04-brokerage-comparison.html</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Compounding and time value of money: how to build your first financial system from a balance sheet? | GugoPro Academy</t>
+          <t>Complete guide to opening a US brokerage account: Taiwan sub-account vs. overseas brokers | GugoPro Academy</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Compounding and time value of money: how to build your first financial system from a balance sheet?</t>
+          <t>Complete guide to opening a US brokerage account: Taiwan sub-account vs. overseas brokers (Firstrade, IB, Schwab) comparison</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/02-etf-investing-bible.html</t>
+          <t>en/articles/investment/05-fundamental-valuation-metrics.html</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/02-etf-investing-bible.html</t>
+          <t>https://gugopro.com/en/articles/investment/05-fundamental-valuation-metrics.html</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Index Investing Bible: Taiwan 0050/006208 vs US VTI/VOO/QQQ — complete analysis | GugoPro Academy</t>
+          <t>Fundamental valuation metrics: P/E, P/B and ROE | GugoPro Academy</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Index Investing Bible: Taiwan 0050/006208 vs US VTI/VOO/QQQ — complete analysis</t>
+          <t>Fundamental valuation metrics: correctly reading P/E, P/B and ROE</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2538,12 +2538,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/03-asset-allocation-rebalancing.html</t>
+          <t>en/articles/investment/06-sharpe-mdd-risk-control.html</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/03-asset-allocation-rebalancing.html</t>
+          <t>https://gugopro.com/en/articles/investment/06-sharpe-mdd-risk-control.html</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Asset allocation and dynamic rebalancing: from target weights to trading frictions｜GugoPro Academy</t>
+          <t>Risk‑return and maximum drawdown analysis: Sharpe, Sortino, Calmar implementation guide｜GugoPro Academy</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Asset allocation and dynamic rebalancing: Turn target weights into actionable decision rules.</t>
+          <t>Risk‑return and maximum drawdown analysis</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2589,12 +2589,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/04-brokerage-comparison.html</t>
+          <t>en/articles/investment/07-fire-4-percent-rule.html</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/04-brokerage-comparison.html</t>
+          <t>https://gugopro.com/en/articles/investment/07-fire-4-percent-rule.html</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Complete guide to opening a US brokerage account: Taiwan sub-account vs. overseas brokers | GugoPro Academy</t>
+          <t>[Retirement Planning] What is the FIRE movement and the 4% rule? How to calculate withdrawal rates and your retirement funding gap | GugoPro Academy</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Complete guide to opening a US brokerage account: Taiwan sub-account vs. overseas brokers (Firstrade, IB, Schwab) comparison</t>
+          <t>[Retirement Planning] What is the FIRE movement and the 4% rule? How to calculate withdrawal rates and your retirement funding gap</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>169</v>
+        <v>250</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2640,12 +2640,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/05-fundamental-valuation-metrics.html</t>
+          <t>en/articles/investment/08-overseas-tax-guide.html</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/05-fundamental-valuation-metrics.html</t>
+          <t>https://gugopro.com/en/articles/investment/08-overseas-tax-guide.html</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2655,12 +2655,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Fundamental valuation metrics: P/E, P/B and ROE | GugoPro Academy</t>
+          <t>[Tax Optimization &amp; Filing] How are US stock investments taxed? Practical guide to the 750 萬 tax‑exempt threshold for foreign income and 30% dividend withholding practice | GugoPro Academy</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Fundamental valuation metrics: correctly reading P/E, P/B and ROE</t>
+          <t>[Tax Optimization &amp; Filing] How are US stock investments taxed? Practical guide to the 750 萬 tax‑exempt threshold for foreign income and 30% dividend withholding practice</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>117</v>
+        <v>227</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2691,12 +2691,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/06-sharpe-mdd-risk-control.html</t>
+          <t>en/articles/investment/09-high-dividend-etf-trap.html</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/06-sharpe-mdd-risk-control.html</t>
+          <t>https://gugopro.com/en/articles/investment/09-high-dividend-etf-trap.html</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Risk‑return and maximum drawdown analysis: Sharpe, Sortino, Calmar implementation guide｜GugoPro Academy</t>
+          <t>[High‑Dividend ETF Review] Taiwan ETFs 00878/00919/00929 vs US ETF SCHD: debunking high‑yield traps and the truth about total return | GugoPro Academy</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Risk‑return and maximum drawdown analysis</t>
+          <t>[High‑Dividend ETF Review] Taiwan ETFs 00878/00919/00929 vs US ETF SCHD: debunking high‑yield traps and the truth about total return</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2742,12 +2742,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/07-fire-4-percent-rule.html</t>
+          <t>en/articles/investment/10-bond-investing-guide.html</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/07-fire-4-percent-rule.html</t>
+          <t>https://gugopro.com/en/articles/investment/10-bond-investing-guide.html</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2757,12 +2757,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>[Retirement Planning] What is the FIRE movement and the 4% rule? How to calculate withdrawal rates and your retirement funding gap | GugoPro Academy</t>
+          <t>[Bond Investment Guide] US Treasuries (TLT/IEF) vs. Investment‑Grade Corporate Bonds (LQD): Asset‑allocation strategies in a rate‑cutting cycle | GugoPro Academy</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>[Retirement Planning] What is the FIRE movement and the 4% rule? How to calculate withdrawal rates and your retirement funding gap</t>
+          <t>[Bond Investment Guide] US Treasuries (TLT/IEF) vs. Investment‑Grade Corporate Bonds (LQD): Asset‑allocation strategies in a rate‑cutting cycle</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>250</v>
+        <v>219</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/08-overseas-tax-guide.html</t>
+          <t>en/articles/investment/11-brokerage-deep-review.html</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/08-overseas-tax-guide.html</t>
+          <t>https://gugopro.com/en/articles/investment/11-brokerage-deep-review.html</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>[Tax Optimization &amp; Filing] How are US stock investments taxed? Practical guide to the 750 萬 tax‑exempt threshold for foreign income and 30% dividend withholding practice | GugoPro Academy</t>
+          <t>[Encyclopedia of Overseas Broker Reviews] IB (Interactive Brokers), Firstrade, Charles Schwab — pros, cons, safety and hidden cost comparisons | GugoPro Academy</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>[Tax Optimization &amp; Filing] How are US stock investments taxed? Practical guide to the 750 萬 tax‑exempt threshold for foreign income and 30% dividend withholding practice</t>
+          <t>[Encyclopedia of Overseas Broker Reviews] IB (Interactive Brokers), Firstrade, Charles Schwab — pros, cons, safety and hidden cost comparisons</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2844,12 +2844,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/09-high-dividend-etf-trap.html</t>
+          <t>en/articles/investment/12-inflation-hedging-reits-gold.html</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/09-high-dividend-etf-trap.html</t>
+          <t>https://gugopro.com/en/articles/investment/12-inflation-hedging-reits-gold.html</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>[High‑Dividend ETF Review] Taiwan ETFs 00878/00919/00929 vs US ETF SCHD: debunking high‑yield traps and the truth about total return | GugoPro Academy</t>
+          <t>[Hedge Assets] How do gold (GLD) and real estate investment trusts (REITs) fit into asset allocation to hedge inflation? | GugoPro Academy</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>[High‑Dividend ETF Review] Taiwan ETFs 00878/00919/00929 vs US ETF SCHD: debunking high‑yield traps and the truth about total return</t>
+          <t>[Hedge Assets] How do gold (GLD) and real estate investment trusts (REITs) fit into asset allocation to hedge inflation?</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/10-bond-investing-guide.html</t>
+          <t>en/articles/investment/13-technical-indicators-truth.html</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/10-bond-investing-guide.html</t>
+          <t>https://gugopro.com/en/articles/investment/13-technical-indicators-truth.html</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>[Bond Investment Guide] US Treasuries (TLT/IEF) vs. Investment‑Grade Corporate Bonds (LQD): Asset‑allocation strategies in a rate‑cutting cycle | GugoPro Academy</t>
+          <t>[The Truth About Technical Analysis] Moving averages (MA), RSI, MACD — are they really useful? Technical indicators and blind spots from a quant trader's perspective | GugoPro Academy</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>[Bond Investment Guide] US Treasuries (TLT/IEF) vs. Investment‑Grade Corporate Bonds (LQD): Asset‑allocation strategies in a rate‑cutting cycle</t>
+          <t>[The Truth About Technical Analysis] Moving averages (MA), RSI, MACD — are they really useful? Technical indicators and blind spots from a quant trader's perspective</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -2946,12 +2946,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/11-brokerage-deep-review.html</t>
+          <t>en/articles/investment/14-backtesting-overfitting-guide.html</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/11-brokerage-deep-review.html</t>
+          <t>https://gugopro.com/en/articles/investment/14-backtesting-overfitting-guide.html</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>[Encyclopedia of Overseas Broker Reviews] IB (Interactive Brokers), Firstrade, Charles Schwab — pros, cons, safety and hidden cost comparisons | GugoPro Academy</t>
+          <t>[Systematic Trading] What is backtesting (回測)? How to avoid overfitting (過度擬合) and historical traps | GugoPro Academy</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>[Encyclopedia of Overseas Broker Reviews] IB (Interactive Brokers), Firstrade, Charles Schwab — pros, cons, safety and hidden cost comparisons</t>
+          <t>[Systematic Trading] What is backtesting (回測)? How to avoid overfitting (過度擬合) and historical traps</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -2997,12 +2997,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/12-inflation-hedging-reits-gold.html</t>
+          <t>en/articles/investment/15-quant-research-workflow.html</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/12-inflation-hedging-reits-gold.html</t>
+          <t>https://gugopro.com/en/articles/investment/15-quant-research-workflow.html</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>[Hedge Assets] How do gold (GLD) and real estate investment trusts (REITs) fit into asset allocation to hedge inflation? | GugoPro Academy</t>
+          <t>Quant research workflow: 5MA offsets, volatility Z‑Score and out‑of‑sample backtesting｜GugoPro Academy Z-Score</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>[Hedge Assets] How do gold (GLD) and real estate investment trusts (REITs) fit into asset allocation to hedge inflation?</t>
+          <t>Quant research workflow: Put 5MA, volatility and backtests into the same chain of evidence.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/13-technical-indicators-truth.html</t>
+          <t>en/articles/investment/16-futures-pairs-basis.html</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/13-technical-indicators-truth.html</t>
+          <t>https://gugopro.com/en/articles/investment/16-futures-pairs-basis.html</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>[The Truth About Technical Analysis] Moving averages (MA), RSI, MACD — are they really useful? Technical indicators and blind spots from a quant trader's perspective | GugoPro Academy</t>
+          <t>Pair trading and cash‑futures spread for Taiwan index futures / 富台期: from Basis to roll risk｜GugoPro Academy</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>[The Truth About Technical Analysis] Moving averages (MA), RSI, MACD — are they really useful? Technical indicators and blind spots from a quant trader's perspective</t>
+          <t>Taiwan index futures / 富台期 pair trading: Break down the Basis first, then discuss arbitrage.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3099,12 +3099,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/14-backtesting-overfitting-guide.html</t>
+          <t>en/articles/investment/17-practical-trading.html</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/14-backtesting-overfitting-guide.html</t>
+          <t>https://gugopro.com/en/articles/investment/17-practical-trading.html</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>[Systematic Trading] What is backtesting (回測)? How to avoid overfitting (過度擬合) and historical traps | GugoPro Academy</t>
+          <t>Category 13 Practical Trading: trading plan, execution, risk control and review — complete knowledge tree｜GugoPro Academy</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>[Systematic Trading] What is backtesting (回測)? How to avoid overfitting (過度擬合) and historical traps</t>
+          <t>Practical trading: Turn ideas into executable, stop‑lossable and reviewable processes.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>168</v>
+        <v>221</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3150,12 +3150,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/15-quant-research-workflow.html</t>
+          <t>en/articles/investment/18-trend-following-breakout-playbook.html</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/15-quant-research-workflow.html</t>
+          <t>https://gugopro.com/en/articles/investment/18-trend-following-breakout-playbook.html</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Quant research workflow: 5MA offsets, volatility Z‑Score and out‑of‑sample backtesting｜GugoPro Academy Z-Score</t>
+          <t>Trend following and breakout strategy Playbook: rules, sizing, false breakouts and backtest validation｜GugoPro Academy</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Quant research workflow: Put 5MA, volatility and backtests into the same chain of evidence.</t>
+          <t>Trend following and breakout strategy: Write your view as verifiable rules.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3196,17 +3196,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>首頁</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/16-futures-pairs-basis.html</t>
+          <t>en/articles/investment/index.html</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/16-futures-pairs-basis.html</t>
+          <t>https://gugopro.com/en/articles/investment/index.html</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Pair trading and cash‑futures spread for Taiwan index futures / 富台期: from Basis to roll risk｜GugoPro Academy</t>
+          <t>Investment Education Academy | GugoPro Academy</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Taiwan index futures / 富台期 pair trading: Break down the Basis first, then discuss arbitrage.</t>
+          <t>Systematized Investment education and practical matrix</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>237</v>
+        <v>168</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3252,12 +3252,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/17-practical-trading.html</t>
+          <t>en/articles/modern-ziwei-guide.html</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/17-practical-trading.html</t>
+          <t>https://gugopro.com/en/articles/modern-ziwei-guide.html</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Category 13 Practical Trading: trading plan, execution, risk control and review — complete knowledge tree｜GugoPro Academy</t>
+          <t>Farewell to Fatalism and Esoteric Intimidation! Reconstructing Ziwei Astrology with Modern Psychology: From Twelve Palaces and Si-Hua Dynamics to AI Decision Reflection Models | GugoPro Decision Science Column</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Practical trading: Turn ideas into executable, stop‑lossable and reviewable processes.</t>
+          <t>Farewell to Fatalism and Esoteric Intimidation! Reconstructing Ziwei Astrology with Modern Psychology: From Twelve Palaces and Si-Hua Dynamics to AI Decision Reflection Models</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>221</v>
+        <v>539</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/18-trend-following-breakout-playbook.html</t>
+          <t>en/articles/shadowing-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/18-trend-following-breakout-playbook.html</t>
+          <t>https://gugopro.com/en/articles/shadowing-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Trend following and breakout strategy Playbook: rules, sizing, false breakouts and backtest validation｜GugoPro Academy</t>
+          <t>Overcoming 'Mute English': Shadowing, CEFR Output, and AI Tutoring for Fluent Speaking | GugoPro Language Science</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Trend following and breakout strategy: Write your view as verifiable rules.</t>
+          <t>Overcoming 'Mute English': Shadowing, CEFR Output, and AI Tutoring for Fluent Speaking</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>205</v>
+        <v>281</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3349,17 +3349,17 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/index.html</t>
+          <t>en/articles/tarot-decision-framework.html</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/index.html</t>
+          <t>https://gugopro.com/en/articles/tarot-decision-framework.html</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3369,12 +3369,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Investment Education Academy | GugoPro Academy</t>
+          <t>Farewell to Fatalism: From Jungian Archetypal Psychology and Synchronicity to AI Tarot: Deconstructing Career Dilemmas and Relationship Anxiety via Structured Decision Models | GugoPro Decision Science Column</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Systematized Investment education and practical matrix</t>
+          <t>Farewell to Fatalism: From Jungian Archetypal Psychology and Synchronicity to AI Tarot: Deconstructing Career Dilemmas and Relationship Anxiety via Structured Decision Models</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>168</v>
+        <v>496</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>en/articles/modern-ziwei-guide.html</t>
+          <t>en/articles/tblt-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/modern-ziwei-guide.html</t>
+          <t>https://gugopro.com/en/articles/tblt-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Farewell to Fatalism and Esoteric Intimidation! Reconstructing Ziwei Astrology with Modern Psychology: From Twelve Palaces and Si-Hua Dynamics to AI Decision Reflection Models | GugoPro Decision Science Column</t>
+          <t>Beyond Rote Memorization: Task-Based Language Teaching (TBLT), Robinson's Cognition Hypothesis, and High-Impact Speaking with AI | GugoPro Language Science</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Farewell to Fatalism and Esoteric Intimidation! Reconstructing Ziwei Astrology with Modern Psychology: From Twelve Palaces and Si-Hua Dynamics to AI Decision Reflection Models</t>
+          <t>Beyond Rote Memorization: Task-Based Language Teaching (TBLT), Robinson's Cognition Hypothesis, and High-Impact Speaking with AI</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>539</v>
+        <v>522</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>2</v>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>en/articles/shadowing-with-ai-tutor.html</t>
+          <t>en/articles/tdee-and-macros-guide.html</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/shadowing-with-ai-tutor.html</t>
+          <t>https://gugopro.com/en/articles/tdee-and-macros-guide.html</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Overcoming 'Mute English': Shadowing, CEFR Output, and AI Tutoring for Fluent Speaking | GugoPro Language Science</t>
+          <t>Defeat Chronic Dieting &amp; Yo-Yo Rebound: The Complete Scientific Guide to TDEE, Adaptive Thermogenesis &amp; Macronutrient Control for Dining Out | GugoPro Metabolic Health Column</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Overcoming 'Mute English': Shadowing, CEFR Output, and AI Tutoring for Fluent Speaking</t>
+          <t>Defeat Chronic Dieting &amp; Yo-Yo Rebound: The Complete Scientific Guide to TDEE, Adaptive Thermogenesis &amp; Macronutrient Control for Dining Out</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>281</v>
+        <v>543</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>2</v>
@@ -3507,12 +3507,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>en/articles/tarot-decision-framework.html</t>
+          <t>en/articles/travel-translator-guide.html</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/tarot-decision-framework.html</t>
+          <t>https://gugopro.com/en/articles/travel-translator-guide.html</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3522,12 +3522,12 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Farewell to Fatalism: From Jungian Archetypal Psychology and Synchronicity to AI Tarot: Deconstructing Career Dilemmas and Relationship Anxiety via Structured Decision Models | GugoPro Decision Science Column</t>
+          <t>Say Goodbye to Awkward Phone-Passing! 180° Face-to-Face Flipped UI Design, HCI Spatial Psychology, and Practical Travel Communication Guide | GugoPro Cross-Cultural Column</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Farewell to Fatalism: From Jungian Archetypal Psychology and Synchronicity to AI Tarot: Deconstructing Career Dilemmas and Relationship Anxiety via Structured Decision Models</t>
+          <t>Say Goodbye to Awkward Phone-Passing! 180° Face-to-Face Flipped UI Design, HCI Spatial Psychology, and Practical Travel Communication Guide</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>2</v>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>en/articles/tblt-with-ai-tutor.html</t>
+          <t>en/articles/weight-loss-planner-guide.html</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/tblt-with-ai-tutor.html</t>
+          <t>https://gugopro.com/en/articles/weight-loss-planner-guide.html</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3573,12 +3573,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Beyond Rote Memorization: Task-Based Language Teaching (TBLT), Robinson's Cognition Hypothesis, and High-Impact Speaking with AI | GugoPro Language Science</t>
+          <t>Beyond Linear Weight Loss Myths: From Wishnofsky's 7,700 kcal Rule Flaws to Resistance Periodization and Plateau Breakthroughs: The Definitive Dynamic Fat Loss &amp; Caloric Deficit Guide | GugoPro Exercise Physiology Column</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Beyond Rote Memorization: Task-Based Language Teaching (TBLT), Robinson's Cognition Hypothesis, and High-Impact Speaking with AI</t>
+          <t>Beyond Linear Weight Loss Myths: From Wishnofsky's 7,700 kcal Rule Flaws to Resistance Periodization and Plateau Breakthroughs: The Definitive Dynamic Fat Loss &amp; Caloric Deficit Guide</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>2</v>
@@ -3609,12 +3609,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>en/articles/tdee-and-macros-guide.html</t>
+          <t>en/articles/youtube-english-listening-and-shadowing-guide.html</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/tdee-and-macros-guide.html</t>
+          <t>https://gugopro.com/en/articles/youtube-english-listening-and-shadowing-guide.html</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Defeat Chronic Dieting &amp; Yo-Yo Rebound: The Complete Scientific Guide to TDEE, Adaptive Thermogenesis &amp; Macronutrient Control for Dining Out | GugoPro Metabolic Health Column</t>
+          <t>Decoding YouTube Bilingual Listening &amp; Shadowing: L-Player Mastery &amp; Auditory Neural Shaping Guide | GugoPro Language Science</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Defeat Chronic Dieting &amp; Yo-Yo Rebound: The Complete Scientific Guide to TDEE, Adaptive Thermogenesis &amp; Macronutrient Control for Dining Out</t>
+          <t>Decoding YouTube Bilingual Listening &amp; Shadowing: L-Player Mastery &amp; Auditory Neural Shaping Guide</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>543</v>
+        <v>474</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>2</v>
@@ -3660,12 +3660,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>en/articles/travel-translator-guide.html</t>
+          <t>en/articles/youtube-listening-connected-speech-guide.html</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/travel-translator-guide.html</t>
+          <t>https://gugopro.com/en/articles/youtube-listening-connected-speech-guide.html</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Say Goodbye to Awkward Phone-Passing! 180° Face-to-Face Flipped UI Design, HCI Spatial Psychology, and Practical Travel Communication Guide | GugoPro Cross-Cultural Column</t>
+          <t>Why Watching YouTube Fails for English Learning: Speech Perception, Levenshtein Dictation Diff, and Shadowing Guide | GugoPro Language Science</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Say Goodbye to Awkward Phone-Passing! 180° Face-to-Face Flipped UI Design, HCI Spatial Psychology, and Practical Travel Communication Guide</t>
+          <t>Why Watching YouTube Fails for English Learning: Building Native Auditory Circuits via Speech Perception, Levenshtein Dictation Diff, and Shadowing</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>501</v>
+        <v>413</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>2</v>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>en/articles/weight-loss-planner-guide.html</t>
+          <t>en/articles/youtube-sequel-tracker-guide.html</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/weight-loss-planner-guide.html</t>
+          <t>https://gugopro.com/en/articles/youtube-sequel-tracker-guide.html</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Beyond Linear Weight Loss Myths: From Wishnofsky's 7,700 kcal Rule Flaws to Resistance Periodization and Plateau Breakthroughs: The Definitive Dynamic Fat Loss &amp; Caloric Deficit Guide | GugoPro Exercise Physiology Column</t>
+          <t>2026 YouTube Video Algorithm &amp; Series Retrieval Master Guide: Overcoming Recommendation Gaps via NLP Regex Denoising &amp; Incremental Diff Tracking | GugoPro Streaming Media Lab</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Beyond Linear Weight Loss Myths: From Wishnofsky's 7,700 kcal Rule Flaws to Resistance Periodization and Plateau Breakthroughs: The Definitive Dynamic Fat Loss &amp; Caloric Deficit Guide</t>
+          <t>2026 YouTube Video Algorithm &amp; Series Retrieval Master Guide: Overcoming Recommendation Gaps via NLP Regex Denoising &amp; Incremental Diff Tracking</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>511</v>
+        <v>492</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>2</v>
@@ -3757,17 +3757,17 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>en/articles/youtube-english-listening-and-shadowing-guide.html</t>
+          <t>en/tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/youtube-english-listening-and-shadowing-guide.html</t>
+          <t>https://gugopro.com/en/tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Decoding YouTube Bilingual Listening &amp; Shadowing: L-Player Mastery &amp; Auditory Neural Shaping Guide | GugoPro Language Science</t>
+          <t>Redirecting - AI Multilingual Speaking Tutor | GugoPro</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Decoding YouTube Bilingual Listening &amp; Shadowing: L-Player Mastery &amp; Auditory Neural Shaping Guide</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3792,14 +3792,14 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>474</v>
+        <v>0</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -3808,17 +3808,17 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>en/articles/youtube-listening-connected-speech-guide.html</t>
+          <t>en/tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/youtube-listening-connected-speech-guide.html</t>
+          <t>https://gugopro.com/en/tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Why Watching YouTube Fails for English Learning: Speech Perception, Levenshtein Dictation Diff, and Shadowing Guide | GugoPro Language Science</t>
+          <t>Redirecting - Face-to-Face Travel Voice Translator | GugoPro</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Why Watching YouTube Fails for English Learning: Building Native Auditory Circuits via Speech Perception, Levenshtein Dictation Diff, and Shadowing</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3843,14 +3843,14 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>413</v>
+        <v>0</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -3859,17 +3859,17 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>en/articles/youtube-sequel-tracker-guide.html</t>
+          <t>en/tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/youtube-sequel-tracker-guide.html</t>
+          <t>https://gugopro.com/en/tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026 YouTube Video Algorithm &amp; Series Retrieval Master Guide: Overcoming Recommendation Gaps via NLP Regex Denoising &amp; Incremental Diff Tracking | GugoPro Streaming Media Lab</t>
+          <t>Redirecting - AI Tarot Master | GugoPro</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>2026 YouTube Video Algorithm &amp; Series Retrieval Master Guide: Overcoming Recommendation Gaps via NLP Regex Denoising &amp; Incremental Diff Tracking</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3894,14 +3894,14 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>492</v>
+        <v>0</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -3910,17 +3910,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>en/index.html</t>
+          <t>en/tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/index.html</t>
+          <t>https://gugopro.com/en/tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>GugoPro Official Homepage | AI and Utility Tools</t>
+          <t>Redirecting - GugoPro AI Ziwei Astrology Master | GugoPro</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Web AI, data and utility tools for everyday work.</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3945,14 +3945,14 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai/english-speaking-tutor.html</t>
+          <t>en/tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai/english-speaking-tutor.html</t>
+          <t>https://gugopro.com/en/tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - AI Multilingual Speaking Tutor | GugoPro</t>
+          <t>Redirecting - YouTube Sequel Tracker | GugoPro</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai/realtime-translator.html</t>
+          <t>en/tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai/realtime-translator.html</t>
+          <t>https://gugopro.com/en/tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - Face-to-Face Travel Voice Translator | GugoPro</t>
+          <t>Redirecting - YouTube Study Player | GugoPro</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai/tarot-master.html</t>
+          <t>en/tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai/tarot-master.html</t>
+          <t>https://gugopro.com/en/tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - AI Tarot Master | GugoPro</t>
+          <t>Redirecting - AI Nutritionist | GugoPro</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai/ziwei-astrology.html</t>
+          <t>en/tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai/ziwei-astrology.html</t>
+          <t>https://gugopro.com/en/tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - GugoPro AI Ziwei Astrology Master | GugoPro</t>
+          <t>Redirecting - AI Weight Loss Coach | GugoPro</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -4165,29 +4165,21 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai-media/ai-video-tracker.html</t>
+          <t>googled0dfad57039c64f6.html</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai-media/ai-video-tracker.html</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>Redirecting - YouTube Sequel Tracker | GugoPro</t>
-        </is>
-      </c>
+          <t>https://gugopro.com/googled0dfad57039c64f6.html</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
@@ -4207,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4216,32 +4208,32 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>首頁</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>en/tools/english/l-player-study.html</t>
+          <t>index.html</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/english/l-player-study.html</t>
+          <t>https://gugopro.com/index.html</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - YouTube Study Player | GugoPro</t>
+          <t>GugoPro 工具箱｜YouTube 雙語字幕學習、AI 翻譯塔羅、TDEE 減脂計算與 Gemini API 配額監控等 9 款免費工具</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>GugoPro 工具箱</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4251,14 +4243,14 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75">
@@ -4267,17 +4259,17 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>首頁</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>en/tools/health/tdee-macros-calculator.html</t>
+          <t>index_en.html</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/health/tdee-macros-calculator.html</t>
+          <t>https://gugopro.com/index_en.html</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4287,12 +4279,12 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - AI Nutritionist | GugoPro</t>
+          <t>GugoPro Hub | 9 Free Browser Tools for YouTube Study, AI Translation, Tarot, TDEE &amp; Gemini Quota</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>GugoPro Hub</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4302,14 +4294,14 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76">
@@ -4318,32 +4310,32 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>首頁</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>en/tools/health/weight-loss-planner.html</t>
+          <t>index_ja.html</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/health/weight-loss-planner.html</t>
+          <t>https://gugopro.com/index_ja.html</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - AI Weight Loss Coach | GugoPro</t>
+          <t>GugoPro ツールボックス｜YouTube 2言語字幕学習、AI 翻訳タロット、TDEE 減脂計算、Gemini API 配額監視など無料ブラウザツール9選</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>GugoPro ツールボックス</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4353,14 +4345,14 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77">
@@ -4369,32 +4361,32 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>歷史工具</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>en/tools/pdf/pdf-suite.html</t>
+          <t>ja/articles/affective-filter-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/pdf/pdf-suite.html</t>
+          <t>https://gugopro.com/ja/articles/affective-filter-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - PDF Suite | GugoPro</t>
+          <t>話す恐怖を克服する心理学：クラッシェンの「情意フィルター仮説」、外国語不安（FLA）と AI チューターのゼロ圧力スピーキング完全ガイド｜GugoPro 言語学習コラム</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>話す恐怖を克服する心理学：クラッシェンの「情意フィルター仮説」、外国語不安（FLA）と AI チューターのゼロ圧力スピーキング完全ガイド</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4404,14 +4396,14 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -4420,24 +4412,32 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>googled0dfad57039c64f6.html</t>
+          <t>ja/articles/amazon-ai-product-research-guide.html</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/googled0dfad57039c64f6.html</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr"/>
+          <t>https://gugopro.com/ja/articles/amazon-ai-product-research-guide.html</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>2026 越境EC・高精度リサーチ完全攻略：AIセマンティック・リバースエンジニアリングによるAmazonヒット商品開発、競合低評価（VOC）痛点分析とListingキーワード配置マトリクス｜GugoPro EC戦略コラム</t>
+        </is>
+      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>2026 越境EC・高精度リサーチ完全攻略：AIセマンティック・リバースエンジニアリングによるAmazonヒット商品開発、競合低評価（VOC）痛点分析とListingキーワード配置マトリクス</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4447,14 +4447,14 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4463,32 +4463,32 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>index.html</t>
+          <t>ja/articles/carb-cycling-and-home-workout-guide.html</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/index.html</t>
+          <t>https://gugopro.com/ja/articles/carb-cycling-and-home-workout-guide.html</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>zh-TW</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>GugoPro 工具箱｜YouTube 雙語字幕學習、AI 翻譯塔羅、TDEE 減脂計算與跨境選品等 10 款免費免安裝工具</t>
+          <t>炭水化物循環法（カーボサイクル）完全減脂ガイド：高・低炭水化物日の生化学機序、器具不要の自宅燃焼ルーティン、筋分解防止の極意｜GugoPro 運動生理学コラム</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>GugoPro 工具箱</t>
+          <t>炭水化物循環法（カーボサイクル）完全減脂ガイド：高・低炭水化物日の生化学機序、器具不要の自宅燃焼ルーティン、筋分解防止の極意</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -4514,32 +4514,32 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>index_en.html</t>
+          <t>ja/articles/diabetes-and-insulin-resistance-guide.html</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/index_en.html</t>
+          <t>https://gugopro.com/ja/articles/diabetes-and-insulin-resistance-guide.html</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>GugoPro Hub | 10 Free Browser Tools for YouTube Study, AI Translation &amp; Tarot, TDEE, and Product Research</t>
+          <t>糖尿病予備群・インスリン抵抗性の食事法完全ガイド：GI/GL値・カーボカウントからAI写真食事管理まで——血糖値スパイクを防ぐ栄養素調控｜GugoPro 代謝医学コラム</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>GugoPro Hub</t>
+          <t>糖尿病予備群・インスリン抵抗性の食事法完全ガイド：GI/GL値・カーボカウントからAI写真食事管理まで——血糖値スパイクを防ぐ栄養素調控</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4553,10 +4553,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>396</v>
+        <v>164</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -4565,17 +4565,17 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>index_ja.html</t>
+          <t>ja/articles/english-intro-break-the-ice.html</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/index_ja.html</t>
+          <t>https://gugopro.com/ja/articles/english-intro-break-the-ice.html</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4585,12 +4585,12 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>GugoPro ツールボックス｜YouTube 2言語字幕学習、AI 翻訳タロット、TDEE 減脂計算、越境EC商品選定など無料ブラウザツール10選</t>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイング完全ガイド｜GugoPro 言語科学コラム</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>GugoPro ツールボックス</t>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>213</v>
+        <v>170</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/affective-filter-with-ai-tutor.html</t>
+          <t>ja/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/affective-filter-with-ai-tutor.html</t>
+          <t>https://gugopro.com/ja/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>話す恐怖を克服する心理学：クラッシェンの「情意フィルター仮説」、外国語不安（FLA）と AI チューターのゼロ圧力スピーキング完全ガイド｜GugoPro 言語学習コラム</t>
+          <t>脂肪肝を逆転する減糖＆地中海食完全ガイド：内臓脂肪燃焼からPFC黄金比率・外食AI管理まで——MASLDを根本改善する長寿実戦マニュアル｜GugoPro 肝臓代謝コラム</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>話す恐怖を克服する心理学：クラッシェンの「情意フィルター仮説」、外国語不安（FLA）と AI チューターのゼロ圧力スピーキング完全ガイド</t>
+          <t>脂肪肝を逆転する減糖＆地中海食完全ガイド：内臓脂肪燃焼からPFC黄金比率・外食AI管理まで——MASLDを根本改善する長寿実戦マニュアル</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>2</v>
@@ -4672,12 +4672,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/amazon-ai-product-research-guide.html</t>
+          <t>ja/articles/gemini-api-free-tier-and-developer-guide.html</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/amazon-ai-product-research-guide.html</t>
+          <t>https://gugopro.com/ja/articles/gemini-api-free-tier-and-developer-guide.html</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026 越境EC・高精度リサーチ完全攻略：AIセマンティック・リバースエンジニアリングによるAmazonヒット商品開発、競合低評価（VOC）痛点分析とListingキーワード配置マトリクス｜GugoPro EC戦略コラム</t>
+          <t>2026 開発者完全攻略ハンドブック：Google Gemini 公式無料APIを活用したゼロコスト商用グレードアプリのアーキテクチャ設計とエラー完全トラブルシューティング指南｜GugoPro クラウドシステムコラム</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>2026 越境EC・高精度リサーチ完全攻略：AIセマンティック・リバースエンジニアリングによるAmazonヒット商品開発、競合低評価（VOC）痛点分析とListingキーワード配置マトリクス</t>
+          <t>2026 開発者完全攻略ハンドブック：Google Gemini 公式無料APIを活用したゼロコスト商用グレードアプリのアーキテクチャ設計とエラー完全トラブルシューティング指南</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>227</v>
+        <v>271</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -4723,12 +4723,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/carb-cycling-and-home-workout-guide.html</t>
+          <t>ja/articles/how-to-master-tarot-guide.html</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/carb-cycling-and-home-workout-guide.html</t>
+          <t>https://gugopro.com/ja/articles/how-to-master-tarot-guide.html</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4738,12 +4738,12 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>炭水化物循環法（カーボサイクル）完全減脂ガイド：高・低炭水化物日の生化学機序、器具不要の自宅燃焼ルーティン、筋分解防止の極意｜GugoPro 運動生理学コラム</t>
+          <t>タロットマスターへの道：78枚の丸暗記を脱し「直観的フロー・リーディング」へ——古典記号論、ナラティブ心理学、AI協同による限界的練習完全ガイド｜GugoPro 意思決定科学コラム</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>炭水化物循環法（カーボサイクル）完全減脂ガイド：高・低炭水化物日の生化学機序、器具不要の自宅燃焼ルーティン、筋分解防止の極意</t>
+          <t>如何にしてタロットマスターとなるか？ 78枚の意味の丸暗記から「直観的フロー・リーディング」へ：古典記号論・ナラティブ心理学・AI協同による限界的練習完全手引</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>204</v>
+        <v>145</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>2</v>
@@ -4774,12 +4774,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/diabetes-and-insulin-resistance-guide.html</t>
+          <t>ja/articles/how-to-master-ziwei-guide.html</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/diabetes-and-insulin-resistance-guide.html</t>
+          <t>https://gugopro.com/ja/articles/how-to-master-ziwei-guide.html</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>糖尿病予備群・インスリン抵抗性の食事法完全ガイド：GI/GL値・カーボカウントからAI写真食事管理まで——血糖値スパイクを防ぐ栄養素調控｜GugoPro 代謝医学コラム</t>
+          <t>紫微斗数マスターへの道：百の星の丸暗記を脱し「動態格局解盤」へ——文化記号論、システムダイナミクス、AI協同による限界的練習完全ガイド｜GugoPro 意思決定科学コラム</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>糖尿病予備群・インスリン抵抗性の食事法完全ガイド：GI/GL値・カーボカウントからAI写真食事管理まで——血糖値スパイクを防ぐ栄養素調控</t>
+          <t>紫微斗数マスターへの道：百の星の丸暗記を脱し「動態格局解盤」へ——文化記号論、システムダイナミクス、AI協同による限界的練習完全ガイド</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>2</v>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/english-intro-break-the-ice.html</t>
+          <t>ja/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/english-intro-break-the-ice.html</t>
+          <t>https://gugopro.com/ja/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイング完全ガイド｜GugoPro 言語科学コラム</t>
+          <t>168断食はカロリー計算より本当に痩せるのか？細胞自噬、インスリン仮説からエネルギー赤字の真相まで：リバウンドと筋肉減少の罠を解体する完全ガイド｜GugoPro 代謝内分泌コラム</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
+          <t>168断食はカロリー計算より本当に痩せるのか？細胞自噬、インスリン仮説からエネルギー赤字の真相まで：リバウンドと筋肉減少の罠を解体する完全ガイド</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>170</v>
+        <v>233</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>2</v>
@@ -4876,12 +4876,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
+          <t>ja/articles/investment/01-compound-interest-guide.html</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
+          <t>https://gugopro.com/ja/articles/investment/01-compound-interest-guide.html</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>脂肪肝を逆転する減糖＆地中海食完全ガイド：内臓脂肪燃焼からPFC黄金比率・外食AI管理まで——MASLDを根本改善する長寿実戦マニュアル｜GugoPro 肝臓代謝コラム</t>
+          <t>複利効果と時間価値：バランスシートから最初のファイナンシャルシステムを構築するには？ | GugoPro Academy</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>脂肪肝を逆転する減糖＆地中海食完全ガイド：内臓脂肪燃焼からPFC黄金比率・外食AI管理まで——MASLDを根本改善する長寿実戦マニュアル</t>
+          <t>複利効果と時間価値：バランスシートから最初のファイナンシャルシステムを構築するには？</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>206</v>
+        <v>43</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/gemini-api-free-tier-and-developer-guide.html</t>
+          <t>ja/articles/investment/02-etf-investing-bible.html</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/gemini-api-free-tier-and-developer-guide.html</t>
+          <t>https://gugopro.com/ja/articles/investment/02-etf-investing-bible.html</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4942,12 +4942,12 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026 開発者完全攻略ハンドブック：Google Gemini 公式無料APIを活用したゼロコスト商用グレードアプリのアーキテクチャ設計とエラー完全トラブルシューティング指南｜GugoPro クラウドシステムコラム</t>
+          <t>インデックス投資バイブル：台湾 0050/006208 vs 米国 VTI/VOO/QQQ 完全解析 | GugoPro Academy</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>2026 開発者完全攻略ハンドブック：Google Gemini 公式無料APIを活用したゼロコスト商用グレードアプリのアーキテクチャ設計とエラー完全トラブルシューティング指南</t>
+          <t>インデックス投資バイブル：台湾 0050/006208 vs 米国 VTI/VOO/QQQ 完全解析</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>271</v>
+        <v>63</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/how-to-master-tarot-guide.html</t>
+          <t>ja/articles/investment/03-asset-allocation-rebalancing.html</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/how-to-master-tarot-guide.html</t>
+          <t>https://gugopro.com/ja/articles/investment/03-asset-allocation-rebalancing.html</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>タロットマスターへの道：78枚の丸暗記を脱し「直観的フロー・リーディング」へ——古典記号論、ナラティブ心理学、AI協同による限界的練習完全ガイド｜GugoPro 意思決定科学コラム</t>
+          <t>資産配分と動的リバランス：目標ウェイトから取引摩擦まで｜GugoPro Academy</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>如何にしてタロットマスターとなるか？ 78枚の意味の丸暗記から「直観的フロー・リーディング」へ：古典記号論・ナラティブ心理学・AI協同による限界的練習完全手引</t>
+          <t>資産配分と動的リバランス： 目標ウェイトを実行可能な意思決定ルールにする。</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>145</v>
+        <v>88</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/how-to-master-ziwei-guide.html</t>
+          <t>ja/articles/investment/04-brokerage-comparison.html</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/how-to-master-ziwei-guide.html</t>
+          <t>https://gugopro.com/ja/articles/investment/04-brokerage-comparison.html</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5044,12 +5044,12 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>紫微斗数マスターへの道：百の星の丸暗記を脱し「動態格局解盤」へ——文化記号論、システムダイナミクス、AI協同による限界的練習完全ガイド｜GugoPro 意思決定科学コラム</t>
+          <t>米国ブローカー口座開設完全ガイド：台湾の複委託 vs 海外ブローカー | GugoPro Academy</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>紫微斗数マスターへの道：百の星の丸暗記を脱し「動態格局解盤」へ——文化記号論、システムダイナミクス、AI協同による限界的練習完全ガイド</t>
+          <t>米国ブローカー口座開設完全ガイド：台湾の複委託 vs 海外ブローカー（Firstrade、IB、Schwab）比較</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5063,10 +5063,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>199</v>
+        <v>63</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
+          <t>ja/articles/investment/05-fundamental-valuation-metrics.html</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
+          <t>https://gugopro.com/ja/articles/investment/05-fundamental-valuation-metrics.html</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>168断食はカロリー計算より本当に痩せるのか？細胞自噬、インスリン仮説からエネルギー赤字の真相まで：リバウンドと筋肉減少の罠を解体する完全ガイド｜GugoPro 代謝内分泌コラム</t>
+          <t>ファンダメンタル評価指標：P/E、P/B、ROE | GugoPro Academy</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>168断食はカロリー計算より本当に痩せるのか？細胞自噬、インスリン仮説からエネルギー赤字の真相まで：リバウンドと筋肉減少の罠を解体する完全ガイド</t>
+          <t>ファンダメンタル評価指標：P/E（株価収益率）、P/B（株価純資産倍率）、ROEの正しい読み方</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>233</v>
+        <v>61</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/01-compound-interest-guide.html</t>
+          <t>ja/articles/investment/06-sharpe-mdd-risk-control.html</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/01-compound-interest-guide.html</t>
+          <t>https://gugopro.com/ja/articles/investment/06-sharpe-mdd-risk-control.html</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>複利効果と時間価値：バランスシートから最初のファイナンシャルシステムを構築するには？ | GugoPro Academy</t>
+          <t>リスクリターンと最大ドローダウン分析：Sharpe、Sortino、Calmar 実装ガイド｜GugoPro Academy</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>複利効果と時間価値：バランスシートから最初のファイナンシャルシステムを構築するには？</t>
+          <t>リスクリターンと最大ドローダウンの分析</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/02-etf-investing-bible.html</t>
+          <t>ja/articles/investment/07-fire-4-percent-rule.html</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/02-etf-investing-bible.html</t>
+          <t>https://gugopro.com/ja/articles/investment/07-fire-4-percent-rule.html</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>インデックス投資バイブル：台湾 0050/006208 vs 米国 VTI/VOO/QQQ 完全解析 | GugoPro Academy</t>
+          <t>【退職金プラン】FIRE ムーブメントと 4% ルールとは？引き出し率と退職資金の不足額の計算方法 | GugoPro Academy</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>インデックス投資バイブル：台湾 0050/006208 vs 米国 VTI/VOO/QQQ 完全解析</t>
+          <t>【退職金プラン】FIRE ムーブメントと 4% ルールとは？引き出し率と退職資金の不足額の計算方法</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5233,12 +5233,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/03-asset-allocation-rebalancing.html</t>
+          <t>ja/articles/investment/08-overseas-tax-guide.html</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/03-asset-allocation-rebalancing.html</t>
+          <t>https://gugopro.com/ja/articles/investment/08-overseas-tax-guide.html</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>資産配分と動的リバランス：目標ウェイトから取引摩擦まで｜GugoPro Academy</t>
+          <t>【節税と確定申告】米国株投資はどう申告するか？海外所得 750 萬 の免税枠と 30% 配当源泉徴収の実務 | GugoPro Academy</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>資産配分と動的リバランス： 目標ウェイトを実行可能な意思決定ルールにする。</t>
+          <t>【節税と確定申告】米国株投資はどう申告するか？海外所得 750 萬 の免税枠と 30% 配当源泉徴収の実務</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/04-brokerage-comparison.html</t>
+          <t>ja/articles/investment/09-high-dividend-etf-trap.html</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/04-brokerage-comparison.html</t>
+          <t>https://gugopro.com/ja/articles/investment/09-high-dividend-etf-trap.html</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>米国ブローカー口座開設完全ガイド：台湾の複委託 vs 海外ブローカー | GugoPro Academy</t>
+          <t>【高配当 ETF 評価】台湾上場 ETF 00878/00919/00929 vs 米国 ETF SCHD：高配当利回りの罠を解くと総リターンの真実が見える | GugoPro Academy</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>米国ブローカー口座開設完全ガイド：台湾の複委託 vs 海外ブローカー（Firstrade、IB、Schwab）比較</t>
+          <t>【高配当 ETF 評価】台湾上場 ETF 00878/00919/00929 vs 米国 ETF SCHD：高配当利回りの罠を解くと総リターンの真実が見える</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5318,7 +5318,7 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5335,12 +5335,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/05-fundamental-valuation-metrics.html</t>
+          <t>ja/articles/investment/10-bond-investing-guide.html</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/05-fundamental-valuation-metrics.html</t>
+          <t>https://gugopro.com/ja/articles/investment/10-bond-investing-guide.html</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>ファンダメンタル評価指標：P/E、P/B、ROE | GugoPro Academy</t>
+          <t>【債券投資ガイド】米国債 (TLT/IEF) vs 投資適格社債 (LQD)：利下げサイクルにおける資産配分戦略 | GugoPro Academy</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>ファンダメンタル評価指標：P/E（株価収益率）、P/B（株価純資産倍率）、ROEの正しい読み方</t>
+          <t>【債券投資ガイド】米国債 (TLT/IEF) vs 投資適格社債 (LQD)：利下げサイクルにおける資産配分戦略</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5386,12 +5386,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/06-sharpe-mdd-risk-control.html</t>
+          <t>ja/articles/investment/11-brokerage-deep-review.html</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/06-sharpe-mdd-risk-control.html</t>
+          <t>https://gugopro.com/ja/articles/investment/11-brokerage-deep-review.html</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>リスクリターンと最大ドローダウン分析：Sharpe、Sortino、Calmar 実装ガイド｜GugoPro Academy</t>
+          <t>【海外証券会社評価大全】IB（盈透／Interactive Brokers）、Firstrade、Charles Schwab（嘉信理財）─ 長所・短所、安全性と隠れたコスト比較 | GugoPro Academy</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>リスクリターンと最大ドローダウンの分析</t>
+          <t>【海外証券会社評価大全】IB（盈透／Interactive Brokers）、Firstrade、Charles Schwab（嘉信理財）─ 長所・短所、安全性と隠れたコスト比較</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5437,12 +5437,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/07-fire-4-percent-rule.html</t>
+          <t>ja/articles/investment/12-inflation-hedging-reits-gold.html</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/07-fire-4-percent-rule.html</t>
+          <t>https://gugopro.com/ja/articles/investment/12-inflation-hedging-reits-gold.html</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>【退職金プラン】FIRE ムーブメントと 4% ルールとは？引き出し率と退職資金の不足額の計算方法 | GugoPro Academy</t>
+          <t>【ヘッジ資産】金（GLD）と不動産投資信託（REITs）はインフレ対策として資産配分にどう組み込むか？ | GugoPro Academy</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>【退職金プラン】FIRE ムーブメントと 4% ルールとは？引き出し率と退職資金の不足額の計算方法</t>
+          <t>【ヘッジ資産】金（GLD）と不動産投資信託（REITs）はインフレ対策として資産配分にどう組み込むか？</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5488,12 +5488,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/08-overseas-tax-guide.html</t>
+          <t>ja/articles/investment/13-technical-indicators-truth.html</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/08-overseas-tax-guide.html</t>
+          <t>https://gugopro.com/ja/articles/investment/13-technical-indicators-truth.html</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>【節税と確定申告】米国株投資はどう申告するか？海外所得 750 萬 の免税枠と 30% 配当源泉徴収の実務 | GugoPro Academy</t>
+          <t>【テクニカル分析の真実】移動平均線 (MA)、RSI、MACD は本当に役立つのか？クオンツトレーダーが見るテクニカル指標の有効場面と盲点 | GugoPro Academy</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>【節税と確定申告】米国株投資はどう申告するか？海外所得 750 萬 の免税枠と 30% 配当源泉徴収の実務</t>
+          <t>【テクニカル分析の真実】移動平均線 (MA)、RSI、MACD は本当に役立つのか？クオンツトレーダーが見るテクニカル指標の有効場面と盲点</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5522,7 +5522,7 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/09-high-dividend-etf-trap.html</t>
+          <t>ja/articles/investment/14-backtesting-overfitting-guide.html</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/09-high-dividend-etf-trap.html</t>
+          <t>https://gugopro.com/ja/articles/investment/14-backtesting-overfitting-guide.html</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>【高配当 ETF 評価】台湾上場 ETF 00878/00919/00929 vs 米国 ETF SCHD：高配当利回りの罠を解くと総リターンの真実が見える | GugoPro Academy</t>
+          <t>【システムトレード】バックテスト (Backtesting/回測) とは？過学習 (Overfitting/過度擬合) と歴史的罠を避ける方法 | GugoPro Academy</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>【高配当 ETF 評価】台湾上場 ETF 00878/00919/00929 vs 米国 ETF SCHD：高配当利回りの罠を解くと総リターンの真実が見える</t>
+          <t>【システムトレード】バックテスト (Backtesting/回測) とは？過学習 (Overfitting/過度擬合) と歴史的罠を避ける方法</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5590,12 +5590,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/10-bond-investing-guide.html</t>
+          <t>ja/articles/investment/15-quant-research-workflow.html</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/10-bond-investing-guide.html</t>
+          <t>https://gugopro.com/ja/articles/investment/15-quant-research-workflow.html</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5605,12 +5605,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>【債券投資ガイド】米国債 (TLT/IEF) vs 投資適格社債 (LQD)：利下げサイクルにおける資産配分戦略 | GugoPro Academy</t>
+          <t>量的研究ワークフロー：5MAオフセット、ボラティリティのZ‑Score、アウト‑オブ‑サンプルバックテスト｜GugoPro Academy Z-Score</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>【債券投資ガイド】米国債 (TLT/IEF) vs 投資適格社債 (LQD)：利下げサイクルにおける資産配分戦略</t>
+          <t>量的研究ワークフロー： 5MA、ボラティリティ、バックテストを同じ証拠チェーンに組み込む。</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/11-brokerage-deep-review.html</t>
+          <t>ja/articles/investment/16-futures-pairs-basis.html</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/11-brokerage-deep-review.html</t>
+          <t>https://gugopro.com/ja/articles/investment/16-futures-pairs-basis.html</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>【海外証券会社評価大全】IB（盈透／Interactive Brokers）、Firstrade、Charles Schwab（嘉信理財）─ 長所・短所、安全性と隠れたコスト比較 | GugoPro Academy</t>
+          <t>臺指期／富台期のペア取引と期現價差：Basisからロールリスクまで｜GugoPro Academy</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>【海外証券会社評価大全】IB（盈透／Interactive Brokers）、Firstrade、Charles Schwab（嘉信理財）─ 長所・短所、安全性と隠れたコスト比較</t>
+          <t>臺指期／富台期ペア取引： まず Basis を分解し、その後で裁定について議論する。</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/12-inflation-hedging-reits-gold.html</t>
+          <t>ja/articles/investment/17-practical-trading.html</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/12-inflation-hedging-reits-gold.html</t>
+          <t>https://gugopro.com/ja/articles/investment/17-practical-trading.html</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>【ヘッジ資産】金（GLD）と不動産投資信託（REITs）はインフレ対策として資産配分にどう組み込むか？ | GugoPro Academy</t>
+          <t>第13類 実戦取引：取引計画、実行、リスク管理、レビューの完全なナレッジツリー｜GugoPro Academy</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>【ヘッジ資産】金（GLD）と不動産投資信託（REITs）はインフレ対策として資産配分にどう組み込むか？</t>
+          <t>実戦トレーディング： アイデアを実行可能でストップが設定でき、再検討できるプロセスにする。</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/13-technical-indicators-truth.html</t>
+          <t>ja/articles/investment/18-trend-following-breakout-playbook.html</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/13-technical-indicators-truth.html</t>
+          <t>https://gugopro.com/ja/articles/investment/18-trend-following-breakout-playbook.html</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>【テクニカル分析の真実】移動平均線 (MA)、RSI、MACD は本当に役立つのか？クオンツトレーダーが見るテクニカル指標の有効場面と盲点 | GugoPro Academy</t>
+          <t>トレンド追跡とブレイクアウト戦略プレイブック：ルール、ポジション、フェイクブレイク、バックテスト検証｜GugoPro Academy</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>【テクニカル分析の真実】移動平均線 (MA)、RSI、MACD は本当に役立つのか？クオンツトレーダーが見るテクニカル指標の有効場面と盲点</t>
+          <t>トレンド追跡とブレイクアウト戦略： 自分の「見解」を検証可能なルールに書き換える。</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5789,17 +5789,17 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>首頁</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/14-backtesting-overfitting-guide.html</t>
+          <t>ja/articles/investment/index.html</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/14-backtesting-overfitting-guide.html</t>
+          <t>https://gugopro.com/ja/articles/investment/index.html</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>【システムトレード】バックテスト (Backtesting/回測) とは？過学習 (Overfitting/過度擬合) と歴史的罠を避ける方法 | GugoPro Academy</t>
+          <t>投資教育アカデミー | GugoPro Academy</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>【システムトレード】バックテスト (Backtesting/回測) とは？過学習 (Overfitting/過度擬合) と歴史的罠を避ける方法</t>
+          <t>システム化 投資教育と実戦のマトリクス</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -5845,12 +5845,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/15-quant-research-workflow.html</t>
+          <t>ja/articles/modern-ziwei-guide.html</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/15-quant-research-workflow.html</t>
+          <t>https://gugopro.com/ja/articles/modern-ziwei-guide.html</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>量的研究ワークフロー：5MAオフセット、ボラティリティのZ‑Score、アウト‑オブ‑サンプルバックテスト｜GugoPro Academy Z-Score</t>
+          <t>宿命論とオカルト的脅迫からの脱却：現代心理学で再構築する紫微斗数——十二宮位、四化の動態からAI意思決定反省モデルへ｜GugoPro 意思決定科学コラム</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>量的研究ワークフロー： 5MA、ボラティリティ、バックテストを同じ証拠チェーンに組み込む。</t>
+          <t>宿命論とオカルト的脅迫からの脱却：現代心理学で再構築する紫微斗数——十二宮位、四化の動態からAI意思決定反省モデルへ</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>92</v>
+        <v>169</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/16-futures-pairs-basis.html</t>
+          <t>ja/articles/shadowing-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/16-futures-pairs-basis.html</t>
+          <t>https://gugopro.com/ja/articles/shadowing-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5911,12 +5911,12 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>臺指期／富台期のペア取引と期現價差：Basisからロールリスクまで｜GugoPro Academy</t>
+          <t>「話せない英語」にサヨナラ！シャドーイング、CEFR文脈出力、AIチューターによるスピーキング実践ガイド｜GugoPro 言語科学コラム</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>臺指期／富台期ペア取引： まず Basis を分解し、その後で裁定について議論する。</t>
+          <t>「話せない英語」にサヨナラ！シャドーイング、CEFR文脈輸出、AIチューターによるスピーキング実践ガイド</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/17-practical-trading.html</t>
+          <t>ja/articles/tarot-decision-framework.html</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/17-practical-trading.html</t>
+          <t>https://gugopro.com/ja/articles/tarot-decision-framework.html</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>第13類 実戦取引：取引計画、実行、リスク管理、レビューの完全なナレッジツリー｜GugoPro Academy</t>
+          <t>迷信的宿命論からの脱却：ユングの「元型」心理学・共時性からAIタロットへ——キャリアの二者択一と関係性不安を解体する構造化意思決定モデル｜GugoPro 意思決定科学コラム</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>実戦トレーディング： アイデアを実行可能でストップが設定でき、再検討できるプロセスにする。</t>
+          <t>迷信的宿命論からの脱却：ユングの「元型」心理学・共時性からAIタロットへ——キャリアの二者択一と関係性不安を解体する構造化意思決定モデル</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/18-trend-following-breakout-playbook.html</t>
+          <t>ja/articles/tblt-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/18-trend-following-breakout-playbook.html</t>
+          <t>https://gugopro.com/ja/articles/tblt-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>トレンド追跡とブレイクアウト戦略プレイブック：ルール、ポジション、フェイクブレイク、バックテスト検証｜GugoPro Academy</t>
+          <t>丸暗記にサヨナラ！タスク型教授法（TBLT）、Robinson認知仮説とAIチューターによる英会話実践ガイド｜GugoPro 言語科学コラム</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>トレンド追跡とブレイクアウト戦略： 自分の「見解」を検証可能なルールに書き換える。</t>
+          <t>丸暗記にサヨナラ！タスク型教授法（TBLT）、Robinson認知仮説とAIチューターによる英会話実践ガイド</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6032,10 +6032,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>117</v>
+        <v>184</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -6044,17 +6044,17 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/index.html</t>
+          <t>ja/articles/tdee-and-macros-guide.html</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/index.html</t>
+          <t>https://gugopro.com/ja/articles/tdee-and-macros-guide.html</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>投資教育アカデミー | GugoPro Academy</t>
+          <t>無駄な食事制限とリバウンドを完全に卒業！熱力学エネルギー収支、適応熱産生からAI食事解析まで：外食派のためのTDEE＆PFCバランス精密調整バイブル｜GugoPro 代謝健康專欄</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>システム化 投資教育と実戦のマトリクス</t>
+          <t>無駄な食事制限とリバウンドを完全に卒業！熱力学エネルギー収支、適応熱産生からAI食事解析まで：外食派のためのTDEE＆PFCバランス精密調整バイブル</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>68</v>
+        <v>248</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/modern-ziwei-guide.html</t>
+          <t>ja/articles/travel-translator-guide.html</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/modern-ziwei-guide.html</t>
+          <t>https://gugopro.com/ja/articles/travel-translator-guide.html</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>宿命論とオカルト的脅迫からの脱却：現代心理学で再構築する紫微斗数——十二宮位、四化の動態からAI意思決定反省モデルへ｜GugoPro 意思決定科学コラム</t>
+          <t>スマホの気まずい手渡しにサヨナラ！180°対面反転UIのデザイン美学・HCI空間心理学と海外旅行会話実践ガイド｜GugoPro 異文化コミュニケーションコラム</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>宿命論とオカルト的脅迫からの脱却：現代心理学で再構築する紫微斗数——十二宮位、四化の動態からAI意思決定反省モデルへ</t>
+          <t>スマホの気まずい手渡しにサヨナラ！180°対面反転UIのデザイン美学・HCI空間心理学と海外旅行会話実践ガイド</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>169</v>
+        <v>206</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>2</v>
@@ -6151,12 +6151,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/shadowing-with-ai-tutor.html</t>
+          <t>ja/articles/weight-loss-planner-guide.html</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/shadowing-with-ai-tutor.html</t>
+          <t>https://gugopro.com/ja/articles/weight-loss-planner-guide.html</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>「話せない英語」にサヨナラ！シャドーイング、CEFR文脈出力、AIチューターによるスピーキング実践ガイド｜GugoPro 言語科学コラム</t>
+          <t>線形減量の幻想からの脱却！Wishnofsky 7700kcal法則の破綻からレジスタンストレーニング期分け・停滞期突破まで：動的減量計画とカロリー赤字完全ガイド｜GugoPro 運動生理学コラム</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>「話せない英語」にサヨナラ！シャドーイング、CEFR文脈輸出、AIチューターによるスピーキング実践ガイド</t>
+          <t>線形減量の幻想からの脱却！Wishnofsky 7700kcal法則の破綻からレジスタンストレーニング期分け・停滞期突破まで：動的減量計画とカロリー赤字完全ガイド</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>146</v>
+        <v>229</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>2</v>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/tarot-decision-framework.html</t>
+          <t>ja/articles/youtube-english-listening-and-shadowing-guide.html</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/tarot-decision-framework.html</t>
+          <t>https://gugopro.com/ja/articles/youtube-english-listening-and-shadowing-guide.html</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>迷信的宿命論からの脱却：ユングの「元型」心理学・共時性からAIタロットへ——キャリアの二者択一と関係性不安を解体する構造化意思決定モデル｜GugoPro 意思決定科学コラム</t>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイングで母語レベルの聴覚神経回路を構築する完全ガイド｜GugoPro 言語科学コラム</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>迷信的宿命論からの脱却：ユングの「元型」心理学・共時性からAIタロットへ——キャリアの二者択一と関係性不安を解体する構造化意思決定モデル</t>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/tblt-with-ai-tutor.html</t>
+          <t>ja/articles/youtube-listening-connected-speech-guide.html</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/tblt-with-ai-tutor.html</t>
+          <t>https://gugopro.com/ja/articles/youtube-listening-connected-speech-guide.html</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>丸暗記にサヨナラ！タスク型教授法（TBLT）、Robinson認知仮説とAIチューターによる英会話実践ガイド｜GugoPro 言語科学コラム</t>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイング完全ガイド｜GugoPro 言語科学コラム</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>丸暗記にサヨナラ！タスク型教授法（TBLT）、Robinson認知仮説とAIチューターによる英会話実践ガイド</t>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>2</v>
@@ -6304,12 +6304,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/tdee-and-macros-guide.html</t>
+          <t>ja/articles/youtube-sequel-tracker-guide.html</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/tdee-and-macros-guide.html</t>
+          <t>https://gugopro.com/ja/articles/youtube-sequel-tracker-guide.html</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>無駄な食事制限とリバウンドを完全に卒業！熱力学エネルギー収支、適応熱産生からAI食事解析まで：外食派のためのTDEE＆PFCバランス精密調整バイブル｜GugoPro 代謝健康專欄</t>
+          <t>2026年YouTube動画推薦アルゴリズムとシリーズ検索完全ガイド：推薦漏れを解消しNLP正規表現ノイズ除去と差分照合で跨チャンネル追跡を実現する｜GugoPro ストリーミング研究コラム</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>無駄な食事制限とリバウンドを完全に卒業！熱力学エネルギー収支、適応熱産生からAI食事解析まで：外食派のためのTDEE＆PFCバランス精密調整バイブル</t>
+          <t>2026年YouTube動画推薦アルゴリズムとシリーズ検索完全ガイド：推薦漏れを解消し NLP正規表現ノイズ除去と差分照合 で跨チャンネル追跡を実現する</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6338,7 +6338,7 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>2</v>
@@ -6350,17 +6350,17 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/travel-translator-guide.html</t>
+          <t>ja/tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/travel-translator-guide.html</t>
+          <t>https://gugopro.com/ja/tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>スマホの気まずい手渡しにサヨナラ！180°対面反転UIのデザイン美学・HCI空間心理学と海外旅行会話実践ガイド｜GugoPro 異文化コミュニケーションコラム</t>
+          <t>リダイレクト中 - AI多言語スピーキングチューター | GugoPro</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>スマホの気まずい手渡しにサヨナラ！180°対面反転UIのデザイン美学・HCI空間心理学と海外旅行会話実践ガイド</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6385,14 +6385,14 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -6401,17 +6401,17 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/weight-loss-planner-guide.html</t>
+          <t>ja/tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/weight-loss-planner-guide.html</t>
+          <t>https://gugopro.com/ja/tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>線形減量の幻想からの脱却！Wishnofsky 7700kcal法則の破綻からレジスタンストレーニング期分け・停滞期突破まで：動的減量計画とカロリー赤字完全ガイド｜GugoPro 運動生理学コラム</t>
+          <t>リダイレクト中 - 対面型リアルタイム音声翻訳 | GugoPro</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>線形減量の幻想からの脱却！Wishnofsky 7700kcal法則の破綻からレジスタンストレーニング期分け・停滞期突破まで：動的減量計画とカロリー赤字完全ガイド</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6436,14 +6436,14 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -6452,17 +6452,17 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/youtube-english-listening-and-shadowing-guide.html</t>
+          <t>ja/tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/youtube-english-listening-and-shadowing-guide.html</t>
+          <t>https://gugopro.com/ja/tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイングで母語レベルの聴覚神経回路を構築する完全ガイド｜GugoPro 言語科学コラム</t>
+          <t>リダイレクト中 - AIタロットマスター | GugoPro</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6487,14 +6487,14 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -6503,17 +6503,17 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/youtube-listening-connected-speech-guide.html</t>
+          <t>ja/tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/youtube-listening-connected-speech-guide.html</t>
+          <t>https://gugopro.com/ja/tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイング完全ガイド｜GugoPro 言語科学コラム</t>
+          <t>リダイレクト中 - AI紫微斗数マスター | GugoPro</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6538,14 +6538,14 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -6554,17 +6554,17 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/youtube-sequel-tracker-guide.html</t>
+          <t>ja/tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/youtube-sequel-tracker-guide.html</t>
+          <t>https://gugopro.com/ja/tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026年YouTube動画推薦アルゴリズムとシリーズ検索完全ガイド：推薦漏れを解消しNLP正規表現ノイズ除去と差分照合で跨チャンネル追跡を実現する｜GugoPro ストリーミング研究コラム</t>
+          <t>リダイレクト中 - YouTube続編追跡 | GugoPro</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>2026年YouTube動画推薦アルゴリズムとシリーズ検索完全ガイド：推薦漏れを解消し NLP正規表現ノイズ除去と差分照合 で跨チャンネル追跡を実現する</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6589,14 +6589,14 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/ai/english-speaking-tutor.html</t>
+          <t>ja/tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/ai/english-speaking-tutor.html</t>
+          <t>https://gugopro.com/ja/tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - AI多言語スピーキングチューター | GugoPro</t>
+          <t>リダイレクト中 - YouTube学習プレイヤー | GugoPro</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/ai/realtime-translator.html</t>
+          <t>ja/tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/ai/realtime-translator.html</t>
+          <t>https://gugopro.com/ja/tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - 対面型リアルタイム音声翻訳 | GugoPro</t>
+          <t>リダイレクト中 - AI栄養士 | GugoPro</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/ai/tarot-master.html</t>
+          <t>ja/tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/ai/tarot-master.html</t>
+          <t>https://gugopro.com/ja/tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - AIタロットマスター | GugoPro</t>
+          <t>リダイレクト中 - AI減量コーチ | GugoPro</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -6758,32 +6758,32 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>法律條款</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/ai/ziwei-astrology.html</t>
+          <t>privacy.html</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/ai/ziwei-astrology.html</t>
+          <t>https://gugopro.com/privacy.html</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - AI紫微斗数マスター | GugoPro</t>
+          <t>隱私權政策｜GugoPro</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>隱私權政策</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -6793,14 +6793,14 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K124" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="K124" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -6809,32 +6809,32 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>法律條款</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/ai-media/ai-video-tracker.html</t>
+          <t>terms.html</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/ai-media/ai-video-tracker.html</t>
+          <t>https://gugopro.com/terms.html</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - YouTube続編追跡 | GugoPro</t>
+          <t>服務條款｜GugoPro</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>服務條款</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6844,14 +6844,14 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="K125" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="K125" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/english/l-player-study.html</t>
+          <t>tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/english/l-player-study.html</t>
+          <t>https://gugopro.com/tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - YouTube学習プレイヤー | GugoPro</t>
+          <t>AI多國語言對話導師</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -6895,11 +6895,11 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>1</v>
@@ -6916,27 +6916,27 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/health/tdee-macros-calculator.html</t>
+          <t>tools/ai/gemini-api-quota.html</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/health/tdee-macros-calculator.html</t>
+          <t>https://gugopro.com/tools/ai/gemini-api-quota.html</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - AI栄養士 | GugoPro</t>
+          <t>Gemini API 配額服務導覽｜GugoPro</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>Gemini API 配額服務導覽</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -6946,14 +6946,14 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="K127" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="K127" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -6967,27 +6967,27 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/health/weight-loss-planner.html</t>
+          <t>tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/health/weight-loss-planner.html</t>
+          <t>https://gugopro.com/tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - AI減量コーチ | GugoPro</t>
+          <t>面對面旅遊對話翻譯｜出國旅遊即時翻譯與雙向語音對話｜GugoPro</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>面對面旅遊對話翻譯：出國旅遊即時翻譯與雙向語音對話</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -6997,14 +6997,14 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="K128" s="2" t="n">
         <v>0</v>
-      </c>
-      <c r="K128" s="2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>法律條款</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>privacy.html</t>
+          <t>tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/privacy.html</t>
+          <t>https://gugopro.com/tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>隱私權政策｜GugoPro</t>
+          <t>AI 塔羅大師｜五種塔羅牌陣、提問指南與自我反思 - GugoPro</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>隱私權政策</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7052,10 +7052,10 @@
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -7064,17 +7064,17 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>法律條款</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>terms.html</t>
+          <t>tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/terms.html</t>
+          <t>https://gugopro.com/tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>服務條款｜GugoPro</t>
+          <t>AI 紫微斗數大師｜紫微斗數線上排盤資料整理與十二宮位指南 - GugoPro</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>服務條款</t>
+          <t>把命盤問題，整理成可行動的洞察</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>tools/ai/english-speaking-tutor.html</t>
+          <t>tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/ai/english-speaking-tutor.html</t>
+          <t>https://gugopro.com/tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -7135,29 +7135,29 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>AI多國語言對話導師</t>
+          <t>YouTube 續集與新季追蹤器 - GugoPro</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
+          <t>YouTube 續集與新季追蹤器</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>可見</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
           <t>❌ 缺失</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
       <c r="J131" s="2" t="n">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>tools/ai/gemini-api-quota.html</t>
+          <t>tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/ai/gemini-api-quota.html</t>
+          <t>https://gugopro.com/tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7186,17 +7186,17 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Gemini API 配額服務導覽｜GugoPro</t>
+          <t>【AB English Podcast】Ep.1 自我介紹與日常社交對話 (Mia &amp; Alex)｜L-Player</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Gemini API 配額服務導覽</t>
+          <t>YouTube 影音「聽・寫・口說」多國語言跟讀器</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>可見</t>
+          <t>疑似隱藏</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -7217,17 +7217,17 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>歷史工具</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>tools/ai/nutritionist.html</t>
+          <t>tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/ai/nutritionist.html</t>
+          <t>https://gugopro.com/tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>AI 專屬營養師｜AI 營養諮詢、TDEE 與飲食紀錄工具、免安裝與隱私說明 - GugoPro</t>
+          <t>AI 專屬營養師 | GugoPro</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>1</v>
@@ -7273,12 +7273,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>tools/ai/realtime-translator.html</t>
+          <t>tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/ai/realtime-translator.html</t>
+          <t>https://gugopro.com/tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>面對面旅遊對話翻譯｜出國旅遊即時翻譯與雙向語音對話｜GugoPro</t>
+          <t>AI減肥瘦身教練｜科學減脂與熱量赤字規劃 | GugoPro</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>面對面旅遊對話翻譯：出國旅遊即時翻譯與雙向語音對話</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -7319,17 +7319,17 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>tools/ai/tarot-master.html</t>
+          <t>tools/pdf/pdf-suite.html</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/ai/tarot-master.html</t>
+          <t>https://gugopro.com/tools/pdf/pdf-suite.html</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7339,12 +7339,12 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>AI 塔羅大師｜五種塔羅牌陣、提問指南與自我反思 - GugoPro</t>
+          <t>PDF 全能工作站｜免安裝線上閱讀、合併、分割與標註、零檔案外洩 - GugoPro</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>先選擇要處理的文件</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7354,11 +7354,11 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 未配置（合規）</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="K135" s="2" t="n">
         <v>1</v>
@@ -7370,17 +7370,17 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>實用教學</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>tools/ai/ziwei-astrology.html</t>
+          <t>tools/tutorials/how-to-get-gemini-api-key.html</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/ai/ziwei-astrology.html</t>
+          <t>https://gugopro.com/tools/tutorials/how-to-get-gemini-api-key.html</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>AI 紫微斗數大師｜紫微斗數線上排盤資料整理與十二宮位指南 - GugoPro</t>
+          <t>Gemini API Key 申請教學｜Google Gemini API Key 取得與安全設定教學、免安裝與隱私說明 - GugoPro</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>把命盤問題，整理成可行動的洞察</t>
+          <t>Google Gemini API Key 1 分鐘快速申請步驟</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>1</v>
@@ -7421,32 +7421,32 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>tools/ai-media/ai-video-tracker.html</t>
+          <t>tools/tw-market/taiwan-pair-trading.html</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/ai-media/ai-video-tracker.html</t>
+          <t>https://gugopro.com/tools/tw-market/taiwan-pair-trading.html</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>zh-TW</t>
+          <t>zh-Hant-TW</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>YouTube 續集與新季追蹤器 - GugoPro</t>
+          <t>Taiwan Pair Trading 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>YouTube 續集與新季追蹤器</t>
+          <t>台灣股票與期貨 配對交易掃描工作站</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7456,885 +7456,18 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>❌ 未配置（合規）</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="K137" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>tools/compound-interest.html</t>
-        </is>
-      </c>
-      <c r="D138" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/compound-interest.html</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>Compound Interest 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>進階複利與退休目標規劃計算機</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I138" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J138" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="K138" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>tools/english/l-player-study.html</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/english/l-player-study.html</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>【AB English Podcast】Ep.1 自我介紹與日常社交對話 (Mia &amp; Alex)｜L-Player</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>YouTube 影音「聽・寫・口說」多國語言跟讀器</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>疑似隱藏</t>
-        </is>
-      </c>
-      <c r="I139" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J139" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="K139" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>tools/etf-dividend-calculator.html</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/etf-dividend-calculator.html</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>zh-Hant</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>Etf Dividend Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>把配息拆成一條， 看得懂的現金流曲線。</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J140" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="K140" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
-        <v>140</v>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>tools/finance/kelly-criterion-calculator.html</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/finance/kelly-criterion-calculator.html</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>Kelly Criterion Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>凱利公式與資金控管模擬器</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J141" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="K141" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="n">
-        <v>141</v>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>tools/finance/sports-hedging-calculator.html</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/finance/sports-hedging-calculator.html</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>Sports Hedging Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>運動彩券賠率換算與套利對沖計算器</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J142" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="K142" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="n">
-        <v>142</v>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>tools/games/mahjong-waits-calculator.html</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/games/mahjong-waits-calculator.html</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>zh-Hant</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>Mahjong Waits Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>麻將聽牌張數與進張勝率計算器</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J143" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="K143" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="n">
-        <v>143</v>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>tools/games/poker-odds-calculator.html</t>
-        </is>
-      </c>
-      <c r="D144" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/games/poker-odds-calculator.html</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>Poker Odds Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>德州撲克即時勝率計算器 Texas Hold'em Odds Calculator</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I144" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J144" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="K144" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="n">
-        <v>144</v>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>tools/gaming/gacha-odds-calculator.html</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/gaming/gacha-odds-calculator.html</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>zh-Hant</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>Gacha Odds Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>Gacha Odds &amp; Pity Simulator v5</t>
-        </is>
-      </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J145" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="K145" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="n">
-        <v>145</v>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>tools/health/tdee-macros-calculator.html</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/health/tdee-macros-calculator.html</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>AI 專屬營養師 | GugoPro</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I146" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J146" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="K146" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>tools/health/weight-loss-planner.html</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/health/weight-loss-planner.html</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>AI減肥瘦身教練｜科學減脂與熱量赤字規劃 | GugoPro</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J147" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="K147" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="n">
-        <v>147</v>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>tools/pdf/pdf-suite.html</t>
-        </is>
-      </c>
-      <c r="D148" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/pdf/pdf-suite.html</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>PDF 全能工作站｜免安裝線上閱讀、合併、分割與標註、零檔案外洩 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="inlineStr">
-        <is>
-          <t>先選擇要處理的文件</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="J148" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="K148" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="n">
-        <v>148</v>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>tools/poker/poker-odds-calculator.html</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/poker/poker-odds-calculator.html</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>Poker Odds Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>德州撲克即時勝率計算器 Texas Hold'em Odds Calculator</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="K149" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="n">
-        <v>149</v>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>tools/realestate-amortization.html</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/realestate-amortization.html</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>zh-Hant</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>Realestate Amortization 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>房貸本息攤還、利息與提前還款工具</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J150" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="K150" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>tools/risk-reward-calculator.html</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/risk-reward-calculator.html</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>zh-Hant</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>Risk Reward Calculator 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>先看即時價格，再決定風險。</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I151" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J151" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="K151" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="n">
-        <v>151</v>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>tools/tradingview-guide.html</t>
-        </is>
-      </c>
-      <c r="D152" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/tradingview-guide.html</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>Tradingview Guide 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>全球最強圖表工具 TradingView</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="K152" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="n">
-        <v>152</v>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>tools/tutorials/how-to-get-gemini-api-key.html</t>
-        </is>
-      </c>
-      <c r="D153" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/tutorials/how-to-get-gemini-api-key.html</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>Gemini API Key 申請教學｜Google Gemini API Key 取得與安全設定教學、免安裝與隱私說明 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>Google Gemini API Key 1 分鐘快速申請步驟</t>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J153" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="K153" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="n">
-        <v>153</v>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>tools/tw-market/taiwan-pair-trading.html</t>
-        </is>
-      </c>
-      <c r="D154" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/tw-market/taiwan-pair-trading.html</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>zh-Hant-TW</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>Taiwan Pair Trading 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>台灣股票與期貨 配對交易掃描工作站</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J154" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="K154" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K154"/>
+  <autoFilter ref="A1:K137"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -8472,27 +7605,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId153"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId154"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId137"/>
   </tableParts>
 </worksheet>
 </file>
@@ -8503,7 +7619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -8529,7 +7645,7 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>153</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3">
@@ -8539,7 +7655,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -8559,77 +7675,87 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>實用教學</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>法律條款</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>法律條款</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>缺少 AdSense 頁面</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H1 缺失頁面</t>
+          <t>缺少 AdSense 頁面</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H1 疑似隱藏頁面</t>
+          <t>H1 缺失頁面</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>H1 疑似隱藏頁面</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>工具目標連結數（每頁去重）</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>185</v>
+      <c r="B13" s="5" t="n">
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/seo_inventory_report.xlsx
+++ b/seo_inventory_report.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SEO AdSense 盤點'!$A$1:$K$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SEO AdSense 盤點'!$A$1:$K$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -157,8 +157,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SEOInventory" displayName="SEOInventory" ref="A1:K137" headerRowCount="1">
-  <autoFilter ref="A1:K137"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SEOInventory" displayName="SEOInventory" ref="A1:K96" headerRowCount="1">
+  <autoFilter ref="A1:K96"/>
   <tableColumns count="11">
     <tableColumn id="1" name="編號"/>
     <tableColumn id="2" name="頁面分類"/>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K137"/>
+  <dimension ref="A1:K96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -855,12 +855,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>articles/english-intro-break-the-ice.html</t>
+          <t>articles/fatty-liver-and-mediterranean-diet-guide.html</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/english-intro-break-the-ice.html</t>
+          <t>https://gugopro.com/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>看 YouTube 學英文為何總是無效？結合音韻知覺理論、Levenshtein 聽寫差量比對與影子跟讀（Shadowing）打造母語聽覺神經迴路全指南｜GugoPro 語言科學專欄</t>
+          <t>減醣飲食與地中海飲食怎麼吃？從逆轉脂肪肝、內臟脂肪燃燒到三大營養素黃金配比：外食族健康長壽實戰手冊｜GugoPro 肝臟代謝專欄</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>看 YouTube 學英文為何總是無效？結合音韻知覺理論、 Levenshtein 聽寫差量比對與影子跟讀（Shadowing） 打造母語聽覺神經迴路全指南</t>
+          <t>減醣飲食與地中海飲食怎麼吃？從逆轉脂肪肝、內臟脂肪燃燒到三大營養素黃金配比：外食族健康長壽實戰手冊</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>2</v>
@@ -906,12 +906,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>articles/fatty-liver-and-mediterranean-diet-guide.html</t>
+          <t>articles/gemini-api-free-tier-and-developer-guide.html</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
+          <t>https://gugopro.com/articles/gemini-api-free-tier-and-developer-guide.html</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>減醣飲食與地中海飲食怎麼吃？從逆轉脂肪肝、內臟脂肪燃燒到三大營養素黃金配比：外食族健康長壽實戰手冊｜GugoPro 肝臟代謝專欄</t>
+          <t>2026 終極開發者手冊：利用 Google Gemini 官方免費 API 打造零成本商用級應用之架構設計與故障排除全指南｜GugoPro 雲端系統專欄</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>減醣飲食與地中海飲食怎麼吃？從逆轉脂肪肝、內臟脂肪燃燒到三大營養素黃金配比：外食族健康長壽實戰手冊</t>
+          <t>2026 終極開發者手冊：利用 Google Gemini 官方免費 API 打造零成本商用級應用之架構設計與故障排除全指南</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>207</v>
+        <v>260</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>2</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>articles/gemini-api-free-tier-and-developer-guide.html</t>
+          <t>articles/how-to-master-tarot-guide.html</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/gemini-api-free-tier-and-developer-guide.html</t>
+          <t>https://gugopro.com/articles/how-to-master-tarot-guide.html</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026 終極開發者手冊：利用 Google Gemini 官方免費 API 打造零成本商用級應用之架構設計與故障排除全指南｜GugoPro 雲端系統專欄</t>
+          <t>如何成為塔羅牌大師？從 78 張牌義生吞活剝到「直覺流動解牌」：結合古典符號學、敘事心理學與 AI 協同實戰刻意練習全指南｜GugoPro 決策科學專欄</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026 終極開發者手冊：利用 Google Gemini 官方免費 API 打造零成本商用級應用之架構設計與故障排除全指南</t>
+          <t>如何成為塔羅牌大師？從 78 張牌義生吞活剝到「直覺流動解牌」：結合古典符號學、敘事心理學與 AI 協同實戰刻意練習全指南</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>260</v>
+        <v>159</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>2</v>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>articles/how-to-master-tarot-guide.html</t>
+          <t>articles/how-to-master-ziwei-guide.html</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/how-to-master-tarot-guide.html</t>
+          <t>https://gugopro.com/articles/how-to-master-ziwei-guide.html</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>如何成為塔羅牌大師？從 78 張牌義生吞活剝到「直覺流動解牌」：結合古典符號學、敘事心理學與 AI 協同實戰刻意練習全指南｜GugoPro 決策科學專欄</t>
+          <t>如何成為紫微斗數大師？從死背百顆星曜到「動態格局解盤」：結合文化符號學、系統動力學與 AI 協同實戰刻意練習全指南｜GugoPro 決策科學專欄</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>如何成為塔羅牌大師？從 78 張牌義生吞活剝到「直覺流動解牌」：結合古典符號學、敘事心理學與 AI 協同實戰刻意練習全指南</t>
+          <t>如何成為紫微斗數大師？從死背百顆星曜到「動態格局解盤」：結合文化符號學、系統動力學與 AI 協同實戰刻意練習全指南</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>159</v>
+        <v>207</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>2</v>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>articles/how-to-master-ziwei-guide.html</t>
+          <t>articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/how-to-master-ziwei-guide.html</t>
+          <t>https://gugopro.com/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>如何成為紫微斗數大師？從死背百顆星曜到「動態格局解盤」：結合文化符號學、系統動力學與 AI 協同實戰刻意練習全指南｜GugoPro 決策科學專欄</t>
+          <t>168 斷食真的比算熱量有效嗎？從自噬反應、胰島素假說到熱量赤字真相：打破越斷越肥的復胖陷阱｜GugoPro 減脂代謝專欄</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>如何成為紫微斗數大師？從死背百顆星曜到「動態格局解盤」：結合文化符號學、系統動力學與 AI 協同實戰刻意練習全指南</t>
+          <t>168 斷食真的比算熱量有效嗎？從自噬反應、胰島素假說到熱量赤字真相：打破越斷越肥的復胖陷阱</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>207</v>
+        <v>265</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>2</v>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
+          <t>articles/modern-ziwei-guide.html</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
+          <t>https://gugopro.com/articles/modern-ziwei-guide.html</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>168 斷食真的比算熱量有效嗎？從自噬反應、胰島素假說到熱量赤字真相：打破越斷越肥的復胖陷阱｜GugoPro 減脂代謝專欄</t>
+          <t>告別宿命論與玄學恐嚇！用現代心理學重構紫微斗數：從十二宮位、四化動態到 AI 決策反思模型｜GugoPro 決策科學專欄</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>168 斷食真的比算熱量有效嗎？從自噬反應、胰島素假說到熱量赤字真相：打破越斷越肥的復胖陷阱</t>
+          <t>告別宿命論與玄學恐嚇！用現代心理學重構紫微斗數：從十二宮位、四化動態到 AI 決策反思模型</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>265</v>
+        <v>140</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>2</v>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>articles/modern-ziwei-guide.html</t>
+          <t>articles/shadowing-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/modern-ziwei-guide.html</t>
+          <t>https://gugopro.com/articles/shadowing-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>告別宿命論與玄學恐嚇！用現代心理學重構紫微斗數：從十二宮位、四化動態到 AI 決策反思模型｜GugoPro 決策科學專欄</t>
+          <t>擺脫「啞巴英語」的科學自學法：結合影子跟讀（Shadowing）、CEFR 脈絡輸出與 AI 導師的高效閉環｜GugoPro 語言學習專欄</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>告別宿命論與玄學恐嚇！用現代心理學重構紫微斗數：從十二宮位、四化動態到 AI 決策反思模型</t>
+          <t>擺脫「啞巴英語」的科學自學法：結合影子跟讀（Shadowing）、CEFR 脈絡輸出與 AI 導師的高效閉環</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>2</v>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>articles/shadowing-with-ai-tutor.html</t>
+          <t>articles/tarot-decision-framework.html</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/shadowing-with-ai-tutor.html</t>
+          <t>https://gugopro.com/articles/tarot-decision-framework.html</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>擺脫「啞巴英語」的科學自學法：結合影子跟讀（Shadowing）、CEFR 脈絡輸出與 AI 導師的高效閉環｜GugoPro 語言學習專欄</t>
+          <t>告別迷信宿命論！從榮格「原型」心理學、共時性到 AI 塔羅：拆解職涯二選一與感情焦慮的結構化決策模型｜GugoPro 決策科學專欄</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>擺脫「啞巴英語」的科學自學法：結合影子跟讀（Shadowing）、CEFR 脈絡輸出與 AI 導師的高效閉環</t>
+          <t>告別迷信宿命論！從榮格「原型」心理學、共時性到 AI 塔羅：拆解職涯二選一與感情焦慮的結構化決策模型</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>2</v>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>articles/tarot-decision-framework.html</t>
+          <t>articles/tblt-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/tarot-decision-framework.html</t>
+          <t>https://gugopro.com/articles/tblt-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>告別迷信宿命論！從榮格「原型」心理學、共時性到 AI 塔羅：拆解職涯二選一與感情焦慮的結構化決策模型｜GugoPro 決策科學專欄</t>
+          <t>告別死記硬背！結合任務型教學法（TBLT）、Robinson 認知假說與 AI 導師的高效口說實戰指南｜GugoPro 語言學習專欄</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>告別迷信宿命論！從榮格「原型」心理學、共時性到 AI 塔羅：拆解職涯二選一與感情焦慮的結構化決策模型</t>
+          <t>告別死記硬背！結合任務型教學法（TBLT）、Robinson 認知假說與 AI 導師的高效口說實戰指南</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>2</v>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>articles/tblt-with-ai-tutor.html</t>
+          <t>articles/tdee-and-macros-guide.html</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/tblt-with-ai-tutor.html</t>
+          <t>https://gugopro.com/articles/tdee-and-macros-guide.html</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>告別死記硬背！結合任務型教學法（TBLT）、Robinson 認知假說與 AI 導師的高效口說實戰指南｜GugoPro 語言學習專欄</t>
+          <t>告別無效節食與溜溜球效應！從能量平衡熱力學、自適應產熱到 AI 拍餐估算：外食族 TDEE 與三大營養素精準調控全指南｜GugoPro 代謝健康專欄</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>告別死記硬背！結合任務型教學法（TBLT）、Robinson 認知假說與 AI 導師的高效口說實戰指南</t>
+          <t>告別無效節食與溜溜球效應！從能量平衡熱力學、自適應產熱到 AI 拍餐估算：外食族 TDEE 與三大營養素精準調控全指南</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>2</v>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>articles/tdee-and-macros-guide.html</t>
+          <t>articles/travel-translator-guide.html</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/tdee-and-macros-guide.html</t>
+          <t>https://gugopro.com/articles/travel-translator-guide.html</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>告別無效節食與溜溜球效應！從能量平衡熱力學、自適應產熱到 AI 拍餐估算：外食族 TDEE 與三大營養素精準調控全指南｜GugoPro 代謝健康專欄</t>
+          <t>告別尷尬遞手機！180° 面對面翻轉介面的設計美學、人機互動（HCI）空間心理學與出國溝通實戰指南｜GugoPro 跨文化專欄</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>告別無效節食與溜溜球效應！從能量平衡熱力學、自適應產熱到 AI 拍餐估算：外食族 TDEE 與三大營養素精準調控全指南</t>
+          <t>告別尷尬遞手機！180° 面對面翻轉介面的設計美學、人機互動（HCI）空間心理學與出國溝通實戰指南</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>2</v>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>articles/travel-translator-guide.html</t>
+          <t>articles/weight-loss-planner-guide.html</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/travel-translator-guide.html</t>
+          <t>https://gugopro.com/articles/weight-loss-planner-guide.html</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>告別尷尬遞手機！180° 面對面翻轉介面的設計美學、人機互動（HCI）空間心理學與出國溝通實戰指南｜GugoPro 跨文化專欄</t>
+          <t>告別線性減重迷思！從 Wishnofsky 7700大卡法則失真、阻力訓練期程化到停滯期突破：動態減脂計畫與熱量赤字全指南｜GugoPro 運動生理學專欄</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>告別尷尬遞手機！180° 面對面翻轉介面的設計美學、人機互動（HCI）空間心理學與出國溝通實戰指南</t>
+          <t>告別線性減重迷思！從 Wishnofsky 7700大卡法則失真、阻力訓練期程化到停滯期突破：動態減脂計畫與熱量赤字全指南</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>2</v>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>articles/weight-loss-planner-guide.html</t>
+          <t>articles/youtube-english-listening-and-shadowing-guide.html</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/weight-loss-planner-guide.html</t>
+          <t>https://gugopro.com/articles/youtube-english-listening-and-shadowing-guide.html</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>告別線性減重迷思！從 Wishnofsky 7700大卡法則失真、阻力訓練期程化到停滯期突破：動態減脂計畫與熱量赤字全指南｜GugoPro 運動生理學專欄</t>
+          <t>解鎖 YouTube 雙語精聽與影子跟讀：L-Player 零摩擦學習系統操作全書與神經聽覺重塑指南｜GugoPro 語言科學專欄</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>告別線性減重迷思！從 Wishnofsky 7700大卡法則失真、阻力訓練期程化到停滯期突破：動態減脂計畫與熱量赤字全指南</t>
+          <t>解鎖 YouTube 雙語精聽與影子跟讀： L-Player 零摩擦學習系統操作全書與神經聽覺重塑指南</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>200</v>
+        <v>244</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>2</v>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>articles/youtube-english-listening-and-shadowing-guide.html</t>
+          <t>articles/youtube-listening-connected-speech-guide.html</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/youtube-english-listening-and-shadowing-guide.html</t>
+          <t>https://gugopro.com/articles/youtube-listening-connected-speech-guide.html</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>解鎖 YouTube 雙語精聽與影子跟讀：L-Player 零摩擦學習系統操作全書與神經聽覺重塑指南｜GugoPro 語言科學專欄</t>
+          <t>看 YouTube 學英文為何總是無效？結合音韻知覺理論、Levenshtein 聽寫差量比對與影子跟讀（Shadowing）打造母語聽覺神經迴路全指南｜GugoPro 語言科學專欄</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>解鎖 YouTube 雙語精聽與影子跟讀： L-Player 零摩擦學習系統操作全書與神經聽覺重塑指南</t>
+          <t>看 YouTube 學英文為何總是無效？結合音韻知覺理論、 Levenshtein 聽寫差量比對與影子跟讀（Shadowing） 打造母語聽覺神經迴路全指南</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>2</v>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>articles/youtube-listening-connected-speech-guide.html</t>
+          <t>articles/youtube-sequel-tracker-guide.html</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/youtube-listening-connected-speech-guide.html</t>
+          <t>https://gugopro.com/articles/youtube-sequel-tracker-guide.html</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>看 YouTube 學英文為何總是無效？結合音韻知覺理論、Levenshtein 聽寫差量比對與影子跟讀（Shadowing）打造母語聽覺神經迴路全指南｜GugoPro 語言科學專欄</t>
+          <t>2026 YouTube 影音演算法與連載檢索全指南：如何破解推薦漏片迷思、利用 NLP 正則去噪與差量比對打造跨頻道追劇閉環｜GugoPro 串流媒體研究專欄</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>看 YouTube 學英文為何總是無效？結合音韻知覺理論、 Levenshtein 聽寫差量比對與影子跟讀（Shadowing） 打造母語聽覺神經迴路全指南</t>
+          <t>2026 YouTube 影音演算法與連載檢索全指南：如何破解推薦漏片迷思、利用 NLP 正則去噪與差量比對 打造跨頻道追劇閉環</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>2</v>
@@ -1615,17 +1615,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>法律條款</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>articles/youtube-sequel-tracker-guide.html</t>
+          <t>contact.html</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/articles/youtube-sequel-tracker-guide.html</t>
+          <t>https://gugopro.com/contact.html</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1635,12 +1635,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026 YouTube 影音演算法與連載檢索全指南：如何破解推薦漏片迷思、利用 NLP 正則去噪與差量比對打造跨頻道追劇閉環｜GugoPro 串流媒體研究專欄</t>
+          <t>聯絡我們 | GugoPro 官方</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2026 YouTube 影音演算法與連載檢索全指南：如何破解推薦漏片迷思、利用 NLP 正則去噪與差量比對 打造跨頻道追劇閉環</t>
+          <t>聯絡我們</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>199</v>
+        <v>62</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>contact.html</t>
+          <t>disclaimer.html</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/contact.html</t>
+          <t>https://gugopro.com/disclaimer.html</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>聯絡我們 | GugoPro 官方</t>
+          <t>免責聲明｜GugoPro 工具與 AI 服務使用限制</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>聯絡我們</t>
+          <t>GugoPro 免責聲明</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1717,32 +1717,32 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>法律條款</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>disclaimer.html</t>
+          <t>en/articles/affective-filter-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/disclaimer.html</t>
+          <t>https://gugopro.com/en/articles/affective-filter-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>zh-TW</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>免責聲明｜GugoPro 工具與 AI 服務使用限制</t>
+          <t>Overcoming the Fear of Speaking: Krashen's Affective Filter, Foreign Language Anxiety (FLA), and Zero-Pressure AI Tutoring | GugoPro Language Science</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>GugoPro 免責聲明</t>
+          <t>Overcoming the Fear of Speaking: Krashen's Affective Filter, Foreign Language Anxiety (FLA), and Zero-Pressure AI Tutoring</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>57</v>
+        <v>455</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>en/articles/affective-filter-with-ai-tutor.html</t>
+          <t>en/articles/amazon-ai-product-research-guide.html</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/affective-filter-with-ai-tutor.html</t>
+          <t>https://gugopro.com/en/articles/amazon-ai-product-research-guide.html</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Fear of Speaking: Krashen's Affective Filter, Foreign Language Anxiety (FLA), and Zero-Pressure AI Tutoring | GugoPro Language Science</t>
+          <t>2026 Cross-Border E-Commerce &amp; Global Sourcing Master Guide: Leveraging AI Semantic Reverse Engineering for Amazon Product Research, Negative Review Mining, and Listing Matrix Architecture | GugoPro Strategy Column</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Fear of Speaking: Krashen's Affective Filter, Foreign Language Anxiety (FLA), and Zero-Pressure AI Tutoring</t>
+          <t>2026 Cross-Border E-Commerce &amp; Global Sourcing Master Guide: Leveraging AI Semantic Reverse Engineering for Amazon Product Research, Negative Review Mining, and Listing Keyword Matrix Architecture</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>en/articles/amazon-ai-product-research-guide.html</t>
+          <t>en/articles/carb-cycling-and-home-workout-guide.html</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/amazon-ai-product-research-guide.html</t>
+          <t>https://gugopro.com/en/articles/carb-cycling-and-home-workout-guide.html</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026 Cross-Border E-Commerce &amp; Global Sourcing Master Guide: Leveraging AI Semantic Reverse Engineering for Amazon Product Research, Negative Review Mining, and Listing Matrix Architecture | GugoPro Strategy Column</t>
+          <t>How to Master Carb Cycling for Maximum Fat Loss: High/Low Carb Biochemistry, Home Bodyweight Workout Splits, and Preserving Muscle Mass | GugoPro Exercise Physiology Column</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2026 Cross-Border E-Commerce &amp; Global Sourcing Master Guide: Leveraging AI Semantic Reverse Engineering for Amazon Product Research, Negative Review Mining, and Listing Keyword Matrix Architecture</t>
+          <t>How to Master Carb Cycling for Maximum Fat Loss: High/Low Carb Biochemistry, Home Bodyweight Workout Splits, and Preserving Muscle Mass</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
         <v>452</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>en/articles/carb-cycling-and-home-workout-guide.html</t>
+          <t>en/articles/diabetes-and-insulin-resistance-guide.html</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/carb-cycling-and-home-workout-guide.html</t>
+          <t>https://gugopro.com/en/articles/diabetes-and-insulin-resistance-guide.html</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>How to Master Carb Cycling for Maximum Fat Loss: High/Low Carb Biochemistry, Home Bodyweight Workout Splits, and Preserving Muscle Mass | GugoPro Exercise Physiology Column</t>
+          <t>What to Eat for Prediabetes and Insulin Resistance? From GI/GL and Carb Counting to AI Meal Tracking: The Definitive Macronutrient Guide to Ending Glucose Spikes | GugoPro Metabolic Science Column</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>How to Master Carb Cycling for Maximum Fat Loss: High/Low Carb Biochemistry, Home Bodyweight Workout Splits, and Preserving Muscle Mass</t>
+          <t>What to Eat for Prediabetes and Insulin Resistance? From GI/GL and Carb Counting to AI Meal Tracking: The Definitive Macronutrient Guide to Ending Glucose Spikes</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>2</v>
@@ -1926,12 +1926,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>en/articles/diabetes-and-insulin-resistance-guide.html</t>
+          <t>en/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/diabetes-and-insulin-resistance-guide.html</t>
+          <t>https://gugopro.com/en/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>What to Eat for Prediabetes and Insulin Resistance? From GI/GL and Carb Counting to AI Meal Tracking: The Definitive Macronutrient Guide to Ending Glucose Spikes | GugoPro Metabolic Science Column</t>
+          <t>What to Eat for Fatty Liver: Low-Carb vs. Mediterranean Diet? From Reversing Hepatic Steatosis &amp; Visceral Fat to Optimal Macronutrient Ratios: The Dining-Out Longevity Handbook | GugoPro Liver Metabolism Column</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>What to Eat for Prediabetes and Insulin Resistance? From GI/GL and Carb Counting to AI Meal Tracking: The Definitive Macronutrient Guide to Ending Glucose Spikes</t>
+          <t>What to Eat for Fatty Liver: Low-Carb vs. Mediterranean Diet? From Reversing Hepatic Steatosis &amp; Visceral Fat to Optimal Macronutrient Ratios: The Dining-Out Longevity Handbook</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>2</v>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>en/articles/english-intro-break-the-ice.html</t>
+          <t>en/articles/gemini-api-free-tier-and-developer-guide.html</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/english-intro-break-the-ice.html</t>
+          <t>https://gugopro.com/en/articles/gemini-api-free-tier-and-developer-guide.html</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Why Watching YouTube Fails for English Learning: Speech Perception, Levenshtein Dictation Diff, and Shadowing Guide | GugoPro Language Science</t>
+          <t>2026 Developer Blueprint: Building Zero-Cost Commercial-Grade Apps with Google Gemini Free API &amp; Comprehensive Error Troubleshooting Guide | GugoPro Cloud Systems Column</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Why Watching YouTube Fails for English Learning: Building Native Auditory Circuits via Speech Perception, Levenshtein Dictation Diff, and Shadowing</t>
+          <t>2026 Developer Blueprint: Building Zero-Cost Commercial-Grade Apps with Google Gemini Free API &amp; Comprehensive Error Troubleshooting Guide</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>2</v>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>en/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
+          <t>en/articles/how-to-master-tarot-guide.html</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
+          <t>https://gugopro.com/en/articles/how-to-master-tarot-guide.html</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>What to Eat for Fatty Liver: Low-Carb vs. Mediterranean Diet? From Reversing Hepatic Steatosis &amp; Visceral Fat to Optimal Macronutrient Ratios: The Dining-Out Longevity Handbook | GugoPro Liver Metabolism Column</t>
+          <t>How to Become a Tarot Master? From Rote Memorization to Intuitive Flow Reading: A Deliberate Practice Guide Combining Classical Semiotics, Narrative Psychology, and AI Collaboration | GugoPro Decision Science Column</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>What to Eat for Fatty Liver: Low-Carb vs. Mediterranean Diet? From Reversing Hepatic Steatosis &amp; Visceral Fat to Optimal Macronutrient Ratios: The Dining-Out Longevity Handbook</t>
+          <t>How to Become a Tarot Master? From Rote Memorization to "Intuitive Flow Reading": A Comprehensive Deliberate Practice Guide Combining Classical Semiotics, Narrative Psychology, and AI Collaboration</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>473</v>
+        <v>384</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>2</v>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>en/articles/gemini-api-free-tier-and-developer-guide.html</t>
+          <t>en/articles/how-to-master-ziwei-guide.html</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/gemini-api-free-tier-and-developer-guide.html</t>
+          <t>https://gugopro.com/en/articles/how-to-master-ziwei-guide.html</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2094,12 +2094,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026 Developer Blueprint: Building Zero-Cost Commercial-Grade Apps with Google Gemini Free API &amp; Comprehensive Error Troubleshooting Guide | GugoPro Cloud Systems Column</t>
+          <t>How to Become a Ziwei Astrology Master? From Rote Memorization to Dynamic Pattern Reading: A Deliberate Practice Guide Combining Cultural Semiotics, System Dynamics, and AI Collaboration | GugoPro Decision Science Column</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2026 Developer Blueprint: Building Zero-Cost Commercial-Grade Apps with Google Gemini Free API &amp; Comprehensive Error Troubleshooting Guide</t>
+          <t>How to Become a Ziwei Astrology Master? From Rote Memorization of 108 Stars to "Dynamic Pattern Reading": A Deliberate Practice Guide Combining Cultural Semiotics, System Dynamics, and AI Collaboration</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>394</v>
+        <v>497</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>2</v>
@@ -2130,12 +2130,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>en/articles/how-to-master-tarot-guide.html</t>
+          <t>en/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/how-to-master-tarot-guide.html</t>
+          <t>https://gugopro.com/en/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Tarot Master? From Rote Memorization to Intuitive Flow Reading: A Deliberate Practice Guide Combining Classical Semiotics, Narrative Psychology, and AI Collaboration | GugoPro Decision Science Column</t>
+          <t>Is 16:8 Intermittent Fasting Really Better Than Counting Calories? From Autophagy and the Insulin Hypothesis to Caloric Deficit Realities: Escaping the Fasting Rebound Trap | GugoPro Metabolic Science Column</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Tarot Master? From Rote Memorization to "Intuitive Flow Reading": A Comprehensive Deliberate Practice Guide Combining Classical Semiotics, Narrative Psychology, and AI Collaboration</t>
+          <t>Is 16:8 Intermittent Fasting Really Better Than Counting Calories? From Autophagy and the Insulin Hypothesis to Caloric Deficit Realities: Escaping the Fasting Rebound Trap</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>384</v>
+        <v>643</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>2</v>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>en/articles/how-to-master-ziwei-guide.html</t>
+          <t>en/articles/modern-ziwei-guide.html</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/how-to-master-ziwei-guide.html</t>
+          <t>https://gugopro.com/en/articles/modern-ziwei-guide.html</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2196,12 +2196,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Ziwei Astrology Master? From Rote Memorization to Dynamic Pattern Reading: A Deliberate Practice Guide Combining Cultural Semiotics, System Dynamics, and AI Collaboration | GugoPro Decision Science Column</t>
+          <t>Farewell to Fatalism and Esoteric Intimidation! Reconstructing Ziwei Astrology with Modern Psychology: From Twelve Palaces and Si-Hua Dynamics to AI Decision Reflection Models | GugoPro Decision Science Column</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Ziwei Astrology Master? From Rote Memorization of 108 Stars to "Dynamic Pattern Reading": A Deliberate Practice Guide Combining Cultural Semiotics, System Dynamics, and AI Collaboration</t>
+          <t>Farewell to Fatalism and Esoteric Intimidation! Reconstructing Ziwei Astrology with Modern Psychology: From Twelve Palaces and Si-Hua Dynamics to AI Decision Reflection Models</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>497</v>
+        <v>539</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>2</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>en/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
+          <t>en/articles/shadowing-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
+          <t>https://gugopro.com/en/articles/shadowing-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Is 16:8 Intermittent Fasting Really Better Than Counting Calories? From Autophagy and the Insulin Hypothesis to Caloric Deficit Realities: Escaping the Fasting Rebound Trap | GugoPro Metabolic Science Column</t>
+          <t>Overcoming 'Mute English': Shadowing, CEFR Output, and AI Tutoring for Fluent Speaking | GugoPro Language Science</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Is 16:8 Intermittent Fasting Really Better Than Counting Calories? From Autophagy and the Insulin Hypothesis to Caloric Deficit Realities: Escaping the Fasting Rebound Trap</t>
+          <t>Overcoming 'Mute English': Shadowing, CEFR Output, and AI Tutoring for Fluent Speaking</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>643</v>
+        <v>281</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>2</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/01-compound-interest-guide.html</t>
+          <t>en/articles/tarot-decision-framework.html</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/01-compound-interest-guide.html</t>
+          <t>https://gugopro.com/en/articles/tarot-decision-framework.html</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Compounding and time value of money: how to build your first financial system from a balance sheet? | GugoPro Academy</t>
+          <t>Farewell to Fatalism: From Jungian Archetypal Psychology and Synchronicity to AI Tarot: Deconstructing Career Dilemmas and Relationship Anxiety via Structured Decision Models | GugoPro Decision Science Column</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Compounding and time value of money: how to build your first financial system from a balance sheet?</t>
+          <t>Farewell to Fatalism: From Jungian Archetypal Psychology and Synchronicity to AI Tarot: Deconstructing Career Dilemmas and Relationship Anxiety via Structured Decision Models</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>164</v>
+        <v>496</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/02-etf-investing-bible.html</t>
+          <t>en/articles/tblt-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/02-etf-investing-bible.html</t>
+          <t>https://gugopro.com/en/articles/tblt-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Index Investing Bible: Taiwan 0050/006208 vs US VTI/VOO/QQQ — complete analysis | GugoPro Academy</t>
+          <t>Beyond Rote Memorization: Task-Based Language Teaching (TBLT), Robinson's Cognition Hypothesis, and High-Impact Speaking with AI | GugoPro Language Science</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Index Investing Bible: Taiwan 0050/006208 vs US VTI/VOO/QQQ — complete analysis</t>
+          <t>Beyond Rote Memorization: Task-Based Language Teaching (TBLT), Robinson's Cognition Hypothesis, and High-Impact Speaking with AI</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>171</v>
+        <v>522</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/03-asset-allocation-rebalancing.html</t>
+          <t>en/articles/tdee-and-macros-guide.html</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/03-asset-allocation-rebalancing.html</t>
+          <t>https://gugopro.com/en/articles/tdee-and-macros-guide.html</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Asset allocation and dynamic rebalancing: from target weights to trading frictions｜GugoPro Academy</t>
+          <t>Defeat Chronic Dieting &amp; Yo-Yo Rebound: The Complete Scientific Guide to TDEE, Adaptive Thermogenesis &amp; Macronutrient Control for Dining Out | GugoPro Metabolic Health Column</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Asset allocation and dynamic rebalancing: Turn target weights into actionable decision rules.</t>
+          <t>Defeat Chronic Dieting &amp; Yo-Yo Rebound: The Complete Scientific Guide to TDEE, Adaptive Thermogenesis &amp; Macronutrient Control for Dining Out</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>217</v>
+        <v>543</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/04-brokerage-comparison.html</t>
+          <t>en/articles/travel-translator-guide.html</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/04-brokerage-comparison.html</t>
+          <t>https://gugopro.com/en/articles/travel-translator-guide.html</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Complete guide to opening a US brokerage account: Taiwan sub-account vs. overseas brokers | GugoPro Academy</t>
+          <t>Say Goodbye to Awkward Phone-Passing! 180° Face-to-Face Flipped UI Design, HCI Spatial Psychology, and Practical Travel Communication Guide | GugoPro Cross-Cultural Column</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Complete guide to opening a US brokerage account: Taiwan sub-account vs. overseas brokers (Firstrade, IB, Schwab) comparison</t>
+          <t>Say Goodbye to Awkward Phone-Passing! 180° Face-to-Face Flipped UI Design, HCI Spatial Psychology, and Practical Travel Communication Guide</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>169</v>
+        <v>501</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/05-fundamental-valuation-metrics.html</t>
+          <t>en/articles/weight-loss-planner-guide.html</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/05-fundamental-valuation-metrics.html</t>
+          <t>https://gugopro.com/en/articles/weight-loss-planner-guide.html</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Fundamental valuation metrics: P/E, P/B and ROE | GugoPro Academy</t>
+          <t>Beyond Linear Weight Loss Myths: From Wishnofsky's 7,700 kcal Rule Flaws to Resistance Periodization and Plateau Breakthroughs: The Definitive Dynamic Fat Loss &amp; Caloric Deficit Guide | GugoPro Exercise Physiology Column</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Fundamental valuation metrics: correctly reading P/E, P/B and ROE</t>
+          <t>Beyond Linear Weight Loss Myths: From Wishnofsky's 7,700 kcal Rule Flaws to Resistance Periodization and Plateau Breakthroughs: The Definitive Dynamic Fat Loss &amp; Caloric Deficit Guide</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>117</v>
+        <v>511</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2538,12 +2538,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/06-sharpe-mdd-risk-control.html</t>
+          <t>en/articles/youtube-english-listening-and-shadowing-guide.html</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/06-sharpe-mdd-risk-control.html</t>
+          <t>https://gugopro.com/en/articles/youtube-english-listening-and-shadowing-guide.html</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Risk‑return and maximum drawdown analysis: Sharpe, Sortino, Calmar implementation guide｜GugoPro Academy</t>
+          <t>Decoding YouTube Bilingual Listening &amp; Shadowing: L-Player Mastery &amp; Auditory Neural Shaping Guide | GugoPro Language Science</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Risk‑return and maximum drawdown analysis</t>
+          <t>Decoding YouTube Bilingual Listening &amp; Shadowing: L-Player Mastery &amp; Auditory Neural Shaping Guide</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>219</v>
+        <v>474</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/07-fire-4-percent-rule.html</t>
+          <t>en/articles/youtube-listening-connected-speech-guide.html</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/07-fire-4-percent-rule.html</t>
+          <t>https://gugopro.com/en/articles/youtube-listening-connected-speech-guide.html</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>[Retirement Planning] What is the FIRE movement and the 4% rule? How to calculate withdrawal rates and your retirement funding gap | GugoPro Academy</t>
+          <t>Why Watching YouTube Fails for English Learning: Speech Perception, Levenshtein Dictation Diff, and Shadowing Guide | GugoPro Language Science</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>[Retirement Planning] What is the FIRE movement and the 4% rule? How to calculate withdrawal rates and your retirement funding gap</t>
+          <t>Why Watching YouTube Fails for English Learning: Building Native Auditory Circuits via Speech Perception, Levenshtein Dictation Diff, and Shadowing</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>250</v>
+        <v>413</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/08-overseas-tax-guide.html</t>
+          <t>en/articles/youtube-sequel-tracker-guide.html</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/08-overseas-tax-guide.html</t>
+          <t>https://gugopro.com/en/articles/youtube-sequel-tracker-guide.html</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2655,12 +2655,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>[Tax Optimization &amp; Filing] How are US stock investments taxed? Practical guide to the 750 萬 tax‑exempt threshold for foreign income and 30% dividend withholding practice | GugoPro Academy</t>
+          <t>2026 YouTube Video Algorithm &amp; Series Retrieval Master Guide: Overcoming Recommendation Gaps via NLP Regex Denoising &amp; Incremental Diff Tracking | GugoPro Streaming Media Lab</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>[Tax Optimization &amp; Filing] How are US stock investments taxed? Practical guide to the 750 萬 tax‑exempt threshold for foreign income and 30% dividend withholding practice</t>
+          <t>2026 YouTube Video Algorithm &amp; Series Retrieval Master Guide: Overcoming Recommendation Gaps via NLP Regex Denoising &amp; Incremental Diff Tracking</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>227</v>
+        <v>492</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2686,17 +2686,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/09-high-dividend-etf-trap.html</t>
+          <t>en/tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/09-high-dividend-etf-trap.html</t>
+          <t>https://gugopro.com/en/tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>[High‑Dividend ETF Review] Taiwan ETFs 00878/00919/00929 vs US ETF SCHD: debunking high‑yield traps and the truth about total return | GugoPro Academy</t>
+          <t>Redirecting - AI Multilingual Speaking Tutor | GugoPro</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>[High‑Dividend ETF Review] Taiwan ETFs 00878/00919/00929 vs US ETF SCHD: debunking high‑yield traps and the truth about total return</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2721,14 +2721,14 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/10-bond-investing-guide.html</t>
+          <t>en/tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/10-bond-investing-guide.html</t>
+          <t>https://gugopro.com/en/tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2757,12 +2757,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>[Bond Investment Guide] US Treasuries (TLT/IEF) vs. Investment‑Grade Corporate Bonds (LQD): Asset‑allocation strategies in a rate‑cutting cycle | GugoPro Academy</t>
+          <t>Redirecting - Face-to-Face Travel Voice Translator | GugoPro</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>[Bond Investment Guide] US Treasuries (TLT/IEF) vs. Investment‑Grade Corporate Bonds (LQD): Asset‑allocation strategies in a rate‑cutting cycle</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2772,14 +2772,14 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2788,17 +2788,17 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/11-brokerage-deep-review.html</t>
+          <t>en/tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/11-brokerage-deep-review.html</t>
+          <t>https://gugopro.com/en/tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>[Encyclopedia of Overseas Broker Reviews] IB (Interactive Brokers), Firstrade, Charles Schwab — pros, cons, safety and hidden cost comparisons | GugoPro Academy</t>
+          <t>Redirecting - AI Tarot Master | GugoPro</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>[Encyclopedia of Overseas Broker Reviews] IB (Interactive Brokers), Firstrade, Charles Schwab — pros, cons, safety and hidden cost comparisons</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2823,14 +2823,14 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2839,17 +2839,17 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/12-inflation-hedging-reits-gold.html</t>
+          <t>en/tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/12-inflation-hedging-reits-gold.html</t>
+          <t>https://gugopro.com/en/tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>[Hedge Assets] How do gold (GLD) and real estate investment trusts (REITs) fit into asset allocation to hedge inflation? | GugoPro Academy</t>
+          <t>Redirecting - GugoPro AI Ziwei Astrology Master | GugoPro</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>[Hedge Assets] How do gold (GLD) and real estate investment trusts (REITs) fit into asset allocation to hedge inflation?</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2874,14 +2874,14 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2890,17 +2890,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/13-technical-indicators-truth.html</t>
+          <t>en/tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/13-technical-indicators-truth.html</t>
+          <t>https://gugopro.com/en/tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>[The Truth About Technical Analysis] Moving averages (MA), RSI, MACD — are they really useful? Technical indicators and blind spots from a quant trader's perspective | GugoPro Academy</t>
+          <t>Redirecting - YouTube Sequel Tracker | GugoPro</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>[The Truth About Technical Analysis] Moving averages (MA), RSI, MACD — are they really useful? Technical indicators and blind spots from a quant trader's perspective</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2925,14 +2925,14 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2941,17 +2941,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/14-backtesting-overfitting-guide.html</t>
+          <t>en/tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/14-backtesting-overfitting-guide.html</t>
+          <t>https://gugopro.com/en/tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>[Systematic Trading] What is backtesting (回測)? How to avoid overfitting (過度擬合) and historical traps | GugoPro Academy</t>
+          <t>Redirecting - YouTube Study Player | GugoPro</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>[Systematic Trading] What is backtesting (回測)? How to avoid overfitting (過度擬合) and historical traps</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2976,14 +2976,14 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/15-quant-research-workflow.html</t>
+          <t>en/tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/15-quant-research-workflow.html</t>
+          <t>https://gugopro.com/en/tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Quant research workflow: 5MA offsets, volatility Z‑Score and out‑of‑sample backtesting｜GugoPro Academy Z-Score</t>
+          <t>Redirecting - AI Nutritionist | GugoPro</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Quant research workflow: Put 5MA, volatility and backtests into the same chain of evidence.</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3027,14 +3027,14 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3043,17 +3043,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/16-futures-pairs-basis.html</t>
+          <t>en/tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/16-futures-pairs-basis.html</t>
+          <t>https://gugopro.com/en/tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Pair trading and cash‑futures spread for Taiwan index futures / 富台期: from Basis to roll risk｜GugoPro Academy</t>
+          <t>Redirecting - AI Weight Loss Coach | GugoPro</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Taiwan index futures / 富台期 pair trading: Break down the Basis first, then discuss arbitrage.</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3078,14 +3078,14 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3094,32 +3094,24 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/17-practical-trading.html</t>
+          <t>googled0dfad57039c64f6.html</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/17-practical-trading.html</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Category 13 Practical Trading: trading plan, execution, risk control and review — complete knowledge tree｜GugoPro Academy</t>
-        </is>
-      </c>
+          <t>https://gugopro.com/googled0dfad57039c64f6.html</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Practical trading: Turn ideas into executable, stop‑lossable and reviewable processes.</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3129,11 +3121,11 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3145,32 +3137,32 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>首頁</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/18-trend-following-breakout-playbook.html</t>
+          <t>index.html</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/18-trend-following-breakout-playbook.html</t>
+          <t>https://gugopro.com/index.html</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Trend following and breakout strategy Playbook: rules, sizing, false breakouts and backtest validation｜GugoPro Academy</t>
+          <t>GugoPro 工具箱｜YouTube 雙語字幕學習、AI 翻譯塔羅、TDEE 減脂計算與 Gemini API 配額監控等 9 款免費工具</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Trend following and breakout strategy: Write your view as verifiable rules.</t>
+          <t>GugoPro 工具箱</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3184,10 +3176,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
@@ -3201,12 +3193,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>en/articles/investment/index.html</t>
+          <t>index_en.html</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/investment/index.html</t>
+          <t>https://gugopro.com/index_en.html</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3216,12 +3208,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Investment Education Academy | GugoPro Academy</t>
+          <t>GugoPro Hub | 9 Free Browser Tools for YouTube Study, AI Translation, Tarot, TDEE &amp; Gemini Quota</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Systematized Investment education and practical matrix</t>
+          <t>GugoPro Hub</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3235,10 +3227,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>168</v>
+        <v>360</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
@@ -3247,32 +3239,32 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>首頁</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>en/articles/modern-ziwei-guide.html</t>
+          <t>index_ja.html</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/modern-ziwei-guide.html</t>
+          <t>https://gugopro.com/index_ja.html</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Farewell to Fatalism and Esoteric Intimidation! Reconstructing Ziwei Astrology with Modern Psychology: From Twelve Palaces and Si-Hua Dynamics to AI Decision Reflection Models | GugoPro Decision Science Column</t>
+          <t>GugoPro ツールボックス｜YouTube 2言語字幕学習、AI 翻訳タロット、TDEE 減脂計算、Gemini API 配額監視など無料ブラウザツール9選</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Farewell to Fatalism and Esoteric Intimidation! Reconstructing Ziwei Astrology with Modern Psychology: From Twelve Palaces and Si-Hua Dynamics to AI Decision Reflection Models</t>
+          <t>GugoPro ツールボックス</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3286,10 +3278,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>539</v>
+        <v>194</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56">
@@ -3303,27 +3295,27 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>en/articles/shadowing-with-ai-tutor.html</t>
+          <t>ja/articles/affective-filter-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/shadowing-with-ai-tutor.html</t>
+          <t>https://gugopro.com/ja/articles/affective-filter-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Overcoming 'Mute English': Shadowing, CEFR Output, and AI Tutoring for Fluent Speaking | GugoPro Language Science</t>
+          <t>話す恐怖を克服する心理学：クラッシェンの「情意フィルター仮説」、外国語不安（FLA）と AI チューターのゼロ圧力スピーキング完全ガイド｜GugoPro 言語学習コラム</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Overcoming 'Mute English': Shadowing, CEFR Output, and AI Tutoring for Fluent Speaking</t>
+          <t>話す恐怖を克服する心理学：クラッシェンの「情意フィルター仮説」、外国語不安（FLA）と AI チューターのゼロ圧力スピーキング完全ガイド</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3337,7 +3329,7 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>281</v>
+        <v>221</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>2</v>
@@ -3354,27 +3346,27 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>en/articles/tarot-decision-framework.html</t>
+          <t>ja/articles/amazon-ai-product-research-guide.html</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/tarot-decision-framework.html</t>
+          <t>https://gugopro.com/ja/articles/amazon-ai-product-research-guide.html</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Farewell to Fatalism: From Jungian Archetypal Psychology and Synchronicity to AI Tarot: Deconstructing Career Dilemmas and Relationship Anxiety via Structured Decision Models | GugoPro Decision Science Column</t>
+          <t>2026 越境EC・高精度リサーチ完全攻略：AIセマンティック・リバースエンジニアリングによるAmazonヒット商品開発、競合低評価（VOC）痛点分析とListingキーワード配置マトリクス｜GugoPro EC戦略コラム</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Farewell to Fatalism: From Jungian Archetypal Psychology and Synchronicity to AI Tarot: Deconstructing Career Dilemmas and Relationship Anxiety via Structured Decision Models</t>
+          <t>2026 越境EC・高精度リサーチ完全攻略：AIセマンティック・リバースエンジニアリングによるAmazonヒット商品開発、競合低評価（VOC）痛点分析とListingキーワード配置マトリクス</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3388,10 +3380,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>496</v>
+        <v>227</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3405,27 +3397,27 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>en/articles/tblt-with-ai-tutor.html</t>
+          <t>ja/articles/carb-cycling-and-home-workout-guide.html</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/tblt-with-ai-tutor.html</t>
+          <t>https://gugopro.com/ja/articles/carb-cycling-and-home-workout-guide.html</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Beyond Rote Memorization: Task-Based Language Teaching (TBLT), Robinson's Cognition Hypothesis, and High-Impact Speaking with AI | GugoPro Language Science</t>
+          <t>炭水化物循環法（カーボサイクル）完全減脂ガイド：高・低炭水化物日の生化学機序、器具不要の自宅燃焼ルーティン、筋分解防止の極意｜GugoPro 運動生理学コラム</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Beyond Rote Memorization: Task-Based Language Teaching (TBLT), Robinson's Cognition Hypothesis, and High-Impact Speaking with AI</t>
+          <t>炭水化物循環法（カーボサイクル）完全減脂ガイド：高・低炭水化物日の生化学機序、器具不要の自宅燃焼ルーティン、筋分解防止の極意</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3439,7 +3431,7 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>522</v>
+        <v>204</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>2</v>
@@ -3456,27 +3448,27 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>en/articles/tdee-and-macros-guide.html</t>
+          <t>ja/articles/diabetes-and-insulin-resistance-guide.html</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/tdee-and-macros-guide.html</t>
+          <t>https://gugopro.com/ja/articles/diabetes-and-insulin-resistance-guide.html</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Defeat Chronic Dieting &amp; Yo-Yo Rebound: The Complete Scientific Guide to TDEE, Adaptive Thermogenesis &amp; Macronutrient Control for Dining Out | GugoPro Metabolic Health Column</t>
+          <t>糖尿病予備群・インスリン抵抗性の食事法完全ガイド：GI/GL値・カーボカウントからAI写真食事管理まで——血糖値スパイクを防ぐ栄養素調控｜GugoPro 代謝医学コラム</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Defeat Chronic Dieting &amp; Yo-Yo Rebound: The Complete Scientific Guide to TDEE, Adaptive Thermogenesis &amp; Macronutrient Control for Dining Out</t>
+          <t>糖尿病予備群・インスリン抵抗性の食事法完全ガイド：GI/GL値・カーボカウントからAI写真食事管理まで——血糖値スパイクを防ぐ栄養素調控</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3490,7 +3482,7 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>543</v>
+        <v>164</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>2</v>
@@ -3507,27 +3499,27 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>en/articles/travel-translator-guide.html</t>
+          <t>ja/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/travel-translator-guide.html</t>
+          <t>https://gugopro.com/ja/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Say Goodbye to Awkward Phone-Passing! 180° Face-to-Face Flipped UI Design, HCI Spatial Psychology, and Practical Travel Communication Guide | GugoPro Cross-Cultural Column</t>
+          <t>脂肪肝を逆転する減糖＆地中海食完全ガイド：内臓脂肪燃焼からPFC黄金比率・外食AI管理まで——MASLDを根本改善する長寿実戦マニュアル｜GugoPro 肝臓代謝コラム</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Say Goodbye to Awkward Phone-Passing! 180° Face-to-Face Flipped UI Design, HCI Spatial Psychology, and Practical Travel Communication Guide</t>
+          <t>脂肪肝を逆転する減糖＆地中海食完全ガイド：内臓脂肪燃焼からPFC黄金比率・外食AI管理まで——MASLDを根本改善する長寿実戦マニュアル</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3541,7 +3533,7 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>501</v>
+        <v>206</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>2</v>
@@ -3558,27 +3550,27 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>en/articles/weight-loss-planner-guide.html</t>
+          <t>ja/articles/gemini-api-free-tier-and-developer-guide.html</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/weight-loss-planner-guide.html</t>
+          <t>https://gugopro.com/ja/articles/gemini-api-free-tier-and-developer-guide.html</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Beyond Linear Weight Loss Myths: From Wishnofsky's 7,700 kcal Rule Flaws to Resistance Periodization and Plateau Breakthroughs: The Definitive Dynamic Fat Loss &amp; Caloric Deficit Guide | GugoPro Exercise Physiology Column</t>
+          <t>2026 開発者完全攻略ハンドブック：Google Gemini 公式無料APIを活用したゼロコスト商用グレードアプリのアーキテクチャ設計とエラー完全トラブルシューティング指南｜GugoPro クラウドシステムコラム</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Beyond Linear Weight Loss Myths: From Wishnofsky's 7,700 kcal Rule Flaws to Resistance Periodization and Plateau Breakthroughs: The Definitive Dynamic Fat Loss &amp; Caloric Deficit Guide</t>
+          <t>2026 開発者完全攻略ハンドブック：Google Gemini 公式無料APIを活用したゼロコスト商用グレードアプリのアーキテクチャ設計とエラー完全トラブルシューティング指南</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3592,7 +3584,7 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>511</v>
+        <v>271</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>2</v>
@@ -3609,27 +3601,27 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>en/articles/youtube-english-listening-and-shadowing-guide.html</t>
+          <t>ja/articles/how-to-master-tarot-guide.html</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/youtube-english-listening-and-shadowing-guide.html</t>
+          <t>https://gugopro.com/ja/articles/how-to-master-tarot-guide.html</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Decoding YouTube Bilingual Listening &amp; Shadowing: L-Player Mastery &amp; Auditory Neural Shaping Guide | GugoPro Language Science</t>
+          <t>タロットマスターへの道：78枚の丸暗記を脱し「直観的フロー・リーディング」へ——古典記号論、ナラティブ心理学、AI協同による限界的練習完全ガイド｜GugoPro 意思決定科学コラム</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Decoding YouTube Bilingual Listening &amp; Shadowing: L-Player Mastery &amp; Auditory Neural Shaping Guide</t>
+          <t>如何にしてタロットマスターとなるか？ 78枚の意味の丸暗記から「直観的フロー・リーディング」へ：古典記号論・ナラティブ心理学・AI協同による限界的練習完全手引</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3643,7 +3635,7 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>474</v>
+        <v>145</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>2</v>
@@ -3660,27 +3652,27 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>en/articles/youtube-listening-connected-speech-guide.html</t>
+          <t>ja/articles/how-to-master-ziwei-guide.html</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/youtube-listening-connected-speech-guide.html</t>
+          <t>https://gugopro.com/ja/articles/how-to-master-ziwei-guide.html</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Why Watching YouTube Fails for English Learning: Speech Perception, Levenshtein Dictation Diff, and Shadowing Guide | GugoPro Language Science</t>
+          <t>紫微斗数マスターへの道：百の星の丸暗記を脱し「動態格局解盤」へ——文化記号論、システムダイナミクス、AI協同による限界的練習完全ガイド｜GugoPro 意思決定科学コラム</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Why Watching YouTube Fails for English Learning: Building Native Auditory Circuits via Speech Perception, Levenshtein Dictation Diff, and Shadowing</t>
+          <t>紫微斗数マスターへの道：百の星の丸暗記を脱し「動態格局解盤」へ——文化記号論、システムダイナミクス、AI協同による限界的練習完全ガイド</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3694,7 +3686,7 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>413</v>
+        <v>199</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>2</v>
@@ -3711,27 +3703,27 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>en/articles/youtube-sequel-tracker-guide.html</t>
+          <t>ja/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/articles/youtube-sequel-tracker-guide.html</t>
+          <t>https://gugopro.com/ja/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026 YouTube Video Algorithm &amp; Series Retrieval Master Guide: Overcoming Recommendation Gaps via NLP Regex Denoising &amp; Incremental Diff Tracking | GugoPro Streaming Media Lab</t>
+          <t>168断食はカロリー計算より本当に痩せるのか？細胞自噬、インスリン仮説からエネルギー赤字の真相まで：リバウンドと筋肉減少の罠を解体する完全ガイド｜GugoPro 代謝内分泌コラム</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2026 YouTube Video Algorithm &amp; Series Retrieval Master Guide: Overcoming Recommendation Gaps via NLP Regex Denoising &amp; Incremental Diff Tracking</t>
+          <t>168断食はカロリー計算より本当に痩せるのか？細胞自噬、インスリン仮説からエネルギー赤字の真相まで：リバウンドと筋肉減少の罠を解体する完全ガイド</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3745,7 +3737,7 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>492</v>
+        <v>233</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>2</v>
@@ -3757,32 +3749,32 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai/english-speaking-tutor.html</t>
+          <t>ja/articles/modern-ziwei-guide.html</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai/english-speaking-tutor.html</t>
+          <t>https://gugopro.com/ja/articles/modern-ziwei-guide.html</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - AI Multilingual Speaking Tutor | GugoPro</t>
+          <t>宿命論とオカルト的脅迫からの脱却：現代心理学で再構築する紫微斗数——十二宮位、四化の動態からAI意思決定反省モデルへ｜GugoPro 意思決定科学コラム</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>宿命論とオカルト的脅迫からの脱却：現代心理学で再構築する紫微斗数——十二宮位、四化の動態からAI意思決定反省モデルへ</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3792,14 +3784,14 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -3808,32 +3800,32 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai/realtime-translator.html</t>
+          <t>ja/articles/shadowing-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai/realtime-translator.html</t>
+          <t>https://gugopro.com/ja/articles/shadowing-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - Face-to-Face Travel Voice Translator | GugoPro</t>
+          <t>「話せない英語」にサヨナラ！シャドーイング、CEFR文脈出力、AIチューターによるスピーキング実践ガイド｜GugoPro 言語科学コラム</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>「話せない英語」にサヨナラ！シャドーイング、CEFR文脈輸出、AIチューターによるスピーキング実践ガイド</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3843,14 +3835,14 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -3859,32 +3851,32 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai/tarot-master.html</t>
+          <t>ja/articles/tarot-decision-framework.html</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai/tarot-master.html</t>
+          <t>https://gugopro.com/ja/articles/tarot-decision-framework.html</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - AI Tarot Master | GugoPro</t>
+          <t>迷信的宿命論からの脱却：ユングの「元型」心理学・共時性からAIタロットへ——キャリアの二者択一と関係性不安を解体する構造化意思決定モデル｜GugoPro 意思決定科学コラム</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>迷信的宿命論からの脱却：ユングの「元型」心理学・共時性からAIタロットへ——キャリアの二者択一と関係性不安を解体する構造化意思決定モデル</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3894,14 +3886,14 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -3910,32 +3902,32 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai/ziwei-astrology.html</t>
+          <t>ja/articles/tblt-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai/ziwei-astrology.html</t>
+          <t>https://gugopro.com/ja/articles/tblt-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - GugoPro AI Ziwei Astrology Master | GugoPro</t>
+          <t>丸暗記にサヨナラ！タスク型教授法（TBLT）、Robinson認知仮説とAIチューターによる英会話実践ガイド｜GugoPro 言語科学コラム</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>丸暗記にサヨナラ！タスク型教授法（TBLT）、Robinson認知仮説とAIチューターによる英会話実践ガイド</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3945,14 +3937,14 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -3961,32 +3953,32 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai-media/ai-video-tracker.html</t>
+          <t>ja/articles/tdee-and-macros-guide.html</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai-media/ai-video-tracker.html</t>
+          <t>https://gugopro.com/ja/articles/tdee-and-macros-guide.html</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - YouTube Sequel Tracker | GugoPro</t>
+          <t>無駄な食事制限とリバウンドを完全に卒業！熱力学エネルギー収支、適応熱産生からAI食事解析まで：外食派のためのTDEE＆PFCバランス精密調整バイブル｜GugoPro 代謝健康專欄</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>無駄な食事制限とリバウンドを完全に卒業！熱力学エネルギー収支、適応熱産生からAI食事解析まで：外食派のためのTDEE＆PFCバランス精密調整バイブル</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3996,14 +3988,14 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4012,32 +4004,32 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>en/tools/english/l-player-study.html</t>
+          <t>ja/articles/travel-translator-guide.html</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/english/l-player-study.html</t>
+          <t>https://gugopro.com/ja/articles/travel-translator-guide.html</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - YouTube Study Player | GugoPro</t>
+          <t>スマホの気まずい手渡しにサヨナラ！180°対面反転UIのデザイン美学・HCI空間心理学と海外旅行会話実践ガイド｜GugoPro 異文化コミュニケーションコラム</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>スマホの気まずい手渡しにサヨナラ！180°対面反転UIのデザイン美学・HCI空間心理学と海外旅行会話実践ガイド</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4047,14 +4039,14 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4063,32 +4055,32 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>en/tools/health/tdee-macros-calculator.html</t>
+          <t>ja/articles/weight-loss-planner-guide.html</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/health/tdee-macros-calculator.html</t>
+          <t>https://gugopro.com/ja/articles/weight-loss-planner-guide.html</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - AI Nutritionist | GugoPro</t>
+          <t>線形減量の幻想からの脱却！Wishnofsky 7700kcal法則の破綻からレジスタンストレーニング期分け・停滞期突破まで：動的減量計画とカロリー赤字完全ガイド｜GugoPro 運動生理学コラム</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>線形減量の幻想からの脱却！Wishnofsky 7700kcal法則の破綻からレジスタンストレーニング期分け・停滞期突破まで：動的減量計画とカロリー赤字完全ガイド</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4098,14 +4090,14 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4114,32 +4106,32 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>en/tools/health/weight-loss-planner.html</t>
+          <t>ja/articles/youtube-english-listening-and-shadowing-guide.html</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/health/weight-loss-planner.html</t>
+          <t>https://gugopro.com/ja/articles/youtube-english-listening-and-shadowing-guide.html</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - AI Weight Loss Coach | GugoPro</t>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイングで母語レベルの聴覚神経回路を構築する完全ガイド｜GugoPro 言語科学コラム</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4149,14 +4141,14 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4165,24 +4157,32 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>googled0dfad57039c64f6.html</t>
+          <t>ja/articles/youtube-listening-connected-speech-guide.html</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/googled0dfad57039c64f6.html</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr"/>
+          <t>https://gugopro.com/ja/articles/youtube-listening-connected-speech-guide.html</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイング完全ガイド｜GugoPro 言語科学コラム</t>
+        </is>
+      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4192,14 +4192,14 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4208,32 +4208,32 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>index.html</t>
+          <t>ja/articles/youtube-sequel-tracker-guide.html</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/index.html</t>
+          <t>https://gugopro.com/ja/articles/youtube-sequel-tracker-guide.html</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>zh-TW</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>GugoPro 工具箱｜YouTube 雙語字幕學習、AI 翻譯塔羅、TDEE 減脂計算與 Gemini API 配額監控等 9 款免費工具</t>
+          <t>2026年YouTube動画推薦アルゴリズムとシリーズ検索完全ガイド：推薦漏れを解消しNLP正規表現ノイズ除去と差分照合で跨チャンネル追跡を実現する｜GugoPro ストリーミング研究コラム</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>GugoPro 工具箱</t>
+          <t>2026年YouTube動画推薦アルゴリズムとシリーズ検索完全ガイド：推薦漏れを解消し NLP正規表現ノイズ除去と差分照合 で跨チャンネル追跡を実現する</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4247,10 +4247,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4259,32 +4259,32 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>index_en.html</t>
+          <t>ja/tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/index_en.html</t>
+          <t>https://gugopro.com/ja/tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>GugoPro Hub | 9 Free Browser Tools for YouTube Study, AI Translation, Tarot, TDEE &amp; Gemini Quota</t>
+          <t>リダイレクト中 - AI多言語スピーキングチューター | GugoPro</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>GugoPro Hub</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4294,14 +4294,14 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>index_ja.html</t>
+          <t>ja/tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/index_ja.html</t>
+          <t>https://gugopro.com/ja/tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>GugoPro ツールボックス｜YouTube 2言語字幕学習、AI 翻訳タロット、TDEE 減脂計算、Gemini API 配額監視など無料ブラウザツール9選</t>
+          <t>リダイレクト中 - 対面型リアルタイム音声翻訳 | GugoPro</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>GugoPro ツールボックス</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4345,14 +4345,14 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/affective-filter-with-ai-tutor.html</t>
+          <t>ja/tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/affective-filter-with-ai-tutor.html</t>
+          <t>https://gugopro.com/ja/tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>話す恐怖を克服する心理学：クラッシェンの「情意フィルター仮説」、外国語不安（FLA）と AI チューターのゼロ圧力スピーキング完全ガイド｜GugoPro 言語学習コラム</t>
+          <t>リダイレクト中 - AIタロットマスター | GugoPro</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>話す恐怖を克服する心理学：クラッシェンの「情意フィルター仮説」、外国語不安（FLA）と AI チューターのゼロ圧力スピーキング完全ガイド</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4396,14 +4396,14 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4412,17 +4412,17 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/amazon-ai-product-research-guide.html</t>
+          <t>ja/tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/amazon-ai-product-research-guide.html</t>
+          <t>https://gugopro.com/ja/tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026 越境EC・高精度リサーチ完全攻略：AIセマンティック・リバースエンジニアリングによるAmazonヒット商品開発、競合低評価（VOC）痛点分析とListingキーワード配置マトリクス｜GugoPro EC戦略コラム</t>
+          <t>リダイレクト中 - AI紫微斗数マスター | GugoPro</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>2026 越境EC・高精度リサーチ完全攻略：AIセマンティック・リバースエンジニアリングによるAmazonヒット商品開発、競合低評価（VOC）痛点分析とListingキーワード配置マトリクス</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4447,11 +4447,11 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>1</v>
@@ -4463,17 +4463,17 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/carb-cycling-and-home-workout-guide.html</t>
+          <t>ja/tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/carb-cycling-and-home-workout-guide.html</t>
+          <t>https://gugopro.com/ja/tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>炭水化物循環法（カーボサイクル）完全減脂ガイド：高・低炭水化物日の生化学機序、器具不要の自宅燃焼ルーティン、筋分解防止の極意｜GugoPro 運動生理学コラム</t>
+          <t>リダイレクト中 - YouTube続編追跡 | GugoPro</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>炭水化物循環法（カーボサイクル）完全減脂ガイド：高・低炭水化物日の生化学機序、器具不要の自宅燃焼ルーティン、筋分解防止の極意</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4498,14 +4498,14 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4514,17 +4514,17 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/diabetes-and-insulin-resistance-guide.html</t>
+          <t>ja/tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/diabetes-and-insulin-resistance-guide.html</t>
+          <t>https://gugopro.com/ja/tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>糖尿病予備群・インスリン抵抗性の食事法完全ガイド：GI/GL値・カーボカウントからAI写真食事管理まで——血糖値スパイクを防ぐ栄養素調控｜GugoPro 代謝医学コラム</t>
+          <t>リダイレクト中 - YouTube学習プレイヤー | GugoPro</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>糖尿病予備群・インスリン抵抗性の食事法完全ガイド：GI/GL値・カーボカウントからAI写真食事管理まで——血糖値スパイクを防ぐ栄養素調控</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4549,14 +4549,14 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -4565,17 +4565,17 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/english-intro-break-the-ice.html</t>
+          <t>ja/tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/english-intro-break-the-ice.html</t>
+          <t>https://gugopro.com/ja/tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4585,12 +4585,12 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイング完全ガイド｜GugoPro 言語科学コラム</t>
+          <t>リダイレクト中 - AI栄養士 | GugoPro</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4600,14 +4600,14 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
+          <t>ja/tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
+          <t>https://gugopro.com/ja/tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>脂肪肝を逆転する減糖＆地中海食完全ガイド：内臓脂肪燃焼からPFC黄金比率・外食AI管理まで——MASLDを根本改善する長寿実戦マニュアル｜GugoPro 肝臓代謝コラム</t>
+          <t>リダイレクト中 - AI減量コーチ | GugoPro</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>脂肪肝を逆転する減糖＆地中海食完全ガイド：内臓脂肪燃焼からPFC黄金比率・外食AI管理まで——MASLDを根本改善する長寿実戦マニュアル</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4651,14 +4651,14 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -4667,32 +4667,32 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>法律條款</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/gemini-api-free-tier-and-developer-guide.html</t>
+          <t>privacy.html</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/gemini-api-free-tier-and-developer-guide.html</t>
+          <t>https://gugopro.com/privacy.html</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026 開発者完全攻略ハンドブック：Google Gemini 公式無料APIを活用したゼロコスト商用グレードアプリのアーキテクチャ設計とエラー完全トラブルシューティング指南｜GugoPro クラウドシステムコラム</t>
+          <t>隱私權政策｜GugoPro</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>2026 開発者完全攻略ハンドブック：Google Gemini 公式無料APIを活用したゼロコスト商用グレードアプリのアーキテクチャ設計とエラー完全トラブルシューティング指南</t>
+          <t>隱私權政策</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>271</v>
+        <v>60</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -4718,32 +4718,32 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>法律條款</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/how-to-master-tarot-guide.html</t>
+          <t>terms.html</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/how-to-master-tarot-guide.html</t>
+          <t>https://gugopro.com/terms.html</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>タロットマスターへの道：78枚の丸暗記を脱し「直観的フロー・リーディング」へ——古典記号論、ナラティブ心理学、AI協同による限界的練習完全ガイド｜GugoPro 意思決定科学コラム</t>
+          <t>服務條款｜GugoPro</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>如何にしてタロットマスターとなるか？ 78枚の意味の丸暗記から「直観的フロー・リーディング」へ：古典記号論・ナラティブ心理学・AI協同による限界的練習完全手引</t>
+          <t>服務條款</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/how-to-master-ziwei-guide.html</t>
+          <t>tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/how-to-master-ziwei-guide.html</t>
+          <t>https://gugopro.com/tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>紫微斗数マスターへの道：百の星の丸暗記を脱し「動態格局解盤」へ——文化記号論、システムダイナミクス、AI協同による限界的練習完全ガイド｜GugoPro 意思決定科学コラム</t>
+          <t>AI多國語言對話導師</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>紫微斗数マスターへの道：百の星の丸暗記を脱し「動態格局解盤」へ——文化記号論、システムダイナミクス、AI協同による限界的練習完全ガイド</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>199</v>
+        <v>65</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -4820,32 +4820,32 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
+          <t>tools/ai/gemini-api-quota.html</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
+          <t>https://gugopro.com/tools/ai/gemini-api-quota.html</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>168断食はカロリー計算より本当に痩せるのか？細胞自噬、インスリン仮説からエネルギー赤字の真相まで：リバウンドと筋肉減少の罠を解体する完全ガイド｜GugoPro 代謝内分泌コラム</t>
+          <t>Gemini API 配額服務導覽｜GugoPro</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>168断食はカロリー計算より本当に痩せるのか？細胞自噬、インスリン仮説からエネルギー赤字の真相まで：リバウンドと筋肉減少の罠を解体する完全ガイド</t>
+          <t>Gemini API 配額服務導覽</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4859,10 +4859,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>233</v>
+        <v>61</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/01-compound-interest-guide.html</t>
+          <t>tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/01-compound-interest-guide.html</t>
+          <t>https://gugopro.com/tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>複利効果と時間価値：バランスシートから最初のファイナンシャルシステムを構築するには？ | GugoPro Academy</t>
+          <t>面對面旅遊對話翻譯｜出國旅遊即時翻譯與雙向語音對話｜GugoPro</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>複利効果と時間価値：バランスシートから最初のファイナンシャルシステムを構築するには？</t>
+          <t>面對面旅遊對話翻譯：出國旅遊即時翻譯與雙向語音對話</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4922,32 +4922,32 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/02-etf-investing-bible.html</t>
+          <t>tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/02-etf-investing-bible.html</t>
+          <t>https://gugopro.com/tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>インデックス投資バイブル：台湾 0050/006208 vs 米国 VTI/VOO/QQQ 完全解析 | GugoPro Academy</t>
+          <t>AI 塔羅大師｜五種塔羅牌陣、提問指南與自我反思 - GugoPro</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>インデックス投資バイブル：台湾 0050/006208 vs 米国 VTI/VOO/QQQ 完全解析</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -4964,7 +4964,7 @@
         <v>63</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -4973,32 +4973,32 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/03-asset-allocation-rebalancing.html</t>
+          <t>tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/03-asset-allocation-rebalancing.html</t>
+          <t>https://gugopro.com/tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>資産配分と動的リバランス：目標ウェイトから取引摩擦まで｜GugoPro Academy</t>
+          <t>AI 紫微斗數大師｜紫微斗數線上排盤資料整理與十二宮位指南 - GugoPro</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>資産配分と動的リバランス： 目標ウェイトを実行可能な意思決定ルールにする。</t>
+          <t>把命盤問題，整理成可行動的洞察</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -5024,32 +5024,32 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/04-brokerage-comparison.html</t>
+          <t>tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/04-brokerage-comparison.html</t>
+          <t>https://gugopro.com/tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>米国ブローカー口座開設完全ガイド：台湾の複委託 vs 海外ブローカー | GugoPro Academy</t>
+          <t>YouTube 續集與新季追蹤器 - GugoPro</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>米国ブローカー口座開設完全ガイド：台湾の複委託 vs 海外ブローカー（Firstrade、IB、Schwab）比較</t>
+          <t>YouTube 續集與新季追蹤器</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5059,11 +5059,11 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5075,37 +5075,37 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/05-fundamental-valuation-metrics.html</t>
+          <t>tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/05-fundamental-valuation-metrics.html</t>
+          <t>https://gugopro.com/tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>ファンダメンタル評価指標：P/E、P/B、ROE | GugoPro Academy</t>
+          <t>【AB English Podcast】Ep.1 自我介紹與日常社交對話 (Mia &amp; Alex)｜L-Player</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>ファンダメンタル評価指標：P/E（株価収益率）、P/B（株価純資産倍率）、ROEの正しい読み方</t>
+          <t>YouTube 影音「聽・寫・口說」多國語言跟讀器</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>可見</t>
+          <t>疑似隱藏</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -5126,32 +5126,32 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/06-sharpe-mdd-risk-control.html</t>
+          <t>tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/06-sharpe-mdd-risk-control.html</t>
+          <t>https://gugopro.com/tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>リスクリターンと最大ドローダウン分析：Sharpe、Sortino、Calmar 実装ガイド｜GugoPro Academy</t>
+          <t>AI 專屬營養師 | GugoPro</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>リスクリターンと最大ドローダウンの分析</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -5177,32 +5177,32 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/07-fire-4-percent-rule.html</t>
+          <t>tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/07-fire-4-percent-rule.html</t>
+          <t>https://gugopro.com/tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>【退職金プラン】FIRE ムーブメントと 4% ルールとは？引き出し率と退職資金の不足額の計算方法 | GugoPro Academy</t>
+          <t>AI減肥瘦身教練｜科學減脂與熱量赤字規劃 | GugoPro</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>【退職金プラン】FIRE ムーブメントと 4% ルールとは？引き出し率と退職資金の不足額の計算方法</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -5228,32 +5228,32 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/08-overseas-tax-guide.html</t>
+          <t>tools/pdf/pdf-suite.html</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/08-overseas-tax-guide.html</t>
+          <t>https://gugopro.com/tools/pdf/pdf-suite.html</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>【節税と確定申告】米国株投資はどう申告するか？海外所得 750 萬 の免税枠と 30% 配当源泉徴収の実務 | GugoPro Academy</t>
+          <t>PDF 全能工作站｜免安裝線上閱讀、合併、分割與標註、零檔案外洩 - GugoPro</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>【節税と確定申告】米国株投資はどう申告するか？海外所得 750 萬 の免税枠と 30% 配当源泉徴収の実務</t>
+          <t>先選擇要處理的文件</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5263,14 +5263,14 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 未配置（合規）</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -5279,32 +5279,32 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>實用教學</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/09-high-dividend-etf-trap.html</t>
+          <t>tools/tutorials/how-to-get-gemini-api-key.html</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/09-high-dividend-etf-trap.html</t>
+          <t>https://gugopro.com/tools/tutorials/how-to-get-gemini-api-key.html</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>【高配当 ETF 評価】台湾上場 ETF 00878/00919/00929 vs 米国 ETF SCHD：高配当利回りの罠を解くと総リターンの真実が見える | GugoPro Academy</t>
+          <t>Gemini API Key 申請教學｜Google Gemini API Key 取得與安全設定教學、免安裝與隱私說明 - GugoPro</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>【高配当 ETF 評価】台湾上場 ETF 00878/00919/00929 vs 米国 ETF SCHD：高配当利回りの罠を解くと総リターンの真実が見える</t>
+          <t>Google Gemini API Key 1 分鐘快速申請步驟</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -5330,32 +5330,32 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/investment/10-bond-investing-guide.html</t>
+          <t>tools/tw-market/taiwan-pair-trading.html</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/investment/10-bond-investing-guide.html</t>
+          <t>https://gugopro.com/tools/tw-market/taiwan-pair-trading.html</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-Hant-TW</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>【債券投資ガイド】米国債 (TLT/IEF) vs 投資適格社債 (LQD)：利下げサイクルにおける資産配分戦略 | GugoPro Academy</t>
+          <t>Taiwan Pair Trading 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>【債券投資ガイド】米国債 (TLT/IEF) vs 投資適格社債 (LQD)：利下げサイクルにおける資産配分戦略</t>
+          <t>台灣股票與期貨 配對交易掃描工作站</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5365,2109 +5365,18 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 未配置（合規）</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>專欄文章</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>ja/articles/investment/11-brokerage-deep-review.html</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/articles/investment/11-brokerage-deep-review.html</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>【海外証券会社評価大全】IB（盈透／Interactive Brokers）、Firstrade、Charles Schwab（嘉信理財）─ 長所・短所、安全性と隠れたコスト比較 | GugoPro Academy</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>【海外証券会社評価大全】IB（盈透／Interactive Brokers）、Firstrade、Charles Schwab（嘉信理財）─ 長所・短所、安全性と隠れたコスト比較</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>111</v>
-      </c>
-      <c r="K97" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>專欄文章</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>ja/articles/investment/12-inflation-hedging-reits-gold.html</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/articles/investment/12-inflation-hedging-reits-gold.html</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>【ヘッジ資産】金（GLD）と不動産投資信託（REITs）はインフレ対策として資産配分にどう組み込むか？ | GugoPro Academy</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>【ヘッジ資産】金（GLD）と不動産投資信託（REITs）はインフレ対策として資産配分にどう組み込むか？</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J98" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="K98" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>專欄文章</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>ja/articles/investment/13-technical-indicators-truth.html</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/articles/investment/13-technical-indicators-truth.html</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>【テクニカル分析の真実】移動平均線 (MA)、RSI、MACD は本当に役立つのか？クオンツトレーダーが見るテクニカル指標の有効場面と盲点 | GugoPro Academy</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>【テクニカル分析の真実】移動平均線 (MA)、RSI、MACD は本当に役立つのか？クオンツトレーダーが見るテクニカル指標の有効場面と盲点</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="K99" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>專欄文章</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>ja/articles/investment/14-backtesting-overfitting-guide.html</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/articles/investment/14-backtesting-overfitting-guide.html</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>【システムトレード】バックテスト (Backtesting/回測) とは？過学習 (Overfitting/過度擬合) と歴史的罠を避ける方法 | GugoPro Academy</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>【システムトレード】バックテスト (Backtesting/回測) とは？過学習 (Overfitting/過度擬合) と歴史的罠を避ける方法</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>專欄文章</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>ja/articles/investment/15-quant-research-workflow.html</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/articles/investment/15-quant-research-workflow.html</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>量的研究ワークフロー：5MAオフセット、ボラティリティのZ‑Score、アウト‑オブ‑サンプルバックテスト｜GugoPro Academy Z-Score</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>量的研究ワークフロー： 5MA、ボラティリティ、バックテストを同じ証拠チェーンに組み込む。</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>專欄文章</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>ja/articles/investment/16-futures-pairs-basis.html</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/articles/investment/16-futures-pairs-basis.html</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>臺指期／富台期のペア取引と期現價差：Basisからロールリスクまで｜GugoPro Academy</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>臺指期／富台期ペア取引： まず Basis を分解し、その後で裁定について議論する。</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="n">
-        <v>102</v>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>專欄文章</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>ja/articles/investment/17-practical-trading.html</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/articles/investment/17-practical-trading.html</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>第13類 実戦取引：取引計画、実行、リスク管理、レビューの完全なナレッジツリー｜GugoPro Academy</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>実戦トレーディング： アイデアを実行可能でストップが設定でき、再検討できるプロセスにする。</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="K103" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>專欄文章</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>ja/articles/investment/18-trend-following-breakout-playbook.html</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/articles/investment/18-trend-following-breakout-playbook.html</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>トレンド追跡とブレイクアウト戦略プレイブック：ルール、ポジション、フェイクブレイク、バックテスト検証｜GugoPro Academy</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>トレンド追跡とブレイクアウト戦略： 自分の「見解」を検証可能なルールに書き換える。</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="n">
-        <v>117</v>
-      </c>
-      <c r="K104" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>首頁</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>ja/articles/investment/index.html</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/articles/investment/index.html</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>投資教育アカデミー | GugoPro Academy</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>システム化 投資教育と実戦のマトリクス</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J105" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="K105" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>專欄文章</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>ja/articles/modern-ziwei-guide.html</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/articles/modern-ziwei-guide.html</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>宿命論とオカルト的脅迫からの脱却：現代心理学で再構築する紫微斗数——十二宮位、四化の動態からAI意思決定反省モデルへ｜GugoPro 意思決定科学コラム</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>宿命論とオカルト的脅迫からの脱却：現代心理学で再構築する紫微斗数——十二宮位、四化の動態からAI意思決定反省モデルへ</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>169</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="n">
-        <v>106</v>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>專欄文章</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>ja/articles/shadowing-with-ai-tutor.html</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/articles/shadowing-with-ai-tutor.html</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>「話せない英語」にサヨナラ！シャドーイング、CEFR文脈出力、AIチューターによるスピーキング実践ガイド｜GugoPro 言語科学コラム</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>「話せない英語」にサヨナラ！シャドーイング、CEFR文脈輸出、AIチューターによるスピーキング実践ガイド</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="K107" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>專欄文章</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>ja/articles/tarot-decision-framework.html</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/articles/tarot-decision-framework.html</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>迷信的宿命論からの脱却：ユングの「元型」心理学・共時性からAIタロットへ——キャリアの二者択一と関係性不安を解体する構造化意思決定モデル｜GugoPro 意思決定科学コラム</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>迷信的宿命論からの脱却：ユングの「元型」心理学・共時性からAIタロットへ——キャリアの二者択一と関係性不安を解体する構造化意思決定モデル</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="n">
-        <v>161</v>
-      </c>
-      <c r="K108" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>專欄文章</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>ja/articles/tblt-with-ai-tutor.html</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/articles/tblt-with-ai-tutor.html</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>丸暗記にサヨナラ！タスク型教授法（TBLT）、Robinson認知仮説とAIチューターによる英会話実践ガイド｜GugoPro 言語科学コラム</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>丸暗記にサヨナラ！タスク型教授法（TBLT）、Robinson認知仮説とAIチューターによる英会話実践ガイド</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J109" s="2" t="n">
-        <v>184</v>
-      </c>
-      <c r="K109" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>專欄文章</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>ja/articles/tdee-and-macros-guide.html</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/articles/tdee-and-macros-guide.html</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>無駄な食事制限とリバウンドを完全に卒業！熱力学エネルギー収支、適応熱産生からAI食事解析まで：外食派のためのTDEE＆PFCバランス精密調整バイブル｜GugoPro 代謝健康專欄</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>無駄な食事制限とリバウンドを完全に卒業！熱力学エネルギー収支、適応熱産生からAI食事解析まで：外食派のためのTDEE＆PFCバランス精密調整バイブル</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J110" s="2" t="n">
-        <v>248</v>
-      </c>
-      <c r="K110" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>專欄文章</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>ja/articles/travel-translator-guide.html</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/articles/travel-translator-guide.html</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>スマホの気まずい手渡しにサヨナラ！180°対面反転UIのデザイン美学・HCI空間心理学と海外旅行会話実践ガイド｜GugoPro 異文化コミュニケーションコラム</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>スマホの気まずい手渡しにサヨナラ！180°対面反転UIのデザイン美学・HCI空間心理学と海外旅行会話実践ガイド</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J111" s="2" t="n">
-        <v>206</v>
-      </c>
-      <c r="K111" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="n">
-        <v>111</v>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>專欄文章</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>ja/articles/weight-loss-planner-guide.html</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/articles/weight-loss-planner-guide.html</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>線形減量の幻想からの脱却！Wishnofsky 7700kcal法則の破綻からレジスタンストレーニング期分け・停滞期突破まで：動的減量計画とカロリー赤字完全ガイド｜GugoPro 運動生理学コラム</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>線形減量の幻想からの脱却！Wishnofsky 7700kcal法則の破綻からレジスタンストレーニング期分け・停滞期突破まで：動的減量計画とカロリー赤字完全ガイド</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J112" s="2" t="n">
-        <v>229</v>
-      </c>
-      <c r="K112" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>專欄文章</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>ja/articles/youtube-english-listening-and-shadowing-guide.html</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/articles/youtube-english-listening-and-shadowing-guide.html</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイングで母語レベルの聴覚神経回路を構築する完全ガイド｜GugoPro 言語科学コラム</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J113" s="2" t="n">
-        <v>161</v>
-      </c>
-      <c r="K113" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>專欄文章</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>ja/articles/youtube-listening-connected-speech-guide.html</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/articles/youtube-listening-connected-speech-guide.html</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイング完全ガイド｜GugoPro 言語科学コラム</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="n">
-        <v>170</v>
-      </c>
-      <c r="K114" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>專欄文章</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>ja/articles/youtube-sequel-tracker-guide.html</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/articles/youtube-sequel-tracker-guide.html</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>2026年YouTube動画推薦アルゴリズムとシリーズ検索完全ガイド：推薦漏れを解消しNLP正規表現ノイズ除去と差分照合で跨チャンネル追跡を実現する｜GugoPro ストリーミング研究コラム</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>2026年YouTube動画推薦アルゴリズムとシリーズ検索完全ガイド：推薦漏れを解消し NLP正規表現ノイズ除去と差分照合 で跨チャンネル追跡を実現する</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J115" s="2" t="n">
-        <v>224</v>
-      </c>
-      <c r="K115" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>ja/tools/ai/english-speaking-tutor.html</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/tools/ai/english-speaking-tutor.html</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>リダイレクト中 - AI多言語スピーキングチューター | GugoPro</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="J116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="n">
-        <v>116</v>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>ja/tools/ai/realtime-translator.html</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/tools/ai/realtime-translator.html</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>リダイレクト中 - 対面型リアルタイム音声翻訳 | GugoPro</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="J117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="n">
-        <v>117</v>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>ja/tools/ai/tarot-master.html</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/tools/ai/tarot-master.html</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>リダイレクト中 - AIタロットマスター | GugoPro</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="J118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="n">
-        <v>118</v>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>ja/tools/ai/ziwei-astrology.html</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/tools/ai/ziwei-astrology.html</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>リダイレクト中 - AI紫微斗数マスター | GugoPro</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="J119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>ja/tools/ai-media/ai-video-tracker.html</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/tools/ai-media/ai-video-tracker.html</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>リダイレクト中 - YouTube続編追跡 | GugoPro</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="J120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>ja/tools/english/l-player-study.html</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/tools/english/l-player-study.html</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>リダイレクト中 - YouTube学習プレイヤー | GugoPro</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="J121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>ja/tools/health/tdee-macros-calculator.html</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/tools/health/tdee-macros-calculator.html</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>リダイレクト中 - AI栄養士 | GugoPro</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="J122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="n">
-        <v>122</v>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>ja/tools/health/weight-loss-planner.html</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/tools/health/weight-loss-planner.html</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>リダイレクト中 - AI減量コーチ | GugoPro</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="J123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="n">
-        <v>123</v>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>法律條款</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>privacy.html</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/privacy.html</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>隱私權政策｜GugoPro</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>隱私權政策</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J124" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="K124" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="n">
-        <v>124</v>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>法律條款</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>terms.html</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/terms.html</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>服務條款｜GugoPro</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>服務條款</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I125" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J125" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="K125" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
-        <v>125</v>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>tools/ai/english-speaking-tutor.html</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/ai/english-speaking-tutor.html</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>AI多國語言對話導師</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J126" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="K126" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="n">
-        <v>126</v>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>tools/ai/gemini-api-quota.html</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/ai/gemini-api-quota.html</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>Gemini API 配額服務導覽｜GugoPro</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>Gemini API 配額服務導覽</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J127" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="K127" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>tools/ai/realtime-translator.html</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/ai/realtime-translator.html</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>面對面旅遊對話翻譯｜出國旅遊即時翻譯與雙向語音對話｜GugoPro</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>面對面旅遊對話翻譯：出國旅遊即時翻譯與雙向語音對話</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I128" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J128" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="K128" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>tools/ai/tarot-master.html</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/ai/tarot-master.html</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>AI 塔羅大師｜五種塔羅牌陣、提問指南與自我反思 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J129" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="K129" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>tools/ai/ziwei-astrology.html</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/ai/ziwei-astrology.html</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>AI 紫微斗數大師｜紫微斗數線上排盤資料整理與十二宮位指南 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>把命盤問題，整理成可行動的洞察</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I130" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J130" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="K130" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="n">
-        <v>130</v>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>tools/ai-media/ai-video-tracker.html</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/ai-media/ai-video-tracker.html</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>YouTube 續集與新季追蹤器 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>YouTube 續集與新季追蹤器</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="J131" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="K131" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>tools/english/l-player-study.html</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/english/l-player-study.html</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>【AB English Podcast】Ep.1 自我介紹與日常社交對話 (Mia &amp; Alex)｜L-Player</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>YouTube 影音「聽・寫・口說」多國語言跟讀器</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>疑似隱藏</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J132" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="K132" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>tools/health/tdee-macros-calculator.html</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/health/tdee-macros-calculator.html</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>AI 專屬營養師 | GugoPro</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I133" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J133" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="K133" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
-        <v>133</v>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>tools/health/weight-loss-planner.html</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/health/weight-loss-planner.html</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>AI減肥瘦身教練｜科學減脂與熱量赤字規劃 | GugoPro</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J134" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="K134" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>tools/pdf/pdf-suite.html</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/pdf/pdf-suite.html</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>PDF 全能工作站｜免安裝線上閱讀、合併、分割與標註、零檔案外洩 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>先選擇要處理的文件</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t>❌ 未配置（合規）</t>
-        </is>
-      </c>
-      <c r="J135" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="K135" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
-        <v>135</v>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>實用教學</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>tools/tutorials/how-to-get-gemini-api-key.html</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/tutorials/how-to-get-gemini-api-key.html</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>Gemini API Key 申請教學｜Google Gemini API Key 取得與安全設定教學、免安裝與隱私說明 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>Google Gemini API Key 1 分鐘快速申請步驟</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J136" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="K136" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
-        <v>136</v>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>tools/tw-market/taiwan-pair-trading.html</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/tw-market/taiwan-pair-trading.html</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>zh-Hant-TW</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>Taiwan Pair Trading 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>台灣股票與期貨 配對交易掃描工作站</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I137" s="2" t="inlineStr">
-        <is>
-          <t>❌ 未配置（合規）</t>
-        </is>
-      </c>
-      <c r="J137" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="K137" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K137"/>
+  <autoFilter ref="A1:K96"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -7564,51 +5473,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId136"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId137"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId96"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7645,7 +5513,7 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>136</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3">
@@ -7655,7 +5523,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -7695,7 +5563,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>96</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
@@ -7755,7 +5623,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/seo_inventory_report.xlsx
+++ b/seo_inventory_report.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SEO AdSense 盤點'!$A$1:$K$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SEO AdSense 盤點'!$A$1:$K$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -157,8 +157,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SEOInventory" displayName="SEOInventory" ref="A1:K96" headerRowCount="1">
-  <autoFilter ref="A1:K96"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SEOInventory" displayName="SEOInventory" ref="A1:K80" headerRowCount="1">
+  <autoFilter ref="A1:K80"/>
   <tableColumns count="11">
     <tableColumn id="1" name="編號"/>
     <tableColumn id="2" name="頁面分類"/>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2686,29 +2686,21 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai/english-speaking-tutor.html</t>
+          <t>googled0dfad57039c64f6.html</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai/english-speaking-tutor.html</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Redirecting - AI Multilingual Speaking Tutor | GugoPro</t>
-        </is>
-      </c>
+          <t>https://gugopro.com/googled0dfad57039c64f6.html</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>❌ 缺失</t>
@@ -2728,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2737,32 +2729,32 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>首頁</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai/realtime-translator.html</t>
+          <t>index.html</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai/realtime-translator.html</t>
+          <t>https://gugopro.com/index.html</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - Face-to-Face Travel Voice Translator | GugoPro</t>
+          <t>GugoPro 工具箱｜YouTube 雙語字幕學習、AI 翻譯塔羅、TDEE 減脂計算與 Gemini API 配額監控等 9 款免費工具</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>GugoPro 工具箱</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2772,14 +2764,14 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
@@ -2788,17 +2780,17 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>首頁</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai/tarot-master.html</t>
+          <t>index_en.html</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai/tarot-master.html</t>
+          <t>https://gugopro.com/index_en.html</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2808,12 +2800,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - AI Tarot Master | GugoPro</t>
+          <t>GugoPro Hub | 9 Free Browser Tools for YouTube Study, AI Translation, Tarot, TDEE &amp; Gemini Quota</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>GugoPro Hub</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2823,14 +2815,14 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -2839,32 +2831,32 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>首頁</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai/ziwei-astrology.html</t>
+          <t>index_ja.html</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai/ziwei-astrology.html</t>
+          <t>https://gugopro.com/index_ja.html</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - GugoPro AI Ziwei Astrology Master | GugoPro</t>
+          <t>GugoPro ツールボックス｜YouTube 2言語字幕学習、AI 翻訳タロット、TDEE 減脂計算、Gemini API 配額監視など無料ブラウザツール9選</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>GugoPro ツールボックス</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2874,14 +2866,14 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -2890,32 +2882,32 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>en/tools/ai-media/ai-video-tracker.html</t>
+          <t>ja/articles/affective-filter-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/ai-media/ai-video-tracker.html</t>
+          <t>https://gugopro.com/ja/articles/affective-filter-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - YouTube Sequel Tracker | GugoPro</t>
+          <t>話す恐怖を克服する心理学：クラッシェンの「情意フィルター仮説」、外国語不安（FLA）と AI チューターのゼロ圧力スピーキング完全ガイド｜GugoPro 言語学習コラム</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>話す恐怖を克服する心理学：クラッシェンの「情意フィルター仮説」、外国語不安（FLA）と AI チューターのゼロ圧力スピーキング完全ガイド</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2925,14 +2917,14 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -2941,32 +2933,32 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>en/tools/english/l-player-study.html</t>
+          <t>ja/articles/amazon-ai-product-research-guide.html</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/english/l-player-study.html</t>
+          <t>https://gugopro.com/ja/articles/amazon-ai-product-research-guide.html</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - YouTube Study Player | GugoPro</t>
+          <t>2026 越境EC・高精度リサーチ完全攻略：AIセマンティック・リバースエンジニアリングによるAmazonヒット商品開発、競合低評価（VOC）痛点分析とListingキーワード配置マトリクス｜GugoPro EC戦略コラム</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>2026 越境EC・高精度リサーチ完全攻略：AIセマンティック・リバースエンジニアリングによるAmazonヒット商品開発、競合低評価（VOC）痛点分析とListingキーワード配置マトリクス</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2976,11 +2968,11 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>1</v>
@@ -2992,32 +2984,32 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>en/tools/health/tdee-macros-calculator.html</t>
+          <t>ja/articles/carb-cycling-and-home-workout-guide.html</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/health/tdee-macros-calculator.html</t>
+          <t>https://gugopro.com/ja/articles/carb-cycling-and-home-workout-guide.html</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - AI Nutritionist | GugoPro</t>
+          <t>炭水化物循環法（カーボサイクル）完全減脂ガイド：高・低炭水化物日の生化学機序、器具不要の自宅燃焼ルーティン、筋分解防止の極意｜GugoPro 運動生理学コラム</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>炭水化物循環法（カーボサイクル）完全減脂ガイド：高・低炭水化物日の生化学機序、器具不要の自宅燃焼ルーティン、筋分解防止の極意</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3027,14 +3019,14 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3043,32 +3035,32 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>en/tools/health/weight-loss-planner.html</t>
+          <t>ja/articles/diabetes-and-insulin-resistance-guide.html</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/en/tools/health/weight-loss-planner.html</t>
+          <t>https://gugopro.com/ja/articles/diabetes-and-insulin-resistance-guide.html</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Redirecting - AI Weight Loss Coach | GugoPro</t>
+          <t>糖尿病予備群・インスリン抵抗性の食事法完全ガイド：GI/GL値・カーボカウントからAI写真食事管理まで——血糖値スパイクを防ぐ栄養素調控｜GugoPro 代謝医学コラム</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>糖尿病予備群・インスリン抵抗性の食事法完全ガイド：GI/GL値・カーボカウントからAI写真食事管理まで——血糖値スパイクを防ぐ栄養素調控</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3078,14 +3070,14 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3094,24 +3086,32 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>googled0dfad57039c64f6.html</t>
+          <t>ja/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/googled0dfad57039c64f6.html</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
+          <t>https://gugopro.com/ja/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>脂肪肝を逆転する減糖＆地中海食完全ガイド：内臓脂肪燃焼からPFC黄金比率・外食AI管理まで——MASLDを根本改善する長寿実戦マニュアル｜GugoPro 肝臓代謝コラム</t>
+        </is>
+      </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>脂肪肝を逆転する減糖＆地中海食完全ガイド：内臓脂肪燃焼からPFC黄金比率・外食AI管理まで——MASLDを根本改善する長寿実戦マニュアル</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3137,32 +3137,32 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>index.html</t>
+          <t>ja/articles/gemini-api-free-tier-and-developer-guide.html</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/index.html</t>
+          <t>https://gugopro.com/ja/articles/gemini-api-free-tier-and-developer-guide.html</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>zh-TW</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>GugoPro 工具箱｜YouTube 雙語字幕學習、AI 翻譯塔羅、TDEE 減脂計算與 Gemini API 配額監控等 9 款免費工具</t>
+          <t>2026 開発者完全攻略ハンドブック：Google Gemini 公式無料APIを活用したゼロコスト商用グレードアプリのアーキテクチャ設計とエラー完全トラブルシューティング指南｜GugoPro クラウドシステムコラム</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>GugoPro 工具箱</t>
+          <t>2026 開発者完全攻略ハンドブック：Google Gemini 公式無料APIを活用したゼロコスト商用グレードアプリのアーキテクチャ設計とエラー完全トラブルシューティング指南</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>194</v>
+        <v>271</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>index_en.html</t>
+          <t>ja/articles/how-to-master-tarot-guide.html</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/index_en.html</t>
+          <t>https://gugopro.com/ja/articles/how-to-master-tarot-guide.html</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>GugoPro Hub | 9 Free Browser Tools for YouTube Study, AI Translation, Tarot, TDEE &amp; Gemini Quota</t>
+          <t>タロットマスターへの道：78枚の丸暗記を脱し「直観的フロー・リーディング」へ——古典記号論、ナラティブ心理学、AI協同による限界的練習完全ガイド｜GugoPro 意思決定科学コラム</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>GugoPro Hub</t>
+          <t>如何にしてタロットマスターとなるか？ 78枚の意味の丸暗記から「直観的フロー・リーディング」へ：古典記号論・ナラティブ心理学・AI協同による限界的練習完全手引</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>360</v>
+        <v>145</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3239,17 +3239,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>首頁</t>
+          <t>專欄文章</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>index_ja.html</t>
+          <t>ja/articles/how-to-master-ziwei-guide.html</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/index_ja.html</t>
+          <t>https://gugopro.com/ja/articles/how-to-master-ziwei-guide.html</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>GugoPro ツールボックス｜YouTube 2言語字幕学習、AI 翻訳タロット、TDEE 減脂計算、Gemini API 配額監視など無料ブラウザツール9選</t>
+          <t>紫微斗数マスターへの道：百の星の丸暗記を脱し「動態格局解盤」へ——文化記号論、システムダイナミクス、AI協同による限界的練習完全ガイド｜GugoPro 意思決定科学コラム</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>GugoPro ツールボックス</t>
+          <t>紫微斗数マスターへの道：百の星の丸暗記を脱し「動態格局解盤」へ——文化記号論、システムダイナミクス、AI協同による限界的練習完全ガイド</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/affective-filter-with-ai-tutor.html</t>
+          <t>ja/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/affective-filter-with-ai-tutor.html</t>
+          <t>https://gugopro.com/ja/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>話す恐怖を克服する心理学：クラッシェンの「情意フィルター仮説」、外国語不安（FLA）と AI チューターのゼロ圧力スピーキング完全ガイド｜GugoPro 言語学習コラム</t>
+          <t>168断食はカロリー計算より本当に痩せるのか？細胞自噬、インスリン仮説からエネルギー赤字の真相まで：リバウンドと筋肉減少の罠を解体する完全ガイド｜GugoPro 代謝内分泌コラム</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>話す恐怖を克服する心理学：クラッシェンの「情意フィルター仮説」、外国語不安（FLA）と AI チューターのゼロ圧力スピーキング完全ガイド</t>
+          <t>168断食はカロリー計算より本当に痩せるのか？細胞自噬、インスリン仮説からエネルギー赤字の真相まで：リバウンドと筋肉減少の罠を解体する完全ガイド</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>2</v>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/amazon-ai-product-research-guide.html</t>
+          <t>ja/articles/modern-ziwei-guide.html</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/amazon-ai-product-research-guide.html</t>
+          <t>https://gugopro.com/ja/articles/modern-ziwei-guide.html</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026 越境EC・高精度リサーチ完全攻略：AIセマンティック・リバースエンジニアリングによるAmazonヒット商品開発、競合低評価（VOC）痛点分析とListingキーワード配置マトリクス｜GugoPro EC戦略コラム</t>
+          <t>宿命論とオカルト的脅迫からの脱却：現代心理学で再構築する紫微斗数——十二宮位、四化の動態からAI意思決定反省モデルへ｜GugoPro 意思決定科学コラム</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>2026 越境EC・高精度リサーチ完全攻略：AIセマンティック・リバースエンジニアリングによるAmazonヒット商品開発、競合低評価（VOC）痛点分析とListingキーワード配置マトリクス</t>
+          <t>宿命論とオカルト的脅迫からの脱却：現代心理学で再構築する紫微斗数——十二宮位、四化の動態からAI意思決定反省モデルへ</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>227</v>
+        <v>169</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/carb-cycling-and-home-workout-guide.html</t>
+          <t>ja/articles/shadowing-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/carb-cycling-and-home-workout-guide.html</t>
+          <t>https://gugopro.com/ja/articles/shadowing-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3412,12 +3412,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>炭水化物循環法（カーボサイクル）完全減脂ガイド：高・低炭水化物日の生化学機序、器具不要の自宅燃焼ルーティン、筋分解防止の極意｜GugoPro 運動生理学コラム</t>
+          <t>「話せない英語」にサヨナラ！シャドーイング、CEFR文脈出力、AIチューターによるスピーキング実践ガイド｜GugoPro 言語科学コラム</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>炭水化物循環法（カーボサイクル）完全減脂ガイド：高・低炭水化物日の生化学機序、器具不要の自宅燃焼ルーティン、筋分解防止の極意</t>
+          <t>「話せない英語」にサヨナラ！シャドーイング、CEFR文脈輸出、AIチューターによるスピーキング実践ガイド</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>204</v>
+        <v>146</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>2</v>
@@ -3448,12 +3448,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/diabetes-and-insulin-resistance-guide.html</t>
+          <t>ja/articles/tarot-decision-framework.html</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/diabetes-and-insulin-resistance-guide.html</t>
+          <t>https://gugopro.com/ja/articles/tarot-decision-framework.html</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>糖尿病予備群・インスリン抵抗性の食事法完全ガイド：GI/GL値・カーボカウントからAI写真食事管理まで——血糖値スパイクを防ぐ栄養素調控｜GugoPro 代謝医学コラム</t>
+          <t>迷信的宿命論からの脱却：ユングの「元型」心理学・共時性からAIタロットへ——キャリアの二者択一と関係性不安を解体する構造化意思決定モデル｜GugoPro 意思決定科学コラム</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>糖尿病予備群・インスリン抵抗性の食事法完全ガイド：GI/GL値・カーボカウントからAI写真食事管理まで——血糖値スパイクを防ぐ栄養素調控</t>
+          <t>迷信的宿命論からの脱却：ユングの「元型」心理学・共時性からAIタロットへ——キャリアの二者択一と関係性不安を解体する構造化意思決定モデル</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>2</v>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
+          <t>ja/articles/tblt-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/fatty-liver-and-mediterranean-diet-guide.html</t>
+          <t>https://gugopro.com/ja/articles/tblt-with-ai-tutor.html</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>脂肪肝を逆転する減糖＆地中海食完全ガイド：内臓脂肪燃焼からPFC黄金比率・外食AI管理まで——MASLDを根本改善する長寿実戦マニュアル｜GugoPro 肝臓代謝コラム</t>
+          <t>丸暗記にサヨナラ！タスク型教授法（TBLT）、Robinson認知仮説とAIチューターによる英会話実践ガイド｜GugoPro 言語科学コラム</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>脂肪肝を逆転する減糖＆地中海食完全ガイド：内臓脂肪燃焼からPFC黄金比率・外食AI管理まで——MASLDを根本改善する長寿実戦マニュアル</t>
+          <t>丸暗記にサヨナラ！タスク型教授法（TBLT）、Robinson認知仮説とAIチューターによる英会話実践ガイド</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>2</v>
@@ -3550,12 +3550,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/gemini-api-free-tier-and-developer-guide.html</t>
+          <t>ja/articles/tdee-and-macros-guide.html</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/gemini-api-free-tier-and-developer-guide.html</t>
+          <t>https://gugopro.com/ja/articles/tdee-and-macros-guide.html</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026 開発者完全攻略ハンドブック：Google Gemini 公式無料APIを活用したゼロコスト商用グレードアプリのアーキテクチャ設計とエラー完全トラブルシューティング指南｜GugoPro クラウドシステムコラム</t>
+          <t>無駄な食事制限とリバウンドを完全に卒業！熱力学エネルギー収支、適応熱産生からAI食事解析まで：外食派のためのTDEE＆PFCバランス精密調整バイブル｜GugoPro 代謝健康專欄</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>2026 開発者完全攻略ハンドブック：Google Gemini 公式無料APIを活用したゼロコスト商用グレードアプリのアーキテクチャ設計とエラー完全トラブルシューティング指南</t>
+          <t>無駄な食事制限とリバウンドを完全に卒業！熱力学エネルギー収支、適応熱産生からAI食事解析まで：外食派のためのTDEE＆PFCバランス精密調整バイブル</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>2</v>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/how-to-master-tarot-guide.html</t>
+          <t>ja/articles/travel-translator-guide.html</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/how-to-master-tarot-guide.html</t>
+          <t>https://gugopro.com/ja/articles/travel-translator-guide.html</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>タロットマスターへの道：78枚の丸暗記を脱し「直観的フロー・リーディング」へ——古典記号論、ナラティブ心理学、AI協同による限界的練習完全ガイド｜GugoPro 意思決定科学コラム</t>
+          <t>スマホの気まずい手渡しにサヨナラ！180°対面反転UIのデザイン美学・HCI空間心理学と海外旅行会話実践ガイド｜GugoPro 異文化コミュニケーションコラム</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>如何にしてタロットマスターとなるか？ 78枚の意味の丸暗記から「直観的フロー・リーディング」へ：古典記号論・ナラティブ心理学・AI協同による限界的練習完全手引</t>
+          <t>スマホの気まずい手渡しにサヨナラ！180°対面反転UIのデザイン美学・HCI空間心理学と海外旅行会話実践ガイド</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>2</v>
@@ -3652,12 +3652,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/how-to-master-ziwei-guide.html</t>
+          <t>ja/articles/weight-loss-planner-guide.html</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/how-to-master-ziwei-guide.html</t>
+          <t>https://gugopro.com/ja/articles/weight-loss-planner-guide.html</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>紫微斗数マスターへの道：百の星の丸暗記を脱し「動態格局解盤」へ——文化記号論、システムダイナミクス、AI協同による限界的練習完全ガイド｜GugoPro 意思決定科学コラム</t>
+          <t>線形減量の幻想からの脱却！Wishnofsky 7700kcal法則の破綻からレジスタンストレーニング期分け・停滞期突破まで：動的減量計画とカロリー赤字完全ガイド｜GugoPro 運動生理学コラム</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>紫微斗数マスターへの道：百の星の丸暗記を脱し「動態格局解盤」へ——文化記号論、システムダイナミクス、AI協同による限界的練習完全ガイド</t>
+          <t>線形減量の幻想からの脱却！Wishnofsky 7700kcal法則の破綻からレジスタンストレーニング期分け・停滞期突破まで：動的減量計画とカロリー赤字完全ガイド</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>2</v>
@@ -3703,12 +3703,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
+          <t>ja/articles/youtube-english-listening-and-shadowing-guide.html</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/intermittent-fasting-and-calorie-deficit-guide.html</t>
+          <t>https://gugopro.com/ja/articles/youtube-english-listening-and-shadowing-guide.html</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>168断食はカロリー計算より本当に痩せるのか？細胞自噬、インスリン仮説からエネルギー赤字の真相まで：リバウンドと筋肉減少の罠を解体する完全ガイド｜GugoPro 代謝内分泌コラム</t>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイングで母語レベルの聴覚神経回路を構築する完全ガイド｜GugoPro 言語科学コラム</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>168断食はカロリー計算より本当に痩せるのか？細胞自噬、インスリン仮説からエネルギー赤字の真相まで：リバウンドと筋肉減少の罠を解体する完全ガイド</t>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>233</v>
+        <v>161</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>2</v>
@@ -3754,12 +3754,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/modern-ziwei-guide.html</t>
+          <t>ja/articles/youtube-listening-connected-speech-guide.html</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/modern-ziwei-guide.html</t>
+          <t>https://gugopro.com/ja/articles/youtube-listening-connected-speech-guide.html</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>宿命論とオカルト的脅迫からの脱却：現代心理学で再構築する紫微斗数——十二宮位、四化の動態からAI意思決定反省モデルへ｜GugoPro 意思決定科学コラム</t>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイング完全ガイド｜GugoPro 言語科学コラム</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>宿命論とオカルト的脅迫からの脱却：現代心理学で再構築する紫微斗数——十二宮位、四化の動態からAI意思決定反省モデルへ</t>
+          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>2</v>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/shadowing-with-ai-tutor.html</t>
+          <t>ja/articles/youtube-sequel-tracker-guide.html</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/shadowing-with-ai-tutor.html</t>
+          <t>https://gugopro.com/ja/articles/youtube-sequel-tracker-guide.html</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>「話せない英語」にサヨナラ！シャドーイング、CEFR文脈出力、AIチューターによるスピーキング実践ガイド｜GugoPro 言語科学コラム</t>
+          <t>2026年YouTube動画推薦アルゴリズムとシリーズ検索完全ガイド：推薦漏れを解消しNLP正規表現ノイズ除去と差分照合で跨チャンネル追跡を実現する｜GugoPro ストリーミング研究コラム</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>「話せない英語」にサヨナラ！シャドーイング、CEFR文脈輸出、AIチューターによるスピーキング実践ガイド</t>
+          <t>2026年YouTube動画推薦アルゴリズムとシリーズ検索完全ガイド：推薦漏れを解消し NLP正規表現ノイズ除去と差分照合 で跨チャンネル追跡を実現する</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>146</v>
+        <v>224</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>2</v>
@@ -3851,32 +3851,32 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>法律條款</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/tarot-decision-framework.html</t>
+          <t>privacy.html</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/tarot-decision-framework.html</t>
+          <t>https://gugopro.com/privacy.html</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>迷信的宿命論からの脱却：ユングの「元型」心理学・共時性からAIタロットへ——キャリアの二者択一と関係性不安を解体する構造化意思決定モデル｜GugoPro 意思決定科学コラム</t>
+          <t>隱私權政策｜GugoPro</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>迷信的宿命論からの脱却：ユングの「元型」心理学・共時性からAIタロットへ——キャリアの二者択一と関係性不安を解体する構造化意思決定モデル</t>
+          <t>隱私權政策</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3902,32 +3902,32 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>法律條款</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/tblt-with-ai-tutor.html</t>
+          <t>terms.html</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/tblt-with-ai-tutor.html</t>
+          <t>https://gugopro.com/terms.html</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>丸暗記にサヨナラ！タスク型教授法（TBLT）、Robinson認知仮説とAIチューターによる英会話実践ガイド｜GugoPro 言語科学コラム</t>
+          <t>服務條款｜GugoPro</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>丸暗記にサヨナラ！タスク型教授法（TBLT）、Robinson認知仮説とAIチューターによる英会話実践ガイド</t>
+          <t>服務條款</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>184</v>
+        <v>49</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -3953,32 +3953,32 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/tdee-and-macros-guide.html</t>
+          <t>tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/tdee-and-macros-guide.html</t>
+          <t>https://gugopro.com/tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>無駄な食事制限とリバウンドを完全に卒業！熱力学エネルギー収支、適応熱産生からAI食事解析まで：外食派のためのTDEE＆PFCバランス精密調整バイブル｜GugoPro 代謝健康專欄</t>
+          <t>AI多國語言對話導師</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>無駄な食事制限とリバウンドを完全に卒業！熱力学エネルギー収支、適応熱産生からAI食事解析まで：外食派のためのTDEE＆PFCバランス精密調整バイブル</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>248</v>
+        <v>65</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4004,32 +4004,32 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/travel-translator-guide.html</t>
+          <t>tools/ai/gemini-api-quota.html</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/travel-translator-guide.html</t>
+          <t>https://gugopro.com/tools/ai/gemini-api-quota.html</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>スマホの気まずい手渡しにサヨナラ！180°対面反転UIのデザイン美学・HCI空間心理学と海外旅行会話実践ガイド｜GugoPro 異文化コミュニケーションコラム</t>
+          <t>Gemini API 配額服務導覽｜GugoPro</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>スマホの気まずい手渡しにサヨナラ！180°対面反転UIのデザイン美学・HCI空間心理学と海外旅行会話実践ガイド</t>
+          <t>Gemini API 配額服務導覽</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>206</v>
+        <v>61</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4055,32 +4055,32 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/weight-loss-planner-guide.html</t>
+          <t>tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/weight-loss-planner-guide.html</t>
+          <t>https://gugopro.com/tools/ai/realtime-translator.html</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>線形減量の幻想からの脱却！Wishnofsky 7700kcal法則の破綻からレジスタンストレーニング期分け・停滞期突破まで：動的減量計画とカロリー赤字完全ガイド｜GugoPro 運動生理学コラム</t>
+          <t>面對面旅遊對話翻譯｜出國旅遊即時翻譯與雙向語音對話｜GugoPro</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>線形減量の幻想からの脱却！Wishnofsky 7700kcal法則の破綻からレジスタンストレーニング期分け・停滞期突破まで：動的減量計画とカロリー赤字完全ガイド</t>
+          <t>面對面旅遊對話翻譯：出國旅遊即時翻譯與雙向語音對話</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4094,10 +4094,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4106,32 +4106,32 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/youtube-english-listening-and-shadowing-guide.html</t>
+          <t>tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/youtube-english-listening-and-shadowing-guide.html</t>
+          <t>https://gugopro.com/tools/ai/tarot-master.html</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイングで母語レベルの聴覚神経回路を構築する完全ガイド｜GugoPro 言語科学コラム</t>
+          <t>AI 塔羅大師｜五種塔羅牌陣、提問指南與自我反思 - GugoPro</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>161</v>
+        <v>63</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4157,32 +4157,32 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/youtube-listening-connected-speech-guide.html</t>
+          <t>tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/youtube-listening-connected-speech-guide.html</t>
+          <t>https://gugopro.com/tools/ai/ziwei-astrology.html</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイング完全ガイド｜GugoPro 言語科学コラム</t>
+          <t>AI 紫微斗數大師｜紫微斗數線上排盤資料整理與十二宮位指南 - GugoPro</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
+          <t>把命盤問題，整理成可行動的洞察</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4208,32 +4208,32 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>專欄文章</t>
+          <t>核心工具</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>ja/articles/youtube-sequel-tracker-guide.html</t>
+          <t>tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/articles/youtube-sequel-tracker-guide.html</t>
+          <t>https://gugopro.com/tools/ai-media/ai-video-tracker.html</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026年YouTube動画推薦アルゴリズムとシリーズ検索完全ガイド：推薦漏れを解消しNLP正規表現ノイズ除去と差分照合で跨チャンネル追跡を実現する｜GugoPro ストリーミング研究コラム</t>
+          <t>YouTube 續集與新季追蹤器 - GugoPro</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>2026年YouTube動画推薦アルゴリズムとシリーズ検索完全ガイド：推薦漏れを解消し NLP正規表現ノイズ除去と差分照合 で跨チャンネル追跡を実現する</t>
+          <t>YouTube 續集與新季追蹤器</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4243,14 +4243,14 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>✅ 已配置</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>224</v>
+        <v>112</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4264,41 +4264,41 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/ai/english-speaking-tutor.html</t>
+          <t>tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/ai/english-speaking-tutor.html</t>
+          <t>https://gugopro.com/tools/english/l-player-study.html</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - AI多言語スピーキングチューター | GugoPro</t>
+          <t>【AB English Podcast】Ep.1 自我介紹與日常社交對話 (Mia &amp; Alex)｜L-Player</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>YouTube 影音「聽・寫・口說」多國語言跟讀器</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>可見</t>
+          <t>疑似隱藏</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>1</v>
@@ -4315,22 +4315,22 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/ai/realtime-translator.html</t>
+          <t>tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/ai/realtime-translator.html</t>
+          <t>https://gugopro.com/tools/health/tdee-macros-calculator.html</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - 対面型リアルタイム音声翻訳 | GugoPro</t>
+          <t>AI 專屬營養師 | GugoPro</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -4345,11 +4345,11 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>1</v>
@@ -4366,22 +4366,22 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/ai/tarot-master.html</t>
+          <t>tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/ai/tarot-master.html</t>
+          <t>https://gugopro.com/tools/health/weight-loss-planner.html</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - AIタロットマスター | GugoPro</t>
+          <t>AI減肥瘦身教練｜科學減脂與熱量赤字規劃 | GugoPro</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -4396,11 +4396,11 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>1</v>
@@ -4412,32 +4412,32 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/ai/ziwei-astrology.html</t>
+          <t>tools/pdf/pdf-suite.html</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/ai/ziwei-astrology.html</t>
+          <t>https://gugopro.com/tools/pdf/pdf-suite.html</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - AI紫微斗数マスター | GugoPro</t>
+          <t>PDF 全能工作站｜免安裝線上閱讀、合併、分割與標註、零檔案外洩 - GugoPro</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>先選擇要處理的文件</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4447,11 +4447,11 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>❌ 未配置（合規）</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>1</v>
@@ -4463,32 +4463,32 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>實用教學</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/ai-media/ai-video-tracker.html</t>
+          <t>tools/tutorials/how-to-get-gemini-api-key.html</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/ai-media/ai-video-tracker.html</t>
+          <t>https://gugopro.com/tools/tutorials/how-to-get-gemini-api-key.html</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-TW</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - YouTube続編追跡 | GugoPro</t>
+          <t>Gemini API Key 申請教學｜Google Gemini API Key 取得與安全設定教學、免安裝與隱私說明 - GugoPro</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>Google Gemini API Key 1 分鐘快速申請步驟</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4498,11 +4498,11 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>1</v>
@@ -4514,32 +4514,32 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>核心工具</t>
+          <t>歷史工具</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>ja/tools/english/l-player-study.html</t>
+          <t>tools/tw-market/taiwan-pair-trading.html</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/ja/tools/english/l-player-study.html</t>
+          <t>https://gugopro.com/tools/tw-market/taiwan-pair-trading.html</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>zh-Hant-TW</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>リダイレクト中 - YouTube学習プレイヤー | GugoPro</t>
+          <t>Taiwan Pair Trading 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>台灣股票與期貨 配對交易掃描工作站</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4549,834 +4549,18 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>❌ 未配置（合規）</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="K80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K80" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>ja/tools/health/tdee-macros-calculator.html</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/tools/health/tdee-macros-calculator.html</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>リダイレクト中 - AI栄養士 | GugoPro</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>ja/tools/health/weight-loss-planner.html</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/ja/tools/health/weight-loss-planner.html</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>リダイレクト中 - AI減量コーチ | GugoPro</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>法律條款</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>privacy.html</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/privacy.html</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>隱私權政策｜GugoPro</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>隱私權政策</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="K83" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>法律條款</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>terms.html</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/terms.html</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>服務條款｜GugoPro</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>服務條款</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="K84" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>tools/ai/english-speaking-tutor.html</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/ai/english-speaking-tutor.html</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>AI多國語言對話導師</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="K85" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>tools/ai/gemini-api-quota.html</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/ai/gemini-api-quota.html</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>Gemini API 配額服務導覽｜GugoPro</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>Gemini API 配額服務導覽</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="K86" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>tools/ai/realtime-translator.html</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/ai/realtime-translator.html</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>面對面旅遊對話翻譯｜出國旅遊即時翻譯與雙向語音對話｜GugoPro</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>面對面旅遊對話翻譯：出國旅遊即時翻譯與雙向語音對話</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="K87" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>tools/ai/tarot-master.html</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/ai/tarot-master.html</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>AI 塔羅大師｜五種塔羅牌陣、提問指南與自我反思 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="K88" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>tools/ai/ziwei-astrology.html</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/ai/ziwei-astrology.html</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>AI 紫微斗數大師｜紫微斗數線上排盤資料整理與十二宮位指南 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>把命盤問題，整理成可行動的洞察</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="K89" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>tools/ai-media/ai-video-tracker.html</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/ai-media/ai-video-tracker.html</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>YouTube 續集與新季追蹤器 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>YouTube 續集與新季追蹤器</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="K90" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>tools/english/l-player-study.html</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/english/l-player-study.html</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>【AB English Podcast】Ep.1 自我介紹與日常社交對話 (Mia &amp; Alex)｜L-Player</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>YouTube 影音「聽・寫・口說」多國語言跟讀器</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>疑似隱藏</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="K91" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>tools/health/tdee-macros-calculator.html</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/health/tdee-macros-calculator.html</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>AI 專屬營養師 | GugoPro</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="K92" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>核心工具</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>tools/health/weight-loss-planner.html</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/health/weight-loss-planner.html</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>AI減肥瘦身教練｜科學減脂與熱量赤字規劃 | GugoPro</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>❌ 缺失</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="K93" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>tools/pdf/pdf-suite.html</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/pdf/pdf-suite.html</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>PDF 全能工作站｜免安裝線上閱讀、合併、分割與標註、零檔案外洩 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>先選擇要處理的文件</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>❌ 未配置（合規）</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="K94" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>實用教學</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>tools/tutorials/how-to-get-gemini-api-key.html</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/tutorials/how-to-get-gemini-api-key.html</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>Gemini API Key 申請教學｜Google Gemini API Key 取得與安全設定教學、免安裝與隱私說明 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>Google Gemini API Key 1 分鐘快速申請步驟</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>tools/tw-market/taiwan-pair-trading.html</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/tw-market/taiwan-pair-trading.html</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>zh-Hant-TW</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>Taiwan Pair Trading 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>台灣股票與期貨 配對交易掃描工作站</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>❌ 未配置（合規）</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K96"/>
+  <autoFilter ref="A1:K80"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -5457,26 +4641,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId96"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId80"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5513,7 +4681,7 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
@@ -5533,7 +4701,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -5593,7 +4761,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5603,7 +4771,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -5623,7 +4791,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/seo_inventory_report.xlsx
+++ b/seo_inventory_report.xlsx
@@ -2771,7 +2771,7 @@
         <v>194</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>tools/ai/english-speaking-tutor.html</t>
+          <t>tools/ai/amazon-product-research.html</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/ai/english-speaking-tutor.html</t>
+          <t>https://gugopro.com/tools/ai/amazon-product-research.html</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>AI多國語言對話導師</t>
+          <t>Amazon AI 全品類智能選品導購 | GugoPro</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>🛒 Amazon AI 智能購物導師</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>1</v>
@@ -4009,12 +4009,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>tools/ai/gemini-api-quota.html</t>
+          <t>tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/ai/gemini-api-quota.html</t>
+          <t>https://gugopro.com/tools/ai/english-speaking-tutor.html</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Gemini API 配額服務導覽｜GugoPro</t>
+          <t>AI多國語言對話導師</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Gemini API 配額服務導覽</t>
+          <t>❌ 缺失</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/seo_inventory_report.xlsx
+++ b/seo_inventory_report.xlsx
@@ -666,12 +666,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>克服開口恐懼的心理學解方：克拉申「情意濾網假說」、外語焦慮（FLA）與 AI 導師的零壓力口說閉環｜GugoPro 語言學習專欄</t>
+          <t>克服開口恐懼的心理學：克拉申情意濾網假說與 AI 零壓力口說｜GugoPro</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>克服開口恐懼的心理學解方：克拉申「情意濾網假說」、外語焦慮（FLA）與 AI 導師的零壓力口說閉環</t>
+          <t>克服外語開口焦慮 (FLA)：情意濾網假說與 AI 導師的零壓力脫敏閉環</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -717,12 +717,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026 跨境電商與高階海淘全指南：如何利用 AI 語意反向工程打造 Amazon 爆款選品、競品差評痛點挖掘與 Listing 關鍵字佈局矩陣｜GugoPro 電商戰略專欄</t>
+          <t>2026 Amazon 跨境選品全指南：AI 語意反向工程與差評痛點挖掘｜GugoPro</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026 跨境電商與高階海淘全指南：如何利用 AI 語意反向工程打造 Amazon 爆款選品、競品差評痛點挖掘與 Listing 關鍵字佈局矩陣</t>
+          <t>跨境電商 Amazon AI 爆款選品指南：利用語意反向工程與差評痛點逆向研發</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>碳水循環法（Carb Cycling）怎麼吃最減脂？高低碳日生化機制、居家無器材燃脂課表與防止掉肌肉全攻略｜GugoPro 減脂運動生理學專欄</t>
+          <t>碳水循環法怎麼吃？高低碳日生化機制與居家燃脂課表全攻略｜GugoPro</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>碳水循環法（Carb Cycling）怎麼吃最減脂？高低碳日生化機制、居家無器材燃脂課表與防止掉肌肉全攻略</t>
+          <t>碳水循環法 (Carb Cycling) 減脂攻略：高低碳日生化機制與增肌防掉肉課表</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>糖尿病前期與胰島素阻抗怎麼吃？從升糖指數（GI/GL）、碳水計數到 AI 拍餐：告別血糖震盪的巨量營養素調控全指南｜GugoPro 慢病代謝專欄</t>
+          <t>糖尿病前期與胰島素阻抗怎麼吃？GI/GL 值與碳水計數全指南｜GugoPro</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>糖尿病前期與胰島素阻抗怎麼吃？從升糖指數（GI/GL）、碳水計數到 AI 拍餐：告別血糖震盪的巨量營養素調控全指南</t>
+          <t>糖尿病前期與胰島素阻抗飲食指南：從升糖指數 (GI/GL) 到進食順序控糖</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>減醣飲食與地中海飲食怎麼吃？從逆轉脂肪肝、內臟脂肪燃燒到三大營養素黃金配比：外食族健康長壽實戰手冊｜GugoPro 肝臟代謝專欄</t>
+          <t>脂肪肝怎麼逆轉？減醣與改良地中海飲食外食健康實戰手冊｜GugoPro</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>減醣飲食與地中海飲食怎麼吃？從逆轉脂肪肝、內臟脂肪燃燒到三大營養素黃金配比：外食族健康長壽實戰手冊</t>
+          <t>逆轉脂肪肝 (MASLD) 全指南：減醣地中海飲食黃金配比與外食避坑手冊</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026 終極開發者手冊：利用 Google Gemini 官方免費 API 打造零成本商用級應用之架構設計與故障排除全指南｜GugoPro 雲端系統專欄</t>
+          <t>2026 Google Gemini 免費 API 開發手冊：架構設計與429錯誤排查｜GugoPro</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2026 終極開發者手冊：利用 Google Gemini 官方免費 API 打造零成本商用級應用之架構設計與故障排除全指南</t>
+          <t>Google Gemini 官方免費 API 開發者手冊：零成本商用架構與高可用 Failover</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>如何成為塔羅牌大師？從 78 張牌義生吞活剝到「直覺流動解牌」：結合古典符號學、敘事心理學與 AI 協同實戰刻意練習全指南｜GugoPro 決策科學專欄</t>
+          <t>如何成為塔羅牌大師？78張牌古典符號學與直覺流動解牌全指南｜GugoPro</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>如何成為塔羅牌大師？從 78 張牌義生吞活剝到「直覺流動解牌」：結合古典符號學、敘事心理學與 AI 協同實戰刻意練習全指南</t>
+          <t>如何成為塔羅牌大師：從死記牌義到直覺流動解牌的刻意練習指南</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>如何成為紫微斗數大師？從死背百顆星曜到「動態格局解盤」：結合文化符號學、系統動力學與 AI 協同實戰刻意練習全指南｜GugoPro 決策科學專欄</t>
+          <t>如何成為紫微斗數大師？百顆星曜文化符號學與動態格局解盤｜GugoPro</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>如何成為紫微斗數大師？從死背百顆星曜到「動態格局解盤」：結合文化符號學、系統動力學與 AI 協同實戰刻意練習全指南</t>
+          <t>如何成為紫微斗數大師：從死背星曜到動態格局解盤的系統動力學手冊</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>168 斷食真的比算熱量有效嗎？從自噬反應、胰島素假說到熱量赤字真相：打破越斷越肥的復胖陷阱｜GugoPro 減脂代謝專欄</t>
+          <t>168 斷食真的比算熱量有效嗎？自噬反應真相與熱量赤字指南｜GugoPro</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>168 斷食真的比算熱量有效嗎？從自噬反應、胰島素假說到熱量赤字真相：打破越斷越肥的復胖陷阱</t>
+          <t>168 斷食與熱量赤字真相對決：揭密自噬反應、皮質醇危機與防復胖課表</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>告別宿命論與玄學恐嚇！用現代心理學重構紫微斗數：從十二宮位、四化動態到 AI 決策反思模型｜GugoPro 決策科學專欄</t>
+          <t>告別玄學恐嚇！現代心理學重構紫微斗數：十二宮位與四化反思｜GugoPro</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>告別宿命論與玄學恐嚇！用現代心理學重構紫微斗數：從十二宮位、四化動態到 AI 決策反思模型</t>
+          <t>用現代心理學重構紫微斗數：解鎖十二宮位、四化動態與人際合盤反思</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>擺脫「啞巴英語」的科學自學法：結合影子跟讀（Shadowing）、CEFR 脈絡輸出與 AI 導師的高效閉環｜GugoPro 語言學習專欄</t>
+          <t>擺脫「啞巴英語」科學自學法：影子跟讀、CEFR 輸出與 AI 導師｜GugoPro</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>擺脫「啞巴英語」的科學自學法：結合影子跟讀（Shadowing）、CEFR 脈絡輸出與 AI 導師的高效閉環</t>
+          <t>擺脫啞巴英語的科學自學法：影子跟讀、CEFR 輸出與 AI 即時回饋閉環</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>告別迷信宿命論！從榮格「原型」心理學、共時性到 AI 塔羅：拆解職涯二選一與感情焦慮的結構化決策模型｜GugoPro 決策科學專欄</t>
+          <t>告別迷信宿命論！榮格原型心理學、共時性與 AI 塔羅決策模型｜GugoPro</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>告別迷信宿命論！從榮格「原型」心理學、共時性到 AI 塔羅：拆解職涯二選一與感情焦慮的結構化決策模型</t>
+          <t>榮格原型心理學與結構化塔羅：職涯二選一與感情焦慮的理性決策模型</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>告別死記硬背！結合任務型教學法（TBLT）、Robinson 認知假說與 AI 導師的高效口說實戰指南｜GugoPro 語言學習專欄</t>
+          <t>告別死背單字文法！任務型語言教學 (TBLT) 與 AI 口說實戰手冊｜GugoPro</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>告別死記硬背！結合任務型教學法（TBLT）、Robinson 認知假說與 AI 導師的高效口說實戰指南</t>
+          <t>任務型語言教學 (TBLT) 實戰全指南：用 AI 打造沉浸式口說任務卡</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>告別無效節食與溜溜球效應！從能量平衡熱力學、自適應產熱到 AI 拍餐估算：外食族 TDEE 與三大營養素精準調控全指南｜GugoPro 代謝健康專欄</t>
+          <t>告別溜溜球效應！TDEE 熱量計算、三大營養素與外食拍餐指南｜GugoPro</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>告別無效節食與溜溜球效應！從能量平衡熱力學、自適應產熱到 AI 拍餐估算：外食族 TDEE 與三大營養素精準調控全指南</t>
+          <t>TDEE 與三大營養素精準調控全指南：能量平衡熱力學與外食減脂手冊</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>告別尷尬遞手機！180° 面對面翻轉介面的設計美學、人機互動（HCI）空間心理學與出國溝通實戰指南｜GugoPro 跨文化專欄</t>
+          <t>告別尷尬遞手機！180° 對向翻轉介面與出國即時語音翻譯手冊｜GugoPro</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>告別尷尬遞手機！180° 面對面翻轉介面的設計美學、人機互動（HCI）空間心理學與出國溝通實戰指南</t>
+          <t>告別尷尬遞手機：180° 面對面翻轉介面設計美學與出國旅遊溝通實戰</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>告別線性減重迷思！從 Wishnofsky 7700大卡法則失真、阻力訓練期程化到停滯期突破：動態減脂計畫與熱量赤字全指南｜GugoPro 運動生理學專欄</t>
+          <t>告別7700大卡迷思！動態熱量赤字與突破減重停滯期全指南｜GugoPro</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>告別線性減重迷思！從 Wishnofsky 7700大卡法則失真、阻力訓練期程化到停滯期突破：動態減脂計畫與熱量赤字全指南</t>
+          <t>告別線性減重迷思：Wishnofsky 法則失真、動態減脂計畫與停滯期突破</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>解鎖 YouTube 雙語精聽與影子跟讀：L-Player 零摩擦學習系統操作全書與神經聽覺重塑指南｜GugoPro 語言科學專欄</t>
+          <t>YouTube 雙語精聽與影子跟讀全書：L-Player 操作與神經聽覺重塑｜GugoPro</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>解鎖 YouTube 雙語精聽與影子跟讀： L-Player 零摩擦學習系統操作全書與神經聽覺重塑指南</t>
+          <t>YouTube 雙語精聽與影子跟讀：L-Player 零摩擦學習系統操作全書</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>看 YouTube 學英文為何總是無效？結合音韻知覺理論、Levenshtein 聽寫差量比對與影子跟讀（Shadowing）打造母語聽覺神經迴路全指南｜GugoPro 語言科學專欄</t>
+          <t>看 YouTube 學英文為何聽不懂？音韻知覺與聽寫差量比對全指南｜GugoPro</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>看 YouTube 學英文為何總是無效？結合音韻知覺理論、 Levenshtein 聽寫差量比對與影子跟讀（Shadowing） 打造母語聽覺神經迴路全指南</t>
+          <t>破解英語聽力盲區：語流音變、聽寫差量比對與影子跟讀自學指南</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026 YouTube 影音演算法與連載檢索全指南：如何破解推薦漏片迷思、利用 NLP 正則去噪與差量比對打造跨頻道追劇閉環｜GugoPro 串流媒體研究專欄</t>
+          <t>2026 YouTube 演算法與連載檢索：NLP 去噪與跨頻道追劇指南｜GugoPro</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026 YouTube 影音演算法與連載檢索全指南：如何破解推薦漏片迷思、利用 NLP 正則去噪與差量比對 打造跨頻道追劇閉環</t>
+          <t>YouTube 演算法與連載檢索指南：破解推薦漏片與跨頻道續集追蹤技術</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Fear of Speaking: Krashen's Affective Filter, Foreign Language Anxiety (FLA), and Zero-Pressure AI Tutoring | GugoPro Language Science</t>
+          <t>Overcoming Speaking Fear: Krashen's Affective Filter &amp; AI Tutoring | GugoPro</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Overcoming the Fear of Speaking: Krashen's Affective Filter, Foreign Language Anxiety (FLA), and Zero-Pressure AI Tutoring</t>
+          <t>Overcoming Foreign Language Anxiety: Affective Filter &amp; Zero-Pressure AI</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026 Cross-Border E-Commerce &amp; Global Sourcing Master Guide: Leveraging AI Semantic Reverse Engineering for Amazon Product Research, Negative Review Mining, and Listing Matrix Architecture | GugoPro Strategy Column</t>
+          <t>2026 Amazon AI Product Research: Review Mining &amp; Listing Guide | GugoPro</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2026 Cross-Border E-Commerce &amp; Global Sourcing Master Guide: Leveraging AI Semantic Reverse Engineering for Amazon Product Research, Negative Review Mining, and Listing Keyword Matrix Architecture</t>
+          <t>Amazon AI Product Research Guide: Semantic Reverse Engineering &amp; Review Mining</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>How to Master Carb Cycling for Maximum Fat Loss: High/Low Carb Biochemistry, Home Bodyweight Workout Splits, and Preserving Muscle Mass | GugoPro Exercise Physiology Column</t>
+          <t>Master Carb Cycling for Fat Loss: High/Low Days &amp; Home Workouts | GugoPro</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>How to Master Carb Cycling for Maximum Fat Loss: High/Low Carb Biochemistry, Home Bodyweight Workout Splits, and Preserving Muscle Mass</t>
+          <t>How to Master Carb Cycling for Maximum Fat Loss: Biochemistry &amp; Bodyweight</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>What to Eat for Prediabetes and Insulin Resistance? From GI/GL and Carb Counting to AI Meal Tracking: The Definitive Macronutrient Guide to Ending Glucose Spikes | GugoPro Metabolic Science Column</t>
+          <t>Prediabetes &amp; Insulin Resistance Diet Guide: GI/GL &amp; Carb Control | GugoPro</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>What to Eat for Prediabetes and Insulin Resistance? From GI/GL and Carb Counting to AI Meal Tracking: The Definitive Macronutrient Guide to Ending Glucose Spikes</t>
+          <t>What to Eat for Prediabetes &amp; Insulin Resistance: GI/GL &amp; Carb Counting</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>What to Eat for Fatty Liver: Low-Carb vs. Mediterranean Diet? From Reversing Hepatic Steatosis &amp; Visceral Fat to Optimal Macronutrient Ratios: The Dining-Out Longevity Handbook | GugoPro Liver Metabolism Column</t>
+          <t>Reversing Fatty Liver: Low-Carb vs. Mediterranean Diet Handbook | GugoPro</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>What to Eat for Fatty Liver: Low-Carb vs. Mediterranean Diet? From Reversing Hepatic Steatosis &amp; Visceral Fat to Optimal Macronutrient Ratios: The Dining-Out Longevity Handbook</t>
+          <t>What to Eat to Reverse Fatty Liver (MASLD): Mediterranean Diet &amp; Fat Loss</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026 Developer Blueprint: Building Zero-Cost Commercial-Grade Apps with Google Gemini Free API &amp; Comprehensive Error Troubleshooting Guide | GugoPro Cloud Systems Column</t>
+          <t>2026 Google Gemini Free API Developer Blueprint &amp; Rate Limits | GugoPro</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026 Developer Blueprint: Building Zero-Cost Commercial-Grade Apps with Google Gemini Free API &amp; Comprehensive Error Troubleshooting Guide</t>
+          <t>Building Zero-Cost Commercial Apps with Gemini Free API: Architecture &amp; Failover</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Tarot Master? From Rote Memorization to Intuitive Flow Reading: A Deliberate Practice Guide Combining Classical Semiotics, Narrative Psychology, and AI Collaboration | GugoPro Decision Science Column</t>
+          <t>How to Master Tarot: Classical Semiotics &amp; Intuitive Reading | GugoPro</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Tarot Master? From Rote Memorization to "Intuitive Flow Reading": A Comprehensive Deliberate Practice Guide Combining Classical Semiotics, Narrative Psychology, and AI Collaboration</t>
+          <t>Mastering Tarot: From Rote Memorization to Intuitive Flow Reading with AI</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2094,12 +2094,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Ziwei Astrology Master? From Rote Memorization to Dynamic Pattern Reading: A Deliberate Practice Guide Combining Cultural Semiotics, System Dynamics, and AI Collaboration | GugoPro Decision Science Column</t>
+          <t>How to Master Zi Wei Dou Shu: Dynamic Natal Chart Reading | GugoPro</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Ziwei Astrology Master? From Rote Memorization of 108 Stars to "Dynamic Pattern Reading": A Deliberate Practice Guide Combining Cultural Semiotics, System Dynamics, and AI Collaboration</t>
+          <t>Mastering Zi Wei Dou Shu: From 108 Stars to Dynamic Pattern Chart Reading</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Is 16:8 Intermittent Fasting Really Better Than Counting Calories? From Autophagy and the Insulin Hypothesis to Caloric Deficit Realities: Escaping the Fasting Rebound Trap | GugoPro Metabolic Science Column</t>
+          <t>Is 16:8 Fasting Better Than Counting Calories? Autophagy Truth | GugoPro</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Is 16:8 Intermittent Fasting Really Better Than Counting Calories? From Autophagy and the Insulin Hypothesis to Caloric Deficit Realities: Escaping the Fasting Rebound Trap</t>
+          <t>Is 16:8 Intermittent Fasting Really Better Than Counting Calories? Science Decoded</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2196,12 +2196,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Farewell to Fatalism and Esoteric Intimidation! Reconstructing Ziwei Astrology with Modern Psychology: From Twelve Palaces and Si-Hua Dynamics to AI Decision Reflection Models | GugoPro Decision Science Column</t>
+          <t>Modernizing Zi Wei Dou Shu: Twelve Palaces &amp; Psychological Growth | GugoPro</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Farewell to Fatalism and Esoteric Intimidation! Reconstructing Ziwei Astrology with Modern Psychology: From Twelve Palaces and Si-Hua Dynamics to AI Decision Reflection Models</t>
+          <t>Reconstructing Zi Wei Dou Shu with Modern Psychology: Twelve Palaces &amp; Si-Hua</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Overcoming 'Mute English': Shadowing, CEFR Output, and AI Tutoring for Fluent Speaking | GugoPro Language Science</t>
+          <t>Overcoming Mute English: Shadowing, CEFR Output &amp; AI Tutoring | GugoPro</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Overcoming 'Mute English': Shadowing, CEFR Output, and AI Tutoring for Fluent Speaking</t>
+          <t>Science-Backed Autonomous Speaking: Shadowing, CEFR Output &amp; AI Dialogue</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Farewell to Fatalism: From Jungian Archetypal Psychology and Synchronicity to AI Tarot: Deconstructing Career Dilemmas and Relationship Anxiety via Structured Decision Models | GugoPro Decision Science Column</t>
+          <t>Tarot Decision Framework: Jungian Archetypes &amp; Synchronicity | GugoPro</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Farewell to Fatalism: From Jungian Archetypal Psychology and Synchronicity to AI Tarot: Deconstructing Career Dilemmas and Relationship Anxiety via Structured Decision Models</t>
+          <t>Deconstructing Dilemmas: Jungian Archetypal Psychology &amp; AI Tarot Decisions</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Beyond Rote Memorization: Task-Based Language Teaching (TBLT), Robinson's Cognition Hypothesis, and High-Impact Speaking with AI | GugoPro Language Science</t>
+          <t>Task-Based Language Teaching (TBLT): High-Impact Speaking with AI | GugoPro</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Beyond Rote Memorization: Task-Based Language Teaching (TBLT), Robinson's Cognition Hypothesis, and High-Impact Speaking with AI</t>
+          <t>Beyond Rote Memorization: Task-Based Language Teaching (TBLT) with AI</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Defeat Chronic Dieting &amp; Yo-Yo Rebound: The Complete Scientific Guide to TDEE, Adaptive Thermogenesis &amp; Macronutrient Control for Dining Out | GugoPro Metabolic Health Column</t>
+          <t>Defeat Yo-Yo Dieting: The Complete Science Guide to TDEE &amp; Macros | GugoPro</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Defeat Chronic Dieting &amp; Yo-Yo Rebound: The Complete Scientific Guide to TDEE, Adaptive Thermogenesis &amp; Macronutrient Control for Dining Out</t>
+          <t>Mastering TDEE &amp; Macronutrients: Energy Balance Thermodynamics &amp; Dining Out</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Say Goodbye to Awkward Phone-Passing! 180° Face-to-Face Flipped UI Design, HCI Spatial Psychology, and Practical Travel Communication Guide | GugoPro Cross-Cultural Column</t>
+          <t>No More Passing Phones: 180° Flipped Screen Travel Translator | GugoPro</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Say Goodbye to Awkward Phone-Passing! 180° Face-to-Face Flipped UI Design, HCI Spatial Psychology, and Practical Travel Communication Guide</t>
+          <t>Say Goodbye to Awkward Phone-Passing! 180° Face-to-Face Flipped UI Design</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Beyond Linear Weight Loss Myths: From Wishnofsky's 7,700 kcal Rule Flaws to Resistance Periodization and Plateau Breakthroughs: The Definitive Dynamic Fat Loss &amp; Caloric Deficit Guide | GugoPro Exercise Physiology Column</t>
+          <t>Beyond 7,700 kcal Myth: Dynamic Caloric Deficit &amp; Plateau Guide | GugoPro</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Beyond Linear Weight Loss Myths: From Wishnofsky's 7,700 kcal Rule Flaws to Resistance Periodization and Plateau Breakthroughs: The Definitive Dynamic Fat Loss &amp; Caloric Deficit Guide</t>
+          <t>Beyond Linear Weight Loss Myths: Kevin Hall Dynamic Balance &amp; Plateau Buster</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Decoding YouTube Bilingual Listening &amp; Shadowing: L-Player Mastery &amp; Auditory Neural Shaping Guide | GugoPro Language Science</t>
+          <t>YouTube Bilingual Listening &amp; Shadowing Guide: L-Player Mastery | GugoPro</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Decoding YouTube Bilingual Listening &amp; Shadowing: L-Player Mastery &amp; Auditory Neural Shaping Guide</t>
+          <t>YouTube Bilingual Listening &amp; Shadowing: L-Player System Blueprint</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Why Watching YouTube Fails for English Learning: Speech Perception, Levenshtein Dictation Diff, and Shadowing Guide | GugoPro Language Science</t>
+          <t>Why Watching YouTube Fails for English: Speech Perception &amp; Dictation | GugoPro</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Why Watching YouTube Fails for English Learning: Building Native Auditory Circuits via Speech Perception, Levenshtein Dictation Diff, and Shadowing</t>
+          <t>Overcoming English Listening Plateaus: Connected Speech &amp; Dictation Diff</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2655,12 +2655,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026 YouTube Video Algorithm &amp; Series Retrieval Master Guide: Overcoming Recommendation Gaps via NLP Regex Denoising &amp; Incremental Diff Tracking | GugoPro Streaming Media Lab</t>
+          <t>2026 YouTube Algorithm &amp; Sequel Retrieval: NLP &amp; Diff Tracking | GugoPro</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2026 YouTube Video Algorithm &amp; Series Retrieval Master Guide: Overcoming Recommendation Gaps via NLP Regex Denoising &amp; Incremental Diff Tracking</t>
+          <t>YouTube Recommendation Architecture &amp; Client-Side Sequel Retrieval</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>—（非網頁驗證資產）</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>可見</t>
+          <t>不適用</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>GugoPro 工具箱｜YouTube 雙語字幕學習、AI 翻譯塔羅、TDEE 減脂計算與 Gemini API 配額監控等 9 款免費工具</t>
+          <t>GugoPro 工具箱｜YouTube 雙語學習、AI 對話翻譯與 TDEE 減脂計算器</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>GugoPro 工具箱</t>
+          <t>GugoPro 生產力與生活決策工具箱</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>GugoPro Hub | 9 Free Browser Tools for YouTube Study, AI Translation, Tarot, TDEE &amp; Gemini Quota</t>
+          <t>GugoPro Hub | Client-Side AI, YouTube Study &amp; TDEE Health Tools</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>GugoPro Hub</t>
+          <t>GugoPro Browser Tools &amp; Methodology Hub</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>GugoPro ツールボックス｜YouTube 2言語字幕学習、AI 翻訳タロット、TDEE 減脂計算、Gemini API 配額監視など無料ブラウザツール9選</t>
+          <t>GugoPro ツールボックス｜YouTube 2言語字幕学習・AI対話翻訳・TDEE計算機</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>GugoPro ツールボックス</t>
+          <t>GugoPro ブラウザ完結型・生産性ツールボックス</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>話す恐怖を克服する心理学：クラッシェンの「情意フィルター仮説」、外国語不安（FLA）と AI チューターのゼロ圧力スピーキング完全ガイド｜GugoPro 言語学習コラム</t>
+          <t>英語を話す恐怖を克服する心理学：情意フィルターと AI チューター｜GugoPro</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>話す恐怖を克服する心理学：クラッシェンの「情意フィルター仮説」、外国語不安（FLA）と AI チューターのゼロ圧力スピーキング完全ガイド</t>
+          <t>話す恐怖を克服する心理学：情意フィルター仮説と AI ゼロ圧力スピーキング</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026 越境EC・高精度リサーチ完全攻略：AIセマンティック・リバースエンジニアリングによるAmazonヒット商品開発、競合低評価（VOC）痛点分析とListingキーワード配置マトリクス｜GugoPro EC戦略コラム</t>
+          <t>2026 越境EC Amazon 商品選定：AI 意味論リサーチと低評価分析｜GugoPro</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2026 越境EC・高精度リサーチ完全攻略：AIセマンティック・リバースエンジニアリングによるAmazonヒット商品開発、競合低評価（VOC）痛点分析とListingキーワード配置マトリクス</t>
+          <t>2026 越境EC・高精度リサーチ完全攻略：AIセマンティック反向工学とVOC痛点分析</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>炭水化物循環法（カーボサイクル）完全減脂ガイド：高・低炭水化物日の生化学機序、器具不要の自宅燃焼ルーティン、筋分解防止の極意｜GugoPro 運動生理学コラム</t>
+          <t>カーボサイクル減脂法：高・低炭水化物日と自宅自重筋トレ攻略｜GugoPro</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>炭水化物循環法（カーボサイクル）完全減脂ガイド：高・低炭水化物日の生化学機序、器具不要の自宅燃焼ルーティン、筋分解防止の極意</t>
+          <t>炭水化物循環法（カーボサイクル）完全減脂ガイド：生化学機序と筋分解防止</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>糖尿病予備群・インスリン抵抗性の食事法完全ガイド：GI/GL値・カーボカウントからAI写真食事管理まで——血糖値スパイクを防ぐ栄養素調控｜GugoPro 代謝医学コラム</t>
+          <t>糖尿病予備群・インスリン抵抗性の食事管理：GI/GL値と糖質調整｜GugoPro</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>糖尿病予備群・インスリン抵抗性の食事法完全ガイド：GI/GL値・カーボカウントからAI写真食事管理まで——血糖値スパイクを防ぐ栄養素調控</t>
+          <t>糖尿病予備群・インスリン抵抗性の食事法：血糖値スパイクを防ぐ栄養素管理</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>脂肪肝を逆転する減糖＆地中海食完全ガイド：内臓脂肪燃焼からPFC黄金比率・外食AI管理まで——MASLDを根本改善する長寿実戦マニュアル｜GugoPro 肝臓代謝コラム</t>
+          <t>脂肪肝を逆転する食事法：減糖＆地中海食の外食実践バイブル｜GugoPro</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>脂肪肝を逆転する減糖＆地中海食完全ガイド：内臓脂肪燃焼からPFC黄金比率・外食AI管理まで——MASLDを根本改善する長寿実戦マニュアル</t>
+          <t>脂肪肝 (MASLD) を逆転する減糖＆地中海食：内臓脂肪燃焼と PFC 黄金比率</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026 開発者完全攻略ハンドブック：Google Gemini 公式無料APIを活用したゼロコスト商用グレードアプリのアーキテクチャ設計とエラー完全トラブルシューティング指南｜GugoPro クラウドシステムコラム</t>
+          <t>2026年 Gemini 無料API開発ハンドブック：429エラー完全対策｜GugoPro</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>2026 開発者完全攻略ハンドブック：Google Gemini 公式無料APIを活用したゼロコスト商用グレードアプリのアーキテクチャ設計とエラー完全トラブルシューティング指南</t>
+          <t>Google Gemini 公式無料API開発者完全攻略：商用アーキテクチャと自動縮退</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>タロットマスターへの道：78枚の丸暗記を脱し「直観的フロー・リーディング」へ——古典記号論、ナラティブ心理学、AI協同による限界的練習完全ガイド｜GugoPro 意思決定科学コラム</t>
+          <t>タロットマスターへの道：78枚の記号論と直観的リーディング｜GugoPro</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>如何にしてタロットマスターとなるか？ 78枚の意味の丸暗記から「直観的フロー・リーディング」へ：古典記号論・ナラティブ心理学・AI協同による限界的練習完全手引</t>
+          <t>タロットマスターへの道：78枚の丸暗記を脱し直観的フロー・リーディングへ</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>紫微斗数マスターへの道：百の星の丸暗記を脱し「動態格局解盤」へ——文化記号論、システムダイナミクス、AI協同による限界的練習完全ガイド｜GugoPro 意思決定科学コラム</t>
+          <t>紫微斗数マスターへの道：文化記号論と動的命盤解読の極意｜GugoPro</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>紫微斗数マスターへの道：百の星の丸暗記を脱し「動態格局解盤」へ——文化記号論、システムダイナミクス、AI協同による限界的練習完全ガイド</t>
+          <t>紫微斗数マスターへの道：星の丸暗記を脱し動態格局解盤へ至る実践手引</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>168断食はカロリー計算より本当に痩せるのか？細胞自噬、インスリン仮説からエネルギー赤字の真相まで：リバウンドと筋肉減少の罠を解体する完全ガイド｜GugoPro 代謝内分泌コラム</t>
+          <t>168断食はカロリー計算より痩せるか？オートファジーの真実｜GugoPro</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>168断食はカロリー計算より本当に痩せるのか？細胞自噬、インスリン仮説からエネルギー赤字の真相まで：リバウンドと筋肉減少の罠を解体する完全ガイド</t>
+          <t>168断食はカロリー計算より本当に痩せるのか？オートファジーとリバウンドの罠</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>宿命論とオカルト的脅迫からの脱却：現代心理学で再構築する紫微斗数——十二宮位、四化の動態からAI意思決定反省モデルへ｜GugoPro 意思決定科学コラム</t>
+          <t>現代心理学で再構築する紫微斗数：十二宮位と四化の自己対話｜GugoPro</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>宿命論とオカルト的脅迫からの脱却：現代心理学で再構築する紫微斗数——十二宮位、四化の動態からAI意思決定反省モデルへ</t>
+          <t>宿命論と恐嚇占いにサヨナラ！現代心理学で再構築する紫微斗数と合盤</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3412,12 +3412,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>「話せない英語」にサヨナラ！シャドーイング、CEFR文脈出力、AIチューターによるスピーキング実践ガイド｜GugoPro 言語科学コラム</t>
+          <t>「話せない英語」脱却の科学的自学法：シャドーイングと AI 対話｜GugoPro</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>「話せない英語」にサヨナラ！シャドーイング、CEFR文脈輸出、AIチューターによるスピーキング実践ガイド</t>
+          <t>「話せない英語」にサヨナラ！シャドーイングと CEFR 文脈出力の AI 閉ループ</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>迷信的宿命論からの脱却：ユングの「元型」心理学・共時性からAIタロットへ——キャリアの二者択一と関係性不安を解体する構造化意思決定モデル｜GugoPro 意思決定科学コラム</t>
+          <t>迷信からの脱却！ユング元型心理学・共時性と AI タロット決断｜GugoPro</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>迷信的宿命論からの脱却：ユングの「元型」心理学・共時性からAIタロットへ——キャリアの二者択一と関係性不安を解体する構造化意思決定モデル</t>
+          <t>宿命論を打破する！ユング元型心理学と AI タロットによる意思決定モデル</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>丸暗記にサヨナラ！タスク型教授法（TBLT）、Robinson認知仮説とAIチューターによる英会話実践ガイド｜GugoPro 言語科学コラム</t>
+          <t>丸暗記を脱するタスク型教授法 (TBLT)：AI 英会話実践ハンドブック｜GugoPro</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>丸暗記にサヨナラ！タスク型教授法（TBLT）、Robinson認知仮説とAIチューターによる英会話実践ガイド</t>
+          <t>丸暗記にサヨナラ！タスク型教授法 (TBLT) と AI スピーキング実践ガイド</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>無駄な食事制限とリバウンドを完全に卒業！熱力学エネルギー収支、適応熱産生からAI食事解析まで：外食派のためのTDEE＆PFCバランス精密調整バイブル｜GugoPro 代謝健康專欄</t>
+          <t>リバウンドを完全に卒業！TDEE 計算と PFC バランス管理完全手引｜GugoPro</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>無駄な食事制限とリバウンドを完全に卒業！熱力学エネルギー収支、適応熱産生からAI食事解析まで：外食派のためのTDEE＆PFCバランス精密調整バイブル</t>
+          <t>無駄な食事制限とリバウンドを卒業！TDEE ＆ PFC バランス精密調整バイブル</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>スマホの気まずい手渡しにサヨナラ！180°対面反転UIのデザイン美学・HCI空間心理学と海外旅行会話実践ガイド｜GugoPro 異文化コミュニケーションコラム</t>
+          <t>スマホ手渡しにサヨナラ！180° 対面反転海外旅行音声翻訳手引｜GugoPro</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>スマホの気まずい手渡しにサヨナラ！180°対面反転UIのデザイン美学・HCI空間心理学と海外旅行会話実践ガイド</t>
+          <t>スマホの気まずい手渡しにサヨナラ！180°対面反転UIのデザイン美学と旅行会話</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>線形減量の幻想からの脱却！Wishnofsky 7700kcal法則の破綻からレジスタンストレーニング期分け・停滞期突破まで：動的減量計画とカロリー赤字完全ガイド｜GugoPro 運動生理学コラム</t>
+          <t>7700kcal 神話の崩壊！動的カロリー赤字と減量停滞期突破手引｜GugoPro</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>線形減量の幻想からの脱却！Wishnofsky 7700kcal法則の破綻からレジスタンストレーニング期分け・停滞期突破まで：動的減量計画とカロリー赤字完全ガイド</t>
+          <t>直線的減量神話の崩壊：動的減量計画、筋トレ期分けと停滞期打破の科学</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイングで母語レベルの聴覚神経回路を構築する完全ガイド｜GugoPro 言語科学コラム</t>
+          <t>YouTube 英語精聴＆シャドーイング完全ガイド：L-Player 学習法｜GugoPro</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
+          <t>YouTube 英語精聴・シャドーイング完全手引：L-Player 操作と聴覚神経回路</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、レーベンシュタイン聴解、シャドーイング完全ガイド｜GugoPro 言語科学コラム</t>
+          <t>YouTube 英語学習が挫折する真の理由：音韻知覚とディクテーション｜GugoPro</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>YouTube英語学習が挫折する真の理由とは？音韻知覚理論、 レーベンシュタイン聴解、シャドーイング で母語レベルの聴覚神経回路を構築する完全ガイド</t>
+          <t>YouTube 英語リスニング挫折の真相：音声変化の解読とディクテーション差分</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026年YouTube動画推薦アルゴリズムとシリーズ検索完全ガイド：推薦漏れを解消しNLP正規表現ノイズ除去と差分照合で跨チャンネル追跡を実現する｜GugoPro ストリーミング研究コラム</t>
+          <t>2026年 YouTube アルゴリズムとシリーズ検索：NLP 差分追跡｜GugoPro</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>2026年YouTube動画推薦アルゴリズムとシリーズ検索完全ガイド：推薦漏れを解消し NLP正規表現ノイズ除去と差分照合 で跨チャンネル追跡を実現する</t>
+          <t>YouTube 動画推薦アルゴリズムとシリーズ検索完全ガイド：推薦漏れの解消</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Amazon AI 全品類智能選品導購 | GugoPro</t>
+          <t>Amazon AI 智慧選品助手｜競品差評挖掘、規格矩陣與藍海選品分析 - GugoPro</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>🛒 Amazon AI 智能購物導師</t>
+          <t>Amazon AI 智慧選品助手：差評痛點挖掘與規格矩陣分析</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>AI多國語言對話導師</t>
+          <t>AI 多國語言口說對話導師｜19國情境模擬、發音評分與自訂教材 - GugoPro</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>AI 多國語言情境口說對話導師</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>面對面旅遊對話翻譯｜出國旅遊即時翻譯與雙向語音對話｜GugoPro</t>
+          <t>出國旅遊即時語音翻譯機｜180° 面對面雙向翻轉對話免安裝 - GugoPro</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>面對面旅遊對話翻譯：出國旅遊即時翻譯與雙向語音對話</t>
+          <t>出國旅遊即時語音翻譯機：180° 面對面雙向對話</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>AI 塔羅大師｜五種塔羅牌陣、提問指南與自我反思 - GugoPro</t>
+          <t>AI 塔羅大師｜免費線上抽牌、五大牌陣解讀與每日感情工作指引 - GugoPro</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>AI 塔羅大師：結構化牌陣抽牌與生活決策反思</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>AI 紫微斗數大師｜紫微斗數線上排盤資料整理與十二宮位指南 - GugoPro</t>
+          <t>AI 紫微斗數大師｜免費線上排盤、十二宮位動態解盤與流年合盤 - GugoPro</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>把命盤問題，整理成可行動的洞察</t>
+          <t>AI 紫微斗數大師：線上排盤與十二宮位現代解讀</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>YouTube 續集與新季追蹤器 - GugoPro</t>
+          <t>YouTube 續集與新季追蹤器｜跨頻道自動找下一集、新季數與短劇連載 - GugoPro</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>【AB English Podcast】Ep.1 自我介紹與日常社交對話 (Mia &amp; Alex)｜L-Player</t>
+          <t>YouTube 雙語跟讀播放器｜精聽聽寫、字幕遮罩與影子口說 - GugoPro L-Player</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>YouTube 影音「聽・寫・口說」多國語言跟讀器</t>
+          <t>YouTube 雙語精聽、聽寫與影子跟讀學習機</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>AI 專屬營養師 | GugoPro</t>
+          <t>TDEE 減脂熱量計算機｜BMR 基礎代謝率與三大營養素配比估算 - GugoPro</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>TDEE 減脂熱量計算機與三大營養素配比工具</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>AI減肥瘦身教練｜科學減脂與熱量赤字規劃 | GugoPro</t>
+          <t>AI 科學減重計畫與熱量赤字教練｜突破停滯期與動態減脂目標 - GugoPro</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>AI 科學減重計畫與熱量赤字教練</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>PDF 全能工作站｜免安裝線上閱讀、合併、分割與標註、零檔案外洩 - GugoPro</t>
+          <t>PDF 全能工作站｜免安裝線上閱讀、合併、分割與轉檔 - GugoPro</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>先選擇要處理的文件</t>
+          <t>PDF 全能工作站：瀏覽器本機隱私處理工具</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Gemini API Key 申請教學｜Google Gemini API Key 取得與安全設定教學、免安裝與隱私說明 - GugoPro</t>
+          <t>Gemini API Key 申請教學｜Google AI Studio 免費金鑰取得與安全設定 - GugoPro</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Google Gemini API Key 1 分鐘快速申請步驟</t>
+          <t>Google Gemini API Key 快速申請與安全設定手冊</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Taiwan Pair Trading 線上工具｜免安裝瀏覽器本機處理、零檔案外洩隱私 - GugoPro</t>
+          <t>台股與期貨配對交易掃描儀｜統計套利與價差策略分析 - GugoPro</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>台灣股票與期貨 配對交易掃描工作站</t>
+          <t>台股與期貨配對交易掃描工作站</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">

--- a/seo_inventory_report.xlsx
+++ b/seo_inventory_report.xlsx
@@ -4243,7 +4243,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>❌ 缺失</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>疑似隱藏</t>
+          <t>可見</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>TDEE 減脂熱量計算機｜BMR 基礎代謝率與三大營養素配比估算 - GugoPro</t>
+          <t>AI 專屬營養師｜TDEE 減脂熱量計算機、BMR 與三大營養素拍餐管理 - GugoPro</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>TDEE 減脂熱量計算機與三大營養素配比工具</t>
+          <t>AI 專屬營養師：TDEE 減脂熱量計算機與三大營養素拍餐分析</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>AI 科學減重計畫與熱量赤字教練｜突破停滯期與動態減脂目標 - GugoPro</t>
+          <t>AI 減肥瘦身教練｜科學減重計畫、熱量赤字試算與停滯期動態管理 - GugoPro</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>AI 科學減重計畫與熱量赤字教練</t>
+          <t>AI 減肥瘦身教練：科學減重計畫與動態熱量赤字管理</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">

--- a/seo_inventory_report.xlsx
+++ b/seo_inventory_report.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SEO AdSense 盤點'!$A$1:$K$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SEO AdSense 盤點'!$A$1:$K$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -157,8 +157,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SEOInventory" displayName="SEOInventory" ref="A1:K80" headerRowCount="1">
-  <autoFilter ref="A1:K80"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SEOInventory" displayName="SEOInventory" ref="A1:K78" headerRowCount="1">
+  <autoFilter ref="A1:K78"/>
   <tableColumns count="11">
     <tableColumn id="1" name="編號"/>
     <tableColumn id="2" name="頁面分類"/>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4412,17 +4412,17 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>歷史工具</t>
+          <t>實用教學</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>tools/pdf/pdf-suite.html</t>
+          <t>tools/tutorials/how-to-get-gemini-api-key.html</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>https://gugopro.com/tools/pdf/pdf-suite.html</t>
+          <t>https://gugopro.com/tools/tutorials/how-to-get-gemini-api-key.html</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>PDF 全能工作站｜免安裝線上閱讀、合併、分割與轉檔 - GugoPro</t>
+          <t>Gemini API Key 申請教學｜Google AI Studio 免費金鑰取得與安全設定 - GugoPro</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>PDF 全能工作站：瀏覽器本機隱私處理工具</t>
+          <t>Google Gemini API Key 快速申請與安全設定手冊</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4447,120 +4447,18 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>❌ 未配置（合規）</t>
+          <t>✅ 已配置</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>實用教學</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>tools/tutorials/how-to-get-gemini-api-key.html</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/tutorials/how-to-get-gemini-api-key.html</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>zh-TW</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>Gemini API Key 申請教學｜Google AI Studio 免費金鑰取得與安全設定 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>Google Gemini API Key 快速申請與安全設定手冊</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>✅ 已配置</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="K79" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>歷史工具</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>tools/tw-market/taiwan-pair-trading.html</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>https://gugopro.com/tools/tw-market/taiwan-pair-trading.html</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>zh-Hant-TW</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>台股與期貨配對交易掃描儀｜統計套利與價差策略分析 - GugoPro</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>台股與期貨配對交易掃描工作站</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>可見</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>❌ 未配置（合規）</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="K80" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K80"/>
+  <autoFilter ref="A1:K78"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -4639,12 +4537,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId79"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId80"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId78"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4681,7 +4577,7 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
@@ -4711,7 +4607,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4791,7 +4687,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/seo_inventory_report.xlsx
+++ b/seo_inventory_report.xlsx
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>2</v>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>脂肪肝 (MASLD) を逆転する減糖＆地中海食：内臓脂肪燃焼と PFC 黄金比率</t>
+          <t>脂肪肝 (MASLD) 対策と代謝サポートする減糖＆地中海食：内臓脂肪燃焼と PFC 黄金比率</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -11336,7 +11336,7 @@
         </is>
       </c>
       <c r="J213" s="2" t="n">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="K213" s="2" t="n">
         <v>2</v>
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="J214" s="2" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K214" s="2" t="n">
         <v>2</v>
